--- a/inventory_master.xlsx
+++ b/inventory_master.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,11 @@
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -191,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -241,6 +246,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -853,27 +870,27 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -881,9 +898,7 @@
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n"/>
       <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n">
-        <v>6</v>
-      </c>
+      <c r="I4" s="10" t="n"/>
       <c r="J4" s="10" t="n"/>
       <c r="K4" s="10" t="inlineStr">
         <is>
@@ -897,27 +912,27 @@
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -925,9 +940,7 @@
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n">
-        <v>6</v>
-      </c>
+      <c r="I5" s="10" t="n"/>
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="inlineStr">
         <is>
@@ -941,27 +954,27 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -969,9 +982,7 @@
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
       <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n">
-        <v>6</v>
-      </c>
+      <c r="I6" s="10" t="n"/>
       <c r="J6" s="10" t="n"/>
       <c r="K6" s="10" t="inlineStr">
         <is>
@@ -1055,27 +1066,27 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1083,9 +1094,7 @@
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n"/>
-      <c r="I9" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
       <c r="K9" s="10" t="inlineStr">
         <is>
@@ -1099,27 +1108,27 @@
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1127,9 +1136,7 @@
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I10" s="10" t="n"/>
       <c r="J10" s="10" t="n"/>
       <c r="K10" s="10" t="inlineStr">
         <is>
@@ -1143,27 +1150,27 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1171,9 +1178,7 @@
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n"/>
-      <c r="I11" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I11" s="10" t="n"/>
       <c r="J11" s="10" t="n"/>
       <c r="K11" s="10" t="inlineStr">
         <is>
@@ -1187,27 +1192,27 @@
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1215,9 +1220,7 @@
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I12" s="10" t="n"/>
       <c r="J12" s="10" t="n"/>
       <c r="K12" s="10" t="inlineStr">
         <is>
@@ -1231,27 +1234,27 @@
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1259,9 +1262,7 @@
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I13" s="10" t="n"/>
       <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="inlineStr">
         <is>
@@ -1275,27 +1276,27 @@
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1303,9 +1304,7 @@
       <c r="F14" s="10" t="n"/>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I14" s="10" t="n"/>
       <c r="J14" s="10" t="n"/>
       <c r="K14" s="10" t="inlineStr">
         <is>
@@ -1389,27 +1388,27 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -1417,9 +1416,7 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="14" t="n"/>
       <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="I17" s="14" t="n"/>
       <c r="J17" s="14" t="n"/>
       <c r="K17" s="14" t="inlineStr">
         <is>
@@ -1517,27 +1514,27 @@
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -1545,9 +1542,7 @@
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I21" s="10" t="n"/>
       <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1561,27 +1556,27 @@
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -1589,9 +1584,7 @@
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="10" t="n"/>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I22" s="10" t="n"/>
       <c r="J22" s="10" t="n"/>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1605,27 +1598,27 @@
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -1633,9 +1626,7 @@
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n"/>
-      <c r="I23" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I23" s="10" t="n"/>
       <c r="J23" s="10" t="n"/>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1649,27 +1640,27 @@
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -1677,9 +1668,7 @@
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I24" s="10" t="n"/>
       <c r="J24" s="10" t="n"/>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1763,27 +1752,27 @@
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1791,9 +1780,7 @@
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I27" s="10" t="n"/>
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="inlineStr">
         <is>
@@ -1807,27 +1794,27 @@
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1835,9 +1822,7 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="14" t="n"/>
       <c r="H28" s="14" t="n"/>
-      <c r="I28" s="14" t="n">
-        <v>8</v>
-      </c>
+      <c r="I28" s="14" t="n"/>
       <c r="J28" s="14" t="n"/>
       <c r="K28" s="14" t="inlineStr">
         <is>
@@ -1935,27 +1920,27 @@
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -1963,9 +1948,7 @@
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I32" s="10" t="n"/>
       <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="inlineStr">
         <is>
@@ -1979,27 +1962,27 @@
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -2007,9 +1990,7 @@
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I33" s="10" t="n"/>
       <c r="J33" s="10" t="n"/>
       <c r="K33" s="10" t="inlineStr">
         <is>
@@ -2023,27 +2004,27 @@
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -2051,9 +2032,7 @@
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="10" t="n"/>
       <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I34" s="10" t="n"/>
       <c r="J34" s="10" t="n"/>
       <c r="K34" s="10" t="inlineStr">
         <is>
@@ -2067,27 +2046,27 @@
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -2095,9 +2074,7 @@
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I35" s="10" t="n"/>
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="inlineStr">
         <is>
@@ -2111,27 +2088,27 @@
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -2139,9 +2116,7 @@
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I36" s="10" t="n"/>
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="inlineStr">
         <is>
@@ -2225,27 +2200,27 @@
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2253,9 +2228,7 @@
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n">
-        <v>9</v>
-      </c>
+      <c r="I39" s="10" t="n"/>
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="inlineStr">
         <is>
@@ -2269,27 +2242,27 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2297,9 +2270,7 @@
       <c r="F40" s="10" t="n"/>
       <c r="G40" s="10" t="n"/>
       <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n">
-        <v>9</v>
-      </c>
+      <c r="I40" s="10" t="n"/>
       <c r="J40" s="10" t="n"/>
       <c r="K40" s="10" t="inlineStr">
         <is>
@@ -2467,27 +2438,27 @@
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2495,9 +2466,7 @@
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
       <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I46" s="10" t="n"/>
       <c r="J46" s="10" t="n"/>
       <c r="K46" s="10" t="inlineStr">
         <is>
@@ -2511,27 +2480,27 @@
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2539,9 +2508,7 @@
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I47" s="10" t="n"/>
       <c r="J47" s="10" t="n"/>
       <c r="K47" s="10" t="inlineStr">
         <is>
@@ -2555,27 +2522,27 @@
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2583,9 +2550,7 @@
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="10" t="n"/>
       <c r="H48" s="10" t="n"/>
-      <c r="I48" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I48" s="10" t="n"/>
       <c r="J48" s="10" t="n"/>
       <c r="K48" s="10" t="inlineStr">
         <is>
@@ -2599,27 +2564,27 @@
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2627,9 +2592,7 @@
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I49" s="10" t="n"/>
       <c r="J49" s="10" t="n"/>
       <c r="K49" s="10" t="inlineStr">
         <is>
@@ -2643,27 +2606,27 @@
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2671,9 +2634,7 @@
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
       <c r="H50" s="10" t="n"/>
-      <c r="I50" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I50" s="10" t="n"/>
       <c r="J50" s="10" t="n"/>
       <c r="K50" s="10" t="inlineStr">
         <is>
@@ -2687,27 +2648,27 @@
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2715,9 +2676,7 @@
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
-      <c r="I51" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I51" s="10" t="n"/>
       <c r="J51" s="10" t="n"/>
       <c r="K51" s="10" t="inlineStr">
         <is>
@@ -2731,27 +2690,27 @@
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="E52" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2759,9 +2718,7 @@
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n">
-        <v>8</v>
-      </c>
+      <c r="I52" s="10" t="n"/>
       <c r="J52" s="10" t="n"/>
       <c r="K52" s="10" t="inlineStr">
         <is>
@@ -2845,27 +2802,27 @@
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" s="22" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" s="22" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="E55" s="22" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
@@ -2873,9 +2830,7 @@
       <c r="F55" s="14" t="n"/>
       <c r="G55" s="14" t="n"/>
       <c r="H55" s="14" t="n"/>
-      <c r="I55" s="14" t="n">
-        <v>6</v>
-      </c>
+      <c r="I55" s="14" t="n"/>
       <c r="J55" s="14" t="n"/>
       <c r="K55" s="14" t="inlineStr">
         <is>
@@ -2973,27 +2928,27 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>Malaga</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B59" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="20" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E59" s="20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3001,9 +2956,7 @@
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n">
-        <v>5</v>
-      </c>
+      <c r="I59" s="10" t="n"/>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="10" t="inlineStr">
         <is>
@@ -3017,27 +2970,27 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>Malaga</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="20" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="D60" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="E60" s="20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3045,9 +2998,7 @@
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="n">
-        <v>5</v>
-      </c>
+      <c r="I60" s="10" t="n"/>
       <c r="J60" s="10" t="n"/>
       <c r="K60" s="10" t="inlineStr">
         <is>
@@ -3061,27 +3012,27 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>Malaga</t>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="B61" s="22" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C61" s="22" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D61" s="22" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E61" s="22" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3089,9 +3040,7 @@
       <c r="F61" s="14" t="n"/>
       <c r="G61" s="14" t="n"/>
       <c r="H61" s="14" t="n"/>
-      <c r="I61" s="14" t="n">
-        <v>5</v>
-      </c>
+      <c r="I61" s="14" t="n"/>
       <c r="J61" s="14" t="n"/>
       <c r="K61" s="14" t="inlineStr">
         <is>
@@ -3189,27 +3138,27 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B65" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="20" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D65" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E65" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -3217,9 +3166,7 @@
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n">
-        <v>6</v>
-      </c>
+      <c r="I65" s="10" t="n"/>
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="inlineStr">
         <is>
@@ -3233,27 +3180,27 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="B66" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="20" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E66" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -3261,9 +3208,7 @@
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="10" t="n"/>
       <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n">
-        <v>6</v>
-      </c>
+      <c r="I66" s="10" t="n"/>
       <c r="J66" s="10" t="n"/>
       <c r="K66" s="10" t="inlineStr">
         <is>
@@ -3277,27 +3222,27 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="20" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="D67" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="E67" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -3305,9 +3250,7 @@
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n">
-        <v>6</v>
-      </c>
+      <c r="I67" s="10" t="n"/>
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="10" t="inlineStr">
         <is>
@@ -3321,27 +3264,27 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" s="20" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C68" s="20" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D68" s="20" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E68" s="20" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -3349,9 +3292,7 @@
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="n">
-        <v>6</v>
-      </c>
+      <c r="I68" s="10" t="n"/>
       <c r="J68" s="10" t="n"/>
       <c r="K68" s="10" t="inlineStr">
         <is>
@@ -3435,27 +3376,27 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D71" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E71" s="20" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -3463,9 +3404,7 @@
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I71" s="10" t="n"/>
       <c r="J71" s="10" t="n"/>
       <c r="K71" s="10" t="inlineStr">
         <is>
@@ -3479,27 +3418,27 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" s="20" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="D72" s="20" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="E72" s="20" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -3507,9 +3446,7 @@
       <c r="F72" s="10" t="n"/>
       <c r="G72" s="10" t="n"/>
       <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n">
-        <v>7</v>
-      </c>
+      <c r="I72" s="10" t="n"/>
       <c r="J72" s="10" t="n"/>
       <c r="K72" s="10" t="inlineStr">
         <is>

--- a/inventory_master.xlsx
+++ b/inventory_master.xlsx
@@ -362,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -536,29 +536,23 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -986,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L133"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1080,27 +1074,27 @@
       <c r="L2" s="24" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>Altea Double Door</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C3" s="71" t="inlineStr">
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D3" s="71" t="inlineStr">
+      <c r="D3" s="69" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E3" s="71" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1312,27 +1306,27 @@
       <c r="L8" s="39" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>Altea Double Door</t>
         </is>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C9" s="73" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D9" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E9" s="73" t="inlineStr">
+      <c r="C9" s="66" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E9" s="66" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -1559,7 +1553,7 @@
       <c r="G14" s="42" t="n"/>
       <c r="H14" s="42" t="n"/>
       <c r="I14" s="32" t="n"/>
-      <c r="J14" s="43" t="n"/>
+      <c r="J14" s="42" t="n"/>
       <c r="K14" s="42" t="n"/>
       <c r="L14" s="36" t="inlineStr">
         <is>
@@ -1620,27 +1614,27 @@
       <c r="L16" s="39" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="A17" s="65" t="inlineStr">
         <is>
           <t>Altea Double Door</t>
         </is>
       </c>
-      <c r="B17" s="73" t="inlineStr">
+      <c r="B17" s="66" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C17" s="73" t="inlineStr">
+      <c r="C17" s="66" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D17" s="73" t="inlineStr">
+      <c r="D17" s="66" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E17" s="73" t="inlineStr">
+      <c r="E17" s="66" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
@@ -1684,27 +1678,27 @@
       <c r="L18" s="39" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="65" t="inlineStr">
         <is>
           <t>Altea Double Door</t>
         </is>
       </c>
-      <c r="B19" s="73" t="inlineStr">
+      <c r="B19" s="66" t="inlineStr">
         <is>
           <t>72" x 80"</t>
         </is>
       </c>
-      <c r="C19" s="73" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D19" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E19" s="73" t="inlineStr">
+      <c r="C19" s="66" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D19" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E19" s="66" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1853,7 +1847,7 @@
           <t>26-0625-0076</t>
         </is>
       </c>
-      <c r="L22" s="65" t="inlineStr">
+      <c r="L22" s="67" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-001</t>
         </is>
@@ -1874,41 +1868,41 @@
       <c r="L23" s="42" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="38" t="n"/>
-      <c r="B24" s="38" t="n"/>
-      <c r="C24" s="38" t="n"/>
-      <c r="D24" s="38" t="n"/>
-      <c r="E24" s="38" t="n"/>
-      <c r="F24" s="38" t="n"/>
-      <c r="G24" s="38" t="n"/>
-      <c r="H24" s="38" t="n"/>
-      <c r="I24" s="38" t="n"/>
-      <c r="J24" s="38" t="n"/>
-      <c r="K24" s="38" t="n"/>
-      <c r="L24" s="42" t="n"/>
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="24" t="n"/>
+      <c r="L24" s="63" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="70" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>Cordova Sliding Window</t>
         </is>
       </c>
-      <c r="B25" s="71" t="inlineStr">
+      <c r="B25" s="69" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C25" s="71" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D25" s="71" t="inlineStr">
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D25" s="69" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E25" s="71" t="inlineStr">
+      <c r="E25" s="69" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -1920,11 +1914,11 @@
         <v>0</v>
       </c>
       <c r="H25" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="68" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="I25" s="70" t="n"/>
       <c r="J25" s="27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K25" s="27" t="inlineStr">
         <is>
@@ -1963,11 +1957,11 @@
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F26" s="42" t="n"/>
-      <c r="G26" s="42" t="n"/>
-      <c r="H26" s="42" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="43" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="n"/>
       <c r="K26" s="42" t="inlineStr">
         <is>
           <t>25-0210-0002</t>
@@ -2005,11 +1999,11 @@
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F27" s="32" t="n"/>
-      <c r="G27" s="32" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="32" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="n"/>
       <c r="K27" s="42" t="inlineStr">
         <is>
           <t>25-0210-0003</t>
@@ -2047,11 +2041,11 @@
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F28" s="32" t="n"/>
-      <c r="G28" s="32" t="n"/>
-      <c r="H28" s="32" t="n"/>
-      <c r="I28" s="32" t="n"/>
-      <c r="J28" s="32" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="n"/>
       <c r="K28" s="42" t="inlineStr">
         <is>
           <t>25-0210-0004</t>
@@ -2089,11 +2083,11 @@
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F29" s="32" t="n"/>
-      <c r="G29" s="32" t="n"/>
-      <c r="H29" s="32" t="n"/>
-      <c r="I29" s="32" t="n"/>
-      <c r="J29" s="32" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="n"/>
       <c r="K29" s="42" t="inlineStr">
         <is>
           <t>25-0210-0005</t>
@@ -2131,11 +2125,11 @@
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F30" s="32" t="n"/>
-      <c r="G30" s="32" t="n"/>
-      <c r="H30" s="32" t="n"/>
-      <c r="I30" s="32" t="n"/>
-      <c r="J30" s="32" t="n"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="n"/>
       <c r="K30" s="42" t="inlineStr">
         <is>
           <t>25-0210-0006</t>
@@ -2148,66 +2142,86 @@
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="37" t="n"/>
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="38" t="n"/>
-      <c r="E31" s="38" t="n"/>
-      <c r="F31" s="38" t="n"/>
-      <c r="G31" s="38" t="n"/>
-      <c r="H31" s="38" t="n"/>
-      <c r="I31" s="38" t="n"/>
-      <c r="J31" s="38" t="n"/>
-      <c r="K31" s="38" t="n"/>
-      <c r="L31" s="39" t="n"/>
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="24" t="n"/>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="24" t="n"/>
+      <c r="K31" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0028</t>
+        </is>
+      </c>
+      <c r="L31" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="72" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>Cordova Sliding Window</t>
         </is>
       </c>
-      <c r="B32" s="73" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C32" s="73" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D32" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E32" s="73" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F32" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="32" t="n"/>
-      <c r="J32" s="42" t="n">
-        <v>3</v>
-      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="24" t="n"/>
       <c r="K32" s="42" t="inlineStr">
         <is>
-          <t>25-0518-0007</t>
-        </is>
-      </c>
-      <c r="L32" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0604-0029</t>
+        </is>
+      </c>
+      <c r="L32" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
@@ -2219,37 +2233,37 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C33" s="35" t="inlineStr">
         <is>
-          <t>Oil-Rubbed Bronze</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="D33" s="35" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E33" s="35" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="32" t="n"/>
-      <c r="H33" s="32" t="n"/>
-      <c r="I33" s="32" t="n"/>
-      <c r="J33" s="32" t="n"/>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="38" t="n"/>
+      <c r="H33" s="38" t="n"/>
+      <c r="I33" s="38" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="42" t="inlineStr">
         <is>
-          <t>25-0518-0008</t>
-        </is>
-      </c>
-      <c r="L33" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0604-0030</t>
+        </is>
+      </c>
+      <c r="L33" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
@@ -2261,165 +2275,185 @@
       </c>
       <c r="B34" s="35" t="inlineStr">
         <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="38" t="n"/>
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="38" t="n"/>
+      <c r="J34" s="38" t="n"/>
+      <c r="K34" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0031</t>
+        </is>
+      </c>
+      <c r="L34" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D35" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F35" s="42" t="n"/>
+      <c r="G35" s="42" t="n"/>
+      <c r="H35" s="42" t="n"/>
+      <c r="I35" s="32" t="n"/>
+      <c r="J35" s="43" t="n"/>
+      <c r="K35" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0032</t>
+        </is>
+      </c>
+      <c r="L35" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D36" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F36" s="32" t="n"/>
+      <c r="G36" s="32" t="n"/>
+      <c r="H36" s="32" t="n"/>
+      <c r="I36" s="32" t="n"/>
+      <c r="J36" s="32" t="n"/>
+      <c r="K36" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0033</t>
+        </is>
+      </c>
+      <c r="L36" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="31" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="32" t="n"/>
+      <c r="H37" s="32" t="n"/>
+      <c r="I37" s="32" t="n"/>
+      <c r="J37" s="32" t="n"/>
+      <c r="K37" s="32" t="n"/>
+      <c r="L37" s="39" t="n"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="65" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B38" s="66" t="inlineStr">
+        <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C38" s="66" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D34" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E34" s="35" t="inlineStr">
+      <c r="D38" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E38" s="66" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="32" t="n"/>
-      <c r="H34" s="32" t="n"/>
-      <c r="I34" s="32" t="n"/>
-      <c r="J34" s="32" t="n"/>
-      <c r="K34" s="42" t="inlineStr">
-        <is>
-          <t>25-0518-0009</t>
-        </is>
-      </c>
-      <c r="L34" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="34" t="n"/>
-      <c r="B35" s="35" t="n"/>
-      <c r="C35" s="35" t="n"/>
-      <c r="D35" s="35" t="n"/>
-      <c r="E35" s="35" t="n"/>
-      <c r="F35" s="24" t="n"/>
-      <c r="G35" s="24" t="n"/>
-      <c r="H35" s="24" t="n"/>
-      <c r="I35" s="24" t="n"/>
-      <c r="J35" s="24" t="n"/>
-      <c r="K35" s="42" t="n"/>
-      <c r="L35" s="39" t="n"/>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="72" t="inlineStr">
-        <is>
-          <t>Cordova Sliding Window</t>
-        </is>
-      </c>
-      <c r="B36" s="73" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C36" s="73" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D36" s="73" t="inlineStr">
-        <is>
-          <t>Right Outswing</t>
-        </is>
-      </c>
-      <c r="E36" s="73" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F36" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="24" t="n"/>
-      <c r="J36" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="42" t="inlineStr">
-        <is>
-          <t>25-0518-0010</t>
-        </is>
-      </c>
-      <c r="L36" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="34" t="n"/>
-      <c r="B37" s="35" t="n"/>
-      <c r="C37" s="35" t="n"/>
-      <c r="D37" s="35" t="n"/>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="24" t="n"/>
-      <c r="G37" s="24" t="n"/>
-      <c r="H37" s="24" t="n"/>
-      <c r="I37" s="24" t="n"/>
-      <c r="J37" s="24" t="n"/>
-      <c r="K37" s="24" t="n"/>
-      <c r="L37" s="39" t="n"/>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="72" t="inlineStr">
-        <is>
-          <t>Cordova Sliding Window</t>
-        </is>
-      </c>
-      <c r="B38" s="73" t="inlineStr">
-        <is>
-          <t>48" x 36"</t>
-        </is>
-      </c>
-      <c r="C38" s="73" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D38" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E38" s="73" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
       <c r="F38" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G38" s="42" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="I38" s="24" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="32" t="n"/>
       <c r="J38" s="42" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K38" s="42" t="inlineStr">
         <is>
-          <t>26-0604-0034</t>
-        </is>
-      </c>
-      <c r="L38" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>25-0518-0007</t>
+        </is>
+      </c>
+      <c r="L38" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2465,12 @@
       </c>
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>48" x 36"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C39" s="35" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
       <c r="D39" s="35" t="inlineStr">
@@ -2449,19 +2483,19 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="n"/>
-      <c r="I39" s="24" t="n"/>
-      <c r="J39" s="24" t="n"/>
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="32" t="n"/>
+      <c r="H39" s="32" t="n"/>
+      <c r="I39" s="32" t="n"/>
+      <c r="J39" s="32" t="n"/>
       <c r="K39" s="42" t="inlineStr">
         <is>
-          <t>26-0604-0035</t>
-        </is>
-      </c>
-      <c r="L39" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>25-0518-0008</t>
+        </is>
+      </c>
+      <c r="L39" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -2473,200 +2507,160 @@
       </c>
       <c r="B40" s="35" t="inlineStr">
         <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>Oil-Rubbed Bronze</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F40" s="38" t="n"/>
+      <c r="G40" s="38" t="n"/>
+      <c r="H40" s="38" t="n"/>
+      <c r="I40" s="38" t="n"/>
+      <c r="J40" s="38" t="n"/>
+      <c r="K40" s="42" t="inlineStr">
+        <is>
+          <t>25-0518-0009</t>
+        </is>
+      </c>
+      <c r="L40" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="40" t="n"/>
+      <c r="B41" s="41" t="n"/>
+      <c r="C41" s="41" t="n"/>
+      <c r="D41" s="41" t="n"/>
+      <c r="E41" s="41" t="n"/>
+      <c r="F41" s="42" t="n"/>
+      <c r="G41" s="42" t="n"/>
+      <c r="H41" s="42" t="n"/>
+      <c r="I41" s="32" t="n"/>
+      <c r="J41" s="43" t="n"/>
+      <c r="K41" s="32" t="n"/>
+      <c r="L41" s="39" t="n"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="65" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B42" s="66" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C42" s="66" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D42" s="66" t="inlineStr">
+        <is>
+          <t>Right Outswing</t>
+        </is>
+      </c>
+      <c r="E42" s="66" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F42" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="32" t="n"/>
+      <c r="J42" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42" t="inlineStr">
+        <is>
+          <t>25-0518-0010</t>
+        </is>
+      </c>
+      <c r="L42" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="31" t="n"/>
+      <c r="C43" s="31" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="31" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="32" t="n"/>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="32" t="n"/>
+      <c r="J43" s="32" t="n"/>
+      <c r="K43" s="32" t="n"/>
+      <c r="L43" s="39" t="n"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="65" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B44" s="66" t="inlineStr">
+        <is>
           <t>48" x 36"</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D40" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E40" s="35" t="inlineStr">
+      <c r="C44" s="66" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D44" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E44" s="66" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F40" s="42" t="n"/>
-      <c r="G40" s="42" t="n"/>
-      <c r="H40" s="42" t="n"/>
-      <c r="I40" s="24" t="n"/>
-      <c r="J40" s="42" t="n"/>
-      <c r="K40" s="42" t="inlineStr">
-        <is>
-          <t>26-0604-0036</t>
-        </is>
-      </c>
-      <c r="L40" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>Cordova Sliding Window</t>
-        </is>
-      </c>
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>48" x 36"</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D41" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E41" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="n"/>
-      <c r="G41" s="24" t="n"/>
-      <c r="H41" s="24" t="n"/>
-      <c r="I41" s="24" t="n"/>
-      <c r="J41" s="24" t="n"/>
-      <c r="K41" s="42" t="inlineStr">
-        <is>
-          <t>26-0604-0037</t>
-        </is>
-      </c>
-      <c r="L41" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="34" t="inlineStr">
-        <is>
-          <t>Cordova Sliding Window</t>
-        </is>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>48" x 36"</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D42" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E42" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="n"/>
-      <c r="G42" s="24" t="n"/>
-      <c r="H42" s="24" t="n"/>
-      <c r="I42" s="24" t="n"/>
-      <c r="J42" s="24" t="n"/>
-      <c r="K42" s="42" t="inlineStr">
-        <is>
-          <t>26-0604-0038</t>
-        </is>
-      </c>
-      <c r="L42" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>Cordova Sliding Window</t>
-        </is>
-      </c>
-      <c r="B43" s="35" t="inlineStr">
-        <is>
-          <t>48" x 36"</t>
-        </is>
-      </c>
-      <c r="C43" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D43" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E43" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="n"/>
-      <c r="G43" s="24" t="n"/>
-      <c r="H43" s="24" t="n"/>
-      <c r="I43" s="24" t="n"/>
-      <c r="J43" s="24" t="n"/>
-      <c r="K43" s="42" t="inlineStr">
-        <is>
-          <t>26-0604-0039</t>
-        </is>
-      </c>
-      <c r="L43" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="34" t="inlineStr">
-        <is>
-          <t>Cordova Sliding Window</t>
-        </is>
-      </c>
-      <c r="B44" s="35" t="inlineStr">
-        <is>
-          <t>48" x 36"</t>
-        </is>
-      </c>
-      <c r="C44" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D44" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E44" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F44" s="24" t="n"/>
-      <c r="G44" s="24" t="n"/>
-      <c r="H44" s="24" t="n"/>
+      <c r="F44" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="42" t="n">
+        <v>12</v>
+      </c>
       <c r="I44" s="24" t="n"/>
-      <c r="J44" s="24" t="n"/>
+      <c r="J44" s="42" t="n">
+        <v>12</v>
+      </c>
       <c r="K44" s="42" t="inlineStr">
         <is>
-          <t>26-0604-0040</t>
+          <t>26-0604-0034</t>
         </is>
       </c>
       <c r="L44" s="64" t="inlineStr">
@@ -2701,14 +2695,14 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F45" s="38" t="n"/>
-      <c r="G45" s="38" t="n"/>
-      <c r="H45" s="38" t="n"/>
-      <c r="I45" s="38" t="n"/>
-      <c r="J45" s="38" t="n"/>
+      <c r="F45" s="24" t="n"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="24" t="n"/>
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="24" t="n"/>
       <c r="K45" s="42" t="inlineStr">
         <is>
-          <t>26-0604-0041</t>
+          <t>26-0604-0035</t>
         </is>
       </c>
       <c r="L45" s="64" t="inlineStr">
@@ -2743,14 +2737,14 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F46" s="38" t="n"/>
-      <c r="G46" s="38" t="n"/>
-      <c r="H46" s="38" t="n"/>
-      <c r="I46" s="38" t="n"/>
-      <c r="J46" s="38" t="n"/>
+      <c r="F46" s="24" t="n"/>
+      <c r="G46" s="24" t="n"/>
+      <c r="H46" s="24" t="n"/>
+      <c r="I46" s="24" t="n"/>
+      <c r="J46" s="24" t="n"/>
       <c r="K46" s="42" t="inlineStr">
         <is>
-          <t>26-0604-0042</t>
+          <t>26-0604-0036</t>
         </is>
       </c>
       <c r="L46" s="64" t="inlineStr">
@@ -2785,14 +2779,14 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F47" s="42" t="n"/>
-      <c r="G47" s="42" t="n"/>
-      <c r="H47" s="42" t="n"/>
-      <c r="I47" s="32" t="n"/>
-      <c r="J47" s="43" t="n"/>
+      <c r="F47" s="24" t="n"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="24" t="n"/>
+      <c r="I47" s="24" t="n"/>
+      <c r="J47" s="24" t="n"/>
       <c r="K47" s="42" t="inlineStr">
         <is>
-          <t>26-0604-0043</t>
+          <t>26-0604-0037</t>
         </is>
       </c>
       <c r="L47" s="64" t="inlineStr">
@@ -2827,14 +2821,14 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F48" s="32" t="n"/>
-      <c r="G48" s="32" t="n"/>
-      <c r="H48" s="32" t="n"/>
-      <c r="I48" s="32" t="n"/>
-      <c r="J48" s="32" t="n"/>
+      <c r="F48" s="24" t="n"/>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="24" t="n"/>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="24" t="n"/>
       <c r="K48" s="42" t="inlineStr">
         <is>
-          <t>26-0604-0044</t>
+          <t>26-0604-0038</t>
         </is>
       </c>
       <c r="L48" s="64" t="inlineStr">
@@ -2844,134 +2838,182 @@
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="49" t="inlineStr">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>Cordova Sliding Window</t>
         </is>
       </c>
-      <c r="B49" s="50" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>48" x 36"</t>
         </is>
       </c>
-      <c r="C49" s="50" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D49" s="50" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E49" s="50" t="inlineStr">
+      <c r="C49" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E49" s="35" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F49" s="46" t="n"/>
-      <c r="G49" s="46" t="n"/>
-      <c r="H49" s="46" t="n"/>
-      <c r="I49" s="46" t="n"/>
-      <c r="J49" s="46" t="n"/>
-      <c r="K49" s="55" t="inlineStr">
-        <is>
-          <t>26-0604-0045</t>
-        </is>
-      </c>
-      <c r="L49" s="65" t="inlineStr">
+      <c r="F49" s="42" t="n"/>
+      <c r="G49" s="42" t="n"/>
+      <c r="H49" s="42" t="n"/>
+      <c r="I49" s="24" t="n"/>
+      <c r="J49" s="42" t="n"/>
+      <c r="K49" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0039</t>
+        </is>
+      </c>
+      <c r="L49" s="64" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="31" t="n"/>
-      <c r="B50" s="31" t="n"/>
-      <c r="C50" s="31" t="n"/>
-      <c r="D50" s="31" t="n"/>
-      <c r="E50" s="31" t="n"/>
-      <c r="F50" s="32" t="n"/>
-      <c r="G50" s="32" t="n"/>
-      <c r="H50" s="32" t="n"/>
-      <c r="I50" s="32" t="n"/>
-      <c r="J50" s="32" t="n"/>
-      <c r="K50" s="32" t="n"/>
-      <c r="L50" s="42" t="n"/>
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B50" s="35" t="inlineStr">
+        <is>
+          <t>48" x 36"</t>
+        </is>
+      </c>
+      <c r="C50" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="n"/>
+      <c r="G50" s="24" t="n"/>
+      <c r="H50" s="24" t="n"/>
+      <c r="I50" s="24" t="n"/>
+      <c r="J50" s="24" t="n"/>
+      <c r="K50" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0040</t>
+        </is>
+      </c>
+      <c r="L50" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="31" t="n"/>
-      <c r="B51" s="31" t="n"/>
-      <c r="C51" s="31" t="n"/>
-      <c r="D51" s="31" t="n"/>
-      <c r="E51" s="31" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
-      <c r="H51" s="32" t="n"/>
-      <c r="I51" s="32" t="n"/>
-      <c r="J51" s="32" t="n"/>
-      <c r="K51" s="32" t="n"/>
-      <c r="L51" s="42" t="n"/>
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B51" s="35" t="inlineStr">
+        <is>
+          <t>48" x 36"</t>
+        </is>
+      </c>
+      <c r="C51" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="n"/>
+      <c r="G51" s="24" t="n"/>
+      <c r="H51" s="24" t="n"/>
+      <c r="I51" s="24" t="n"/>
+      <c r="J51" s="24" t="n"/>
+      <c r="K51" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0041</t>
+        </is>
+      </c>
+      <c r="L51" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="70" t="inlineStr">
-        <is>
-          <t>Granada Bi-fold Door</t>
-        </is>
-      </c>
-      <c r="B52" s="71" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C52" s="71" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D52" s="71" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E52" s="71" t="inlineStr">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B52" s="35" t="inlineStr">
+        <is>
+          <t>48" x 36"</t>
+        </is>
+      </c>
+      <c r="C52" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E52" s="35" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F52" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="G52" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="28" t="n"/>
-      <c r="J52" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="K52" s="27" t="inlineStr">
-        <is>
-          <t>25-0927-0011</t>
-        </is>
-      </c>
-      <c r="L52" s="29" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+      <c r="F52" s="24" t="n"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="24" t="n"/>
+      <c r="I52" s="24" t="n"/>
+      <c r="J52" s="24" t="n"/>
+      <c r="K52" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0042</t>
+        </is>
+      </c>
+      <c r="L52" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="34" t="inlineStr">
         <is>
-          <t>Granada Bi-fold Door</t>
+          <t>Cordova Sliding Window</t>
         </is>
       </c>
       <c r="B53" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>48" x 36"</t>
         </is>
       </c>
       <c r="C53" s="35" t="inlineStr">
@@ -2981,7 +3023,7 @@
       </c>
       <c r="D53" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E53" s="35" t="inlineStr">
@@ -2989,227 +3031,179 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F53" s="38" t="n"/>
-      <c r="G53" s="38" t="n"/>
-      <c r="H53" s="38" t="n"/>
-      <c r="I53" s="38" t="n"/>
-      <c r="J53" s="38" t="n"/>
+      <c r="F53" s="24" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="24" t="n"/>
+      <c r="J53" s="24" t="n"/>
       <c r="K53" s="42" t="inlineStr">
         <is>
-          <t>25-0927-0012</t>
-        </is>
-      </c>
-      <c r="L53" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0604-0043</t>
+        </is>
+      </c>
+      <c r="L53" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="34" t="inlineStr">
         <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B54" s="35" t="inlineStr">
+        <is>
+          <t>48" x 36"</t>
+        </is>
+      </c>
+      <c r="C54" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F54" s="38" t="n"/>
+      <c r="G54" s="38" t="n"/>
+      <c r="H54" s="38" t="n"/>
+      <c r="I54" s="38" t="n"/>
+      <c r="J54" s="38" t="n"/>
+      <c r="K54" s="42" t="inlineStr">
+        <is>
+          <t>26-0604-0044</t>
+        </is>
+      </c>
+      <c r="L54" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="49" t="inlineStr">
+        <is>
+          <t>Cordova Sliding Window</t>
+        </is>
+      </c>
+      <c r="B55" s="50" t="inlineStr">
+        <is>
+          <t>48" x 36"</t>
+        </is>
+      </c>
+      <c r="C55" s="50" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D55" s="50" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E55" s="50" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F55" s="71" t="n"/>
+      <c r="G55" s="71" t="n"/>
+      <c r="H55" s="71" t="n"/>
+      <c r="I55" s="71" t="n"/>
+      <c r="J55" s="71" t="n"/>
+      <c r="K55" s="55" t="inlineStr">
+        <is>
+          <t>26-0604-0045</t>
+        </is>
+      </c>
+      <c r="L55" s="67" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="n"/>
+      <c r="B56" s="41" t="n"/>
+      <c r="C56" s="41" t="n"/>
+      <c r="D56" s="41" t="n"/>
+      <c r="E56" s="41" t="n"/>
+      <c r="F56" s="42" t="n"/>
+      <c r="G56" s="42" t="n"/>
+      <c r="H56" s="42" t="n"/>
+      <c r="I56" s="32" t="n"/>
+      <c r="J56" s="42" t="n"/>
+      <c r="K56" s="32" t="n"/>
+      <c r="L56" s="42" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="n"/>
+      <c r="B57" s="31" t="n"/>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="31" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="32" t="n"/>
+      <c r="H57" s="32" t="n"/>
+      <c r="I57" s="32" t="n"/>
+      <c r="J57" s="32" t="n"/>
+      <c r="K57" s="32" t="n"/>
+      <c r="L57" s="42" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="68" t="inlineStr">
+        <is>
           <t>Granada Bi-fold Door</t>
         </is>
       </c>
-      <c r="B54" s="35" t="inlineStr">
+      <c r="B58" s="69" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C54" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D54" s="35" t="inlineStr">
+      <c r="C58" s="69" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D58" s="69" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E54" s="35" t="inlineStr">
+      <c r="E58" s="69" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F54" s="42" t="n"/>
-      <c r="G54" s="42" t="n"/>
-      <c r="H54" s="42" t="n"/>
-      <c r="I54" s="32" t="n"/>
-      <c r="J54" s="43" t="n"/>
-      <c r="K54" s="42" t="inlineStr">
-        <is>
-          <t>25-0927-0013</t>
-        </is>
-      </c>
-      <c r="L54" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>Granada Bi-fold Door</t>
-        </is>
-      </c>
-      <c r="B55" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C55" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D55" s="35" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E55" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="32" t="n"/>
-      <c r="H55" s="32" t="n"/>
-      <c r="I55" s="32" t="n"/>
-      <c r="J55" s="32" t="n"/>
-      <c r="K55" s="42" t="inlineStr">
-        <is>
-          <t>25-0927-0014</t>
-        </is>
-      </c>
-      <c r="L55" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="34" t="inlineStr">
-        <is>
-          <t>Granada Bi-fold Door</t>
-        </is>
-      </c>
-      <c r="B56" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C56" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D56" s="35" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E56" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F56" s="32" t="n"/>
-      <c r="G56" s="32" t="n"/>
-      <c r="H56" s="32" t="n"/>
-      <c r="I56" s="32" t="n"/>
-      <c r="J56" s="32" t="n"/>
-      <c r="K56" s="42" t="inlineStr">
-        <is>
-          <t>25-0927-0015</t>
-        </is>
-      </c>
-      <c r="L56" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="34" t="inlineStr">
-        <is>
-          <t>Granada Bi-fold Door</t>
-        </is>
-      </c>
-      <c r="B57" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C57" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D57" s="35" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E57" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F57" s="38" t="n"/>
-      <c r="G57" s="38" t="n"/>
-      <c r="H57" s="38" t="n"/>
-      <c r="I57" s="38" t="n"/>
-      <c r="J57" s="38" t="n"/>
-      <c r="K57" s="42" t="inlineStr">
-        <is>
-          <t>25-0927-0016</t>
-        </is>
-      </c>
-      <c r="L57" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="34" t="inlineStr">
-        <is>
-          <t>Granada Bi-fold Door</t>
-        </is>
-      </c>
-      <c r="B58" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C58" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D58" s="35" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E58" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F58" s="42" t="n"/>
-      <c r="G58" s="42" t="n"/>
-      <c r="H58" s="42" t="n"/>
-      <c r="I58" s="32" t="n"/>
-      <c r="J58" s="43" t="n"/>
-      <c r="K58" s="42" t="inlineStr">
-        <is>
-          <t>25-0927-0017</t>
-        </is>
-      </c>
-      <c r="L58" s="33" t="inlineStr">
+      <c r="F58" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="G58" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" s="28" t="n"/>
+      <c r="J58" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="K58" s="27" t="inlineStr">
+        <is>
+          <t>25-0927-0011</t>
+        </is>
+      </c>
+      <c r="L58" s="29" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -3241,14 +3235,14 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F59" s="24" t="n"/>
-      <c r="G59" s="24" t="n"/>
-      <c r="H59" s="24" t="n"/>
-      <c r="I59" s="24" t="n"/>
-      <c r="J59" s="24" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="32" t="n"/>
+      <c r="H59" s="32" t="n"/>
+      <c r="I59" s="32" t="n"/>
+      <c r="J59" s="32" t="n"/>
       <c r="K59" s="42" t="inlineStr">
         <is>
-          <t>25-0927-0018</t>
+          <t>25-0927-0012</t>
         </is>
       </c>
       <c r="L59" s="33" t="inlineStr">
@@ -3258,61 +3252,81 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="34" t="n"/>
-      <c r="B60" s="35" t="n"/>
-      <c r="C60" s="35" t="n"/>
-      <c r="D60" s="35" t="n"/>
-      <c r="E60" s="35" t="n"/>
-      <c r="F60" s="42" t="n"/>
-      <c r="G60" s="42" t="n"/>
-      <c r="H60" s="42" t="n"/>
-      <c r="I60" s="24" t="n"/>
-      <c r="J60" s="42" t="n"/>
-      <c r="K60" s="42" t="n"/>
-      <c r="L60" s="39" t="n"/>
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>Granada Bi-fold Door</t>
+        </is>
+      </c>
+      <c r="B60" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C60" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D60" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E60" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F60" s="32" t="n"/>
+      <c r="G60" s="32" t="n"/>
+      <c r="H60" s="32" t="n"/>
+      <c r="I60" s="32" t="n"/>
+      <c r="J60" s="32" t="n"/>
+      <c r="K60" s="42" t="inlineStr">
+        <is>
+          <t>25-0927-0013</t>
+        </is>
+      </c>
+      <c r="L60" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="72" t="inlineStr">
+      <c r="A61" s="34" t="inlineStr">
         <is>
           <t>Granada Bi-fold Door</t>
         </is>
       </c>
-      <c r="B61" s="73" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C61" s="73" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D61" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E61" s="73" t="inlineStr">
-        <is>
-          <t>Sidelite</t>
-        </is>
-      </c>
-      <c r="F61" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="24" t="n"/>
-      <c r="J61" s="42" t="n">
-        <v>2</v>
-      </c>
+      <c r="B61" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C61" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D61" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E61" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F61" s="32" t="n"/>
+      <c r="G61" s="32" t="n"/>
+      <c r="H61" s="32" t="n"/>
+      <c r="I61" s="32" t="n"/>
+      <c r="J61" s="32" t="n"/>
       <c r="K61" s="42" t="inlineStr">
         <is>
-          <t>25-0927-0019</t>
+          <t>25-0927-0014</t>
         </is>
       </c>
       <c r="L61" s="33" t="inlineStr">
@@ -3329,32 +3343,32 @@
       </c>
       <c r="B62" s="35" t="inlineStr">
         <is>
-          <t>36" x 96"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C62" s="35" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="D62" s="35" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E62" s="35" t="inlineStr">
         <is>
-          <t>Sidelite</t>
-        </is>
-      </c>
-      <c r="F62" s="24" t="n"/>
-      <c r="G62" s="24" t="n"/>
-      <c r="H62" s="24" t="n"/>
-      <c r="I62" s="24" t="n"/>
-      <c r="J62" s="24" t="n"/>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F62" s="38" t="n"/>
+      <c r="G62" s="38" t="n"/>
+      <c r="H62" s="38" t="n"/>
+      <c r="I62" s="38" t="n"/>
+      <c r="J62" s="38" t="n"/>
       <c r="K62" s="42" t="inlineStr">
         <is>
-          <t>25-0927-0020</t>
+          <t>25-0927-0015</t>
         </is>
       </c>
       <c r="L62" s="33" t="inlineStr">
@@ -3364,66 +3378,86 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="34" t="n"/>
-      <c r="B63" s="35" t="n"/>
-      <c r="C63" s="35" t="n"/>
-      <c r="D63" s="35" t="n"/>
-      <c r="E63" s="35" t="n"/>
-      <c r="F63" s="24" t="n"/>
-      <c r="G63" s="24" t="n"/>
-      <c r="H63" s="24" t="n"/>
-      <c r="I63" s="24" t="n"/>
-      <c r="J63" s="24" t="n"/>
-      <c r="K63" s="42" t="n"/>
-      <c r="L63" s="39" t="n"/>
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>Granada Bi-fold Door</t>
+        </is>
+      </c>
+      <c r="B63" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C63" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D63" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E63" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F63" s="42" t="n"/>
+      <c r="G63" s="42" t="n"/>
+      <c r="H63" s="42" t="n"/>
+      <c r="I63" s="32" t="n"/>
+      <c r="J63" s="43" t="n"/>
+      <c r="K63" s="42" t="inlineStr">
+        <is>
+          <t>25-0927-0016</t>
+        </is>
+      </c>
+      <c r="L63" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="72" t="inlineStr">
+      <c r="A64" s="34" t="inlineStr">
         <is>
           <t>Granada Bi-fold Door</t>
         </is>
       </c>
-      <c r="B64" s="73" t="inlineStr">
-        <is>
-          <t>96" x 80"</t>
-        </is>
-      </c>
-      <c r="C64" s="73" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D64" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E64" s="73" t="inlineStr">
+      <c r="B64" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C64" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D64" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E64" s="35" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F64" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" s="24" t="n"/>
-      <c r="J64" s="42" t="n">
-        <v>3</v>
-      </c>
+      <c r="F64" s="32" t="n"/>
+      <c r="G64" s="32" t="n"/>
+      <c r="H64" s="32" t="n"/>
+      <c r="I64" s="32" t="n"/>
+      <c r="J64" s="32" t="n"/>
       <c r="K64" s="42" t="inlineStr">
         <is>
-          <t>26-0611-0049</t>
-        </is>
-      </c>
-      <c r="L64" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>25-0927-0017</t>
+        </is>
+      </c>
+      <c r="L64" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3469,7 @@
       </c>
       <c r="B65" s="35" t="inlineStr">
         <is>
-          <t>96" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C65" s="35" t="inlineStr">
@@ -3445,7 +3479,7 @@
       </c>
       <c r="D65" s="35" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E65" s="35" t="inlineStr">
@@ -3453,176 +3487,204 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F65" s="24" t="n"/>
-      <c r="G65" s="24" t="n"/>
-      <c r="H65" s="24" t="n"/>
-      <c r="I65" s="24" t="n"/>
-      <c r="J65" s="24" t="n"/>
+      <c r="F65" s="32" t="n"/>
+      <c r="G65" s="32" t="n"/>
+      <c r="H65" s="32" t="n"/>
+      <c r="I65" s="32" t="n"/>
+      <c r="J65" s="32" t="n"/>
       <c r="K65" s="42" t="inlineStr">
         <is>
-          <t>26-0611-0050</t>
-        </is>
-      </c>
-      <c r="L65" s="64" t="inlineStr">
+          <t>25-0927-0018</t>
+        </is>
+      </c>
+      <c r="L65" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>Granada Bi-fold Door</t>
+        </is>
+      </c>
+      <c r="B66" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C66" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D66" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E66" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F66" s="38" t="n"/>
+      <c r="G66" s="38" t="n"/>
+      <c r="H66" s="38" t="n"/>
+      <c r="I66" s="38" t="n"/>
+      <c r="J66" s="38" t="n"/>
+      <c r="K66" s="42" t="inlineStr">
+        <is>
+          <t>26-0611-0046</t>
+        </is>
+      </c>
+      <c r="L66" s="64" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="49" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="34" t="inlineStr">
         <is>
           <t>Granada Bi-fold Door</t>
         </is>
       </c>
-      <c r="B66" s="50" t="inlineStr">
-        <is>
-          <t>96" x 80"</t>
-        </is>
-      </c>
-      <c r="C66" s="50" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D66" s="50" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E66" s="50" t="inlineStr">
+      <c r="B67" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C67" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D67" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E67" s="35" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F66" s="51" t="n"/>
-      <c r="G66" s="51" t="n"/>
-      <c r="H66" s="51" t="n"/>
-      <c r="I66" s="51" t="n"/>
-      <c r="J66" s="51" t="n"/>
-      <c r="K66" s="55" t="inlineStr">
-        <is>
-          <t>26-0611-0051</t>
-        </is>
-      </c>
-      <c r="L66" s="65" t="inlineStr">
+      <c r="F67" s="42" t="n"/>
+      <c r="G67" s="42" t="n"/>
+      <c r="H67" s="42" t="n"/>
+      <c r="I67" s="32" t="n"/>
+      <c r="J67" s="43" t="n"/>
+      <c r="K67" s="42" t="inlineStr">
+        <is>
+          <t>26-0611-0047</t>
+        </is>
+      </c>
+      <c r="L67" s="64" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="35" t="n"/>
-      <c r="B67" s="35" t="n"/>
-      <c r="C67" s="35" t="n"/>
-      <c r="D67" s="35" t="n"/>
-      <c r="E67" s="35" t="n"/>
-      <c r="F67" s="24" t="n"/>
-      <c r="G67" s="24" t="n"/>
-      <c r="H67" s="24" t="n"/>
-      <c r="I67" s="24" t="n"/>
-      <c r="J67" s="24" t="n"/>
-      <c r="K67" s="42" t="n"/>
-      <c r="L67" s="42" t="n"/>
-    </row>
     <row r="68">
-      <c r="A68" s="35" t="n"/>
-      <c r="B68" s="35" t="n"/>
-      <c r="C68" s="35" t="n"/>
-      <c r="D68" s="35" t="n"/>
-      <c r="E68" s="35" t="n"/>
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>Granada Bi-fold Door</t>
+        </is>
+      </c>
+      <c r="B68" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C68" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D68" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E68" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
       <c r="F68" s="24" t="n"/>
       <c r="G68" s="24" t="n"/>
       <c r="H68" s="24" t="n"/>
       <c r="I68" s="24" t="n"/>
       <c r="J68" s="24" t="n"/>
-      <c r="K68" s="42" t="n"/>
-      <c r="L68" s="42" t="n"/>
+      <c r="K68" s="42" t="inlineStr">
+        <is>
+          <t>26-0611-0048</t>
+        </is>
+      </c>
+      <c r="L68" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="70" t="inlineStr">
-        <is>
-          <t>Malaga Single Door</t>
-        </is>
-      </c>
-      <c r="B69" s="71" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C69" s="71" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D69" s="71" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E69" s="71" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G69" s="27" t="n">
+      <c r="A69" s="65" t="n"/>
+      <c r="B69" s="66" t="n"/>
+      <c r="C69" s="66" t="n"/>
+      <c r="D69" s="66" t="n"/>
+      <c r="E69" s="66" t="n"/>
+      <c r="F69" s="42" t="n"/>
+      <c r="G69" s="42" t="n"/>
+      <c r="H69" s="42" t="n"/>
+      <c r="I69" s="24" t="n"/>
+      <c r="J69" s="42" t="n"/>
+      <c r="K69" s="42" t="n"/>
+      <c r="L69" s="39" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="65" t="inlineStr">
+        <is>
+          <t>Granada Bi-fold Door</t>
+        </is>
+      </c>
+      <c r="B70" s="66" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C70" s="66" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D70" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E70" s="66" t="inlineStr">
+        <is>
+          <t>Sidelite</t>
+        </is>
+      </c>
+      <c r="F70" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="27" t="n">
+      <c r="H70" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="69" t="n"/>
-      <c r="J69" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K69" s="27" t="inlineStr">
-        <is>
-          <t>25-1205-0021</t>
-        </is>
-      </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="34" t="inlineStr">
-        <is>
-          <t>Malaga Single Door</t>
-        </is>
-      </c>
-      <c r="B70" s="35" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C70" s="35" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D70" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E70" s="35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F70" s="24" t="n"/>
-      <c r="G70" s="24" t="n"/>
-      <c r="H70" s="24" t="n"/>
       <c r="I70" s="24" t="n"/>
-      <c r="J70" s="24" t="n"/>
+      <c r="J70" s="42" t="n">
+        <v>2</v>
+      </c>
       <c r="K70" s="42" t="inlineStr">
         <is>
-          <t>25-1205-0022</t>
+          <t>25-0927-0019</t>
         </is>
       </c>
       <c r="L70" s="33" t="inlineStr">
@@ -3634,17 +3696,17 @@
     <row r="71">
       <c r="A71" s="34" t="inlineStr">
         <is>
-          <t>Malaga Single Door</t>
+          <t>Granada Bi-fold Door</t>
         </is>
       </c>
       <c r="B71" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 96"</t>
         </is>
       </c>
       <c r="C71" s="35" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="D71" s="35" t="inlineStr">
@@ -3654,7 +3716,7 @@
       </c>
       <c r="E71" s="35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sidelite</t>
         </is>
       </c>
       <c r="F71" s="24" t="n"/>
@@ -3664,7 +3726,7 @@
       <c r="J71" s="24" t="n"/>
       <c r="K71" s="42" t="inlineStr">
         <is>
-          <t>25-1205-0023</t>
+          <t>25-0927-0020</t>
         </is>
       </c>
       <c r="L71" s="33" t="inlineStr">
@@ -3674,276 +3736,228 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="34" t="inlineStr">
+      <c r="A72" s="34" t="n"/>
+      <c r="B72" s="35" t="n"/>
+      <c r="C72" s="35" t="n"/>
+      <c r="D72" s="35" t="n"/>
+      <c r="E72" s="35" t="n"/>
+      <c r="F72" s="24" t="n"/>
+      <c r="G72" s="24" t="n"/>
+      <c r="H72" s="24" t="n"/>
+      <c r="I72" s="24" t="n"/>
+      <c r="J72" s="24" t="n"/>
+      <c r="K72" s="42" t="n"/>
+      <c r="L72" s="39" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="65" t="inlineStr">
+        <is>
+          <t>Granada Bi-fold Door</t>
+        </is>
+      </c>
+      <c r="B73" s="66" t="inlineStr">
+        <is>
+          <t>96" x 80"</t>
+        </is>
+      </c>
+      <c r="C73" s="66" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D73" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E73" s="66" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F73" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" s="24" t="n"/>
+      <c r="J73" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" s="42" t="inlineStr">
+        <is>
+          <t>26-0611-0049</t>
+        </is>
+      </c>
+      <c r="L73" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>Granada Bi-fold Door</t>
+        </is>
+      </c>
+      <c r="B74" s="35" t="inlineStr">
+        <is>
+          <t>96" x 80"</t>
+        </is>
+      </c>
+      <c r="C74" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D74" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E74" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="n"/>
+      <c r="G74" s="24" t="n"/>
+      <c r="H74" s="24" t="n"/>
+      <c r="I74" s="24" t="n"/>
+      <c r="J74" s="24" t="n"/>
+      <c r="K74" s="42" t="inlineStr">
+        <is>
+          <t>26-0611-0050</t>
+        </is>
+      </c>
+      <c r="L74" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="49" t="inlineStr">
+        <is>
+          <t>Granada Bi-fold Door</t>
+        </is>
+      </c>
+      <c r="B75" s="50" t="inlineStr">
+        <is>
+          <t>96" x 80"</t>
+        </is>
+      </c>
+      <c r="C75" s="50" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D75" s="50" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E75" s="50" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F75" s="51" t="n"/>
+      <c r="G75" s="51" t="n"/>
+      <c r="H75" s="51" t="n"/>
+      <c r="I75" s="51" t="n"/>
+      <c r="J75" s="51" t="n"/>
+      <c r="K75" s="55" t="inlineStr">
+        <is>
+          <t>26-0611-0051</t>
+        </is>
+      </c>
+      <c r="L75" s="67" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="35" t="n"/>
+      <c r="B76" s="35" t="n"/>
+      <c r="C76" s="35" t="n"/>
+      <c r="D76" s="35" t="n"/>
+      <c r="E76" s="35" t="n"/>
+      <c r="F76" s="24" t="n"/>
+      <c r="G76" s="24" t="n"/>
+      <c r="H76" s="24" t="n"/>
+      <c r="I76" s="24" t="n"/>
+      <c r="J76" s="24" t="n"/>
+      <c r="K76" s="42" t="n"/>
+      <c r="L76" s="42" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="35" t="n"/>
+      <c r="B77" s="35" t="n"/>
+      <c r="C77" s="35" t="n"/>
+      <c r="D77" s="35" t="n"/>
+      <c r="E77" s="35" t="n"/>
+      <c r="F77" s="24" t="n"/>
+      <c r="G77" s="24" t="n"/>
+      <c r="H77" s="24" t="n"/>
+      <c r="I77" s="24" t="n"/>
+      <c r="J77" s="24" t="n"/>
+      <c r="K77" s="42" t="n"/>
+      <c r="L77" s="42" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="68" t="inlineStr">
         <is>
           <t>Malaga Single Door</t>
         </is>
       </c>
-      <c r="B72" s="35" t="inlineStr">
+      <c r="B78" s="69" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C72" s="35" t="inlineStr">
+      <c r="C78" s="69" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D72" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E72" s="35" t="inlineStr">
+      <c r="D78" s="69" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E78" s="69" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F72" s="38" t="n"/>
-      <c r="G72" s="38" t="n"/>
-      <c r="H72" s="38" t="n"/>
-      <c r="I72" s="38" t="n"/>
-      <c r="J72" s="38" t="n"/>
-      <c r="K72" s="42" t="inlineStr">
-        <is>
-          <t>25-1205-0024</t>
-        </is>
-      </c>
-      <c r="L72" s="33" t="inlineStr">
+      <c r="F78" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G78" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" s="70" t="n"/>
+      <c r="J78" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="K78" s="27" t="inlineStr">
+        <is>
+          <t>25-1205-0021</t>
+        </is>
+      </c>
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="37" t="n"/>
-      <c r="B73" s="38" t="n"/>
-      <c r="C73" s="38" t="n"/>
-      <c r="D73" s="38" t="n"/>
-      <c r="E73" s="38" t="n"/>
-      <c r="F73" s="38" t="n"/>
-      <c r="G73" s="38" t="n"/>
-      <c r="H73" s="38" t="n"/>
-      <c r="I73" s="38" t="n"/>
-      <c r="J73" s="38" t="n"/>
-      <c r="K73" s="38" t="n"/>
-      <c r="L73" s="39" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="72" t="inlineStr">
-        <is>
-          <t>Malaga Single Door</t>
-        </is>
-      </c>
-      <c r="B74" s="73" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C74" s="73" t="inlineStr">
-        <is>
-          <t>Gunmetal</t>
-        </is>
-      </c>
-      <c r="D74" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E74" s="73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F74" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="42" t="n">
-        <v>15</v>
-      </c>
-      <c r="I74" s="32" t="n"/>
-      <c r="J74" s="42" t="n">
-        <v>15</v>
-      </c>
-      <c r="K74" s="42" t="inlineStr">
-        <is>
-          <t>26-0618-0056</t>
-        </is>
-      </c>
-      <c r="L74" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="34" t="inlineStr">
-        <is>
-          <t>Malaga Single Door</t>
-        </is>
-      </c>
-      <c r="B75" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C75" s="35" t="inlineStr">
-        <is>
-          <t>Gunmetal</t>
-        </is>
-      </c>
-      <c r="D75" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E75" s="35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="n"/>
-      <c r="G75" s="32" t="n"/>
-      <c r="H75" s="32" t="n"/>
-      <c r="I75" s="32" t="n"/>
-      <c r="J75" s="32" t="n"/>
-      <c r="K75" s="42" t="inlineStr">
-        <is>
-          <t>26-0618-0057</t>
-        </is>
-      </c>
-      <c r="L75" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="34" t="inlineStr">
-        <is>
-          <t>Malaga Single Door</t>
-        </is>
-      </c>
-      <c r="B76" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C76" s="35" t="inlineStr">
-        <is>
-          <t>Gunmetal</t>
-        </is>
-      </c>
-      <c r="D76" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E76" s="35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="n"/>
-      <c r="G76" s="32" t="n"/>
-      <c r="H76" s="32" t="n"/>
-      <c r="I76" s="32" t="n"/>
-      <c r="J76" s="32" t="n"/>
-      <c r="K76" s="42" t="inlineStr">
-        <is>
-          <t>26-0618-0058</t>
-        </is>
-      </c>
-      <c r="L76" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="34" t="inlineStr">
-        <is>
-          <t>Malaga Single Door</t>
-        </is>
-      </c>
-      <c r="B77" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C77" s="35" t="inlineStr">
-        <is>
-          <t>Gunmetal</t>
-        </is>
-      </c>
-      <c r="D77" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E77" s="35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="n"/>
-      <c r="G77" s="32" t="n"/>
-      <c r="H77" s="32" t="n"/>
-      <c r="I77" s="32" t="n"/>
-      <c r="J77" s="32" t="n"/>
-      <c r="K77" s="42" t="inlineStr">
-        <is>
-          <t>26-0618-0059</t>
-        </is>
-      </c>
-      <c r="L77" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="34" t="inlineStr">
-        <is>
-          <t>Malaga Single Door</t>
-        </is>
-      </c>
-      <c r="B78" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C78" s="35" t="inlineStr">
-        <is>
-          <t>Gunmetal</t>
-        </is>
-      </c>
-      <c r="D78" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E78" s="35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="n"/>
-      <c r="G78" s="32" t="n"/>
-      <c r="H78" s="32" t="n"/>
-      <c r="I78" s="32" t="n"/>
-      <c r="J78" s="32" t="n"/>
-      <c r="K78" s="42" t="inlineStr">
-        <is>
-          <t>26-0618-0060</t>
-        </is>
-      </c>
-      <c r="L78" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
@@ -3955,12 +3969,12 @@
       </c>
       <c r="B79" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C79" s="35" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D79" s="35" t="inlineStr">
@@ -3973,19 +3987,19 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F79" s="32" t="n"/>
-      <c r="G79" s="32" t="n"/>
-      <c r="H79" s="32" t="n"/>
-      <c r="I79" s="32" t="n"/>
-      <c r="J79" s="32" t="n"/>
+      <c r="F79" s="24" t="n"/>
+      <c r="G79" s="24" t="n"/>
+      <c r="H79" s="24" t="n"/>
+      <c r="I79" s="24" t="n"/>
+      <c r="J79" s="24" t="n"/>
       <c r="K79" s="42" t="inlineStr">
         <is>
-          <t>26-0618-0061</t>
-        </is>
-      </c>
-      <c r="L79" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>25-1205-0022</t>
+        </is>
+      </c>
+      <c r="L79" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -3997,12 +4011,12 @@
       </c>
       <c r="B80" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C80" s="35" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D80" s="35" t="inlineStr">
@@ -4015,19 +4029,19 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F80" s="32" t="n"/>
-      <c r="G80" s="32" t="n"/>
-      <c r="H80" s="32" t="n"/>
-      <c r="I80" s="32" t="n"/>
-      <c r="J80" s="32" t="n"/>
+      <c r="F80" s="24" t="n"/>
+      <c r="G80" s="24" t="n"/>
+      <c r="H80" s="24" t="n"/>
+      <c r="I80" s="24" t="n"/>
+      <c r="J80" s="24" t="n"/>
       <c r="K80" s="42" t="inlineStr">
         <is>
-          <t>26-0618-0062</t>
-        </is>
-      </c>
-      <c r="L80" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>25-1205-0023</t>
+        </is>
+      </c>
+      <c r="L80" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4053,12 @@
       </c>
       <c r="B81" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C81" s="35" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D81" s="35" t="inlineStr">
@@ -4057,19 +4071,19 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F81" s="32" t="n"/>
-      <c r="G81" s="32" t="n"/>
-      <c r="H81" s="32" t="n"/>
-      <c r="I81" s="32" t="n"/>
-      <c r="J81" s="32" t="n"/>
+      <c r="F81" s="24" t="n"/>
+      <c r="G81" s="24" t="n"/>
+      <c r="H81" s="24" t="n"/>
+      <c r="I81" s="24" t="n"/>
+      <c r="J81" s="24" t="n"/>
       <c r="K81" s="42" t="inlineStr">
         <is>
-          <t>26-0618-0063</t>
-        </is>
-      </c>
-      <c r="L81" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>25-1205-0024</t>
+        </is>
+      </c>
+      <c r="L81" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -4081,12 +4095,12 @@
       </c>
       <c r="B82" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C82" s="35" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D82" s="35" t="inlineStr">
@@ -4099,14 +4113,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F82" s="38" t="n"/>
-      <c r="G82" s="38" t="n"/>
-      <c r="H82" s="38" t="n"/>
-      <c r="I82" s="38" t="n"/>
-      <c r="J82" s="38" t="n"/>
+      <c r="F82" s="24" t="n"/>
+      <c r="G82" s="24" t="n"/>
+      <c r="H82" s="24" t="n"/>
+      <c r="I82" s="24" t="n"/>
+      <c r="J82" s="24" t="n"/>
       <c r="K82" s="42" t="inlineStr">
         <is>
-          <t>26-0618-0064</t>
+          <t>26-0618-0052</t>
         </is>
       </c>
       <c r="L82" s="64" t="inlineStr">
@@ -4123,12 +4137,12 @@
       </c>
       <c r="B83" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C83" s="35" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D83" s="35" t="inlineStr">
@@ -4141,14 +4155,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F83" s="42" t="n"/>
-      <c r="G83" s="42" t="n"/>
-      <c r="H83" s="42" t="n"/>
-      <c r="I83" s="32" t="n"/>
-      <c r="J83" s="43" t="n"/>
+      <c r="F83" s="24" t="n"/>
+      <c r="G83" s="24" t="n"/>
+      <c r="H83" s="24" t="n"/>
+      <c r="I83" s="24" t="n"/>
+      <c r="J83" s="24" t="n"/>
       <c r="K83" s="42" t="inlineStr">
         <is>
-          <t>26-0618-0065</t>
+          <t>26-0618-0053</t>
         </is>
       </c>
       <c r="L83" s="64" t="inlineStr">
@@ -4165,12 +4179,12 @@
       </c>
       <c r="B84" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C84" s="35" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D84" s="35" t="inlineStr">
@@ -4183,14 +4197,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F84" s="32" t="n"/>
-      <c r="G84" s="32" t="n"/>
-      <c r="H84" s="32" t="n"/>
-      <c r="I84" s="32" t="n"/>
-      <c r="J84" s="32" t="n"/>
+      <c r="F84" s="24" t="n"/>
+      <c r="G84" s="24" t="n"/>
+      <c r="H84" s="24" t="n"/>
+      <c r="I84" s="24" t="n"/>
+      <c r="J84" s="24" t="n"/>
       <c r="K84" s="42" t="inlineStr">
         <is>
-          <t>26-0618-0066</t>
+          <t>26-0618-0054</t>
         </is>
       </c>
       <c r="L84" s="64" t="inlineStr">
@@ -4207,12 +4221,12 @@
       </c>
       <c r="B85" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C85" s="35" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D85" s="35" t="inlineStr">
@@ -4232,7 +4246,7 @@
       <c r="J85" s="24" t="n"/>
       <c r="K85" s="42" t="inlineStr">
         <is>
-          <t>26-0618-0067</t>
+          <t>26-0618-0055</t>
         </is>
       </c>
       <c r="L85" s="64" t="inlineStr">
@@ -4242,233 +4256,261 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="34" t="inlineStr">
+      <c r="A86" s="34" t="n"/>
+      <c r="B86" s="35" t="n"/>
+      <c r="C86" s="35" t="n"/>
+      <c r="D86" s="35" t="n"/>
+      <c r="E86" s="35" t="n"/>
+      <c r="F86" s="24" t="n"/>
+      <c r="G86" s="24" t="n"/>
+      <c r="H86" s="24" t="n"/>
+      <c r="I86" s="24" t="n"/>
+      <c r="J86" s="24" t="n"/>
+      <c r="K86" s="42" t="n"/>
+      <c r="L86" s="39" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="65" t="inlineStr">
         <is>
           <t>Malaga Single Door</t>
         </is>
       </c>
-      <c r="B86" s="35" t="inlineStr">
+      <c r="B87" s="66" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C86" s="35" t="inlineStr">
+      <c r="C87" s="66" t="inlineStr">
         <is>
           <t>Gunmetal</t>
         </is>
       </c>
-      <c r="D86" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E86" s="35" t="inlineStr">
+      <c r="D87" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E87" s="66" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F86" s="42" t="n"/>
-      <c r="G86" s="42" t="n"/>
-      <c r="H86" s="42" t="n"/>
-      <c r="I86" s="24" t="n"/>
-      <c r="J86" s="42" t="n"/>
-      <c r="K86" s="42" t="inlineStr">
-        <is>
-          <t>26-0618-0068</t>
-        </is>
-      </c>
-      <c r="L86" s="64" t="inlineStr">
+      <c r="F87" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="I87" s="24" t="n"/>
+      <c r="J87" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="K87" s="42" t="inlineStr">
+        <is>
+          <t>26-0618-0056</t>
+        </is>
+      </c>
+      <c r="L87" s="64" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="34" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="34" t="inlineStr">
         <is>
           <t>Malaga Single Door</t>
         </is>
       </c>
-      <c r="B87" s="35" t="inlineStr">
+      <c r="B88" s="35" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C87" s="35" t="inlineStr">
+      <c r="C88" s="35" t="inlineStr">
         <is>
           <t>Gunmetal</t>
         </is>
       </c>
-      <c r="D87" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E87" s="35" t="inlineStr">
+      <c r="D88" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E88" s="35" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F87" s="24" t="n"/>
-      <c r="G87" s="24" t="n"/>
-      <c r="H87" s="24" t="n"/>
-      <c r="I87" s="24" t="n"/>
-      <c r="J87" s="24" t="n"/>
-      <c r="K87" s="42" t="inlineStr">
-        <is>
-          <t>26-0618-0069</t>
-        </is>
-      </c>
-      <c r="L87" s="64" t="inlineStr">
+      <c r="F88" s="38" t="n"/>
+      <c r="G88" s="38" t="n"/>
+      <c r="H88" s="38" t="n"/>
+      <c r="I88" s="38" t="n"/>
+      <c r="J88" s="38" t="n"/>
+      <c r="K88" s="42" t="inlineStr">
+        <is>
+          <t>26-0618-0057</t>
+        </is>
+      </c>
+      <c r="L88" s="64" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="49" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="34" t="inlineStr">
         <is>
           <t>Malaga Single Door</t>
         </is>
       </c>
-      <c r="B88" s="50" t="inlineStr">
+      <c r="B89" s="35" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C88" s="50" t="inlineStr">
+      <c r="C89" s="35" t="inlineStr">
         <is>
           <t>Gunmetal</t>
         </is>
       </c>
-      <c r="D88" s="50" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E88" s="50" t="inlineStr">
+      <c r="D89" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E89" s="35" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F88" s="51" t="n"/>
-      <c r="G88" s="51" t="n"/>
-      <c r="H88" s="51" t="n"/>
-      <c r="I88" s="51" t="n"/>
-      <c r="J88" s="51" t="n"/>
-      <c r="K88" s="55" t="inlineStr">
-        <is>
-          <t>26-0618-0070</t>
-        </is>
-      </c>
-      <c r="L88" s="65" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="38" t="n"/>
-      <c r="B89" s="38" t="n"/>
-      <c r="C89" s="38" t="n"/>
-      <c r="D89" s="38" t="n"/>
-      <c r="E89" s="38" t="n"/>
       <c r="F89" s="38" t="n"/>
       <c r="G89" s="38" t="n"/>
       <c r="H89" s="38" t="n"/>
       <c r="I89" s="38" t="n"/>
       <c r="J89" s="38" t="n"/>
-      <c r="K89" s="38" t="n"/>
-      <c r="L89" s="42" t="n"/>
+      <c r="K89" s="42" t="inlineStr">
+        <is>
+          <t>26-0618-0058</t>
+        </is>
+      </c>
+      <c r="L89" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="38" t="n"/>
-      <c r="B90" s="38" t="n"/>
-      <c r="C90" s="38" t="n"/>
-      <c r="D90" s="38" t="n"/>
-      <c r="E90" s="38" t="n"/>
-      <c r="F90" s="38" t="n"/>
-      <c r="G90" s="38" t="n"/>
-      <c r="H90" s="38" t="n"/>
-      <c r="I90" s="38" t="n"/>
-      <c r="J90" s="38" t="n"/>
-      <c r="K90" s="38" t="n"/>
-      <c r="L90" s="42" t="n"/>
+      <c r="A90" s="34" t="inlineStr">
+        <is>
+          <t>Malaga Single Door</t>
+        </is>
+      </c>
+      <c r="B90" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C90" s="35" t="inlineStr">
+        <is>
+          <t>Gunmetal</t>
+        </is>
+      </c>
+      <c r="D90" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E90" s="35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F90" s="42" t="n"/>
+      <c r="G90" s="42" t="n"/>
+      <c r="H90" s="42" t="n"/>
+      <c r="I90" s="32" t="n"/>
+      <c r="J90" s="42" t="n"/>
+      <c r="K90" s="42" t="inlineStr">
+        <is>
+          <t>26-0618-0059</t>
+        </is>
+      </c>
+      <c r="L90" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="70" t="inlineStr">
-        <is>
-          <t>Sevilla French Door</t>
-        </is>
-      </c>
-      <c r="B91" s="71" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C91" s="71" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D91" s="71" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E91" s="71" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F91" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="G91" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="28" t="n"/>
-      <c r="J91" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="K91" s="27" t="inlineStr">
-        <is>
-          <t>24-1102-0014</t>
-        </is>
-      </c>
-      <c r="L91" s="29" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+      <c r="A91" s="34" t="inlineStr">
+        <is>
+          <t>Malaga Single Door</t>
+        </is>
+      </c>
+      <c r="B91" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C91" s="35" t="inlineStr">
+        <is>
+          <t>Gunmetal</t>
+        </is>
+      </c>
+      <c r="D91" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E91" s="35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F91" s="32" t="n"/>
+      <c r="G91" s="32" t="n"/>
+      <c r="H91" s="32" t="n"/>
+      <c r="I91" s="32" t="n"/>
+      <c r="J91" s="32" t="n"/>
+      <c r="K91" s="42" t="inlineStr">
+        <is>
+          <t>26-0618-0060</t>
+        </is>
+      </c>
+      <c r="L91" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="34" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="B92" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="D92" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E92" s="35" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F92" s="32" t="n"/>
@@ -4478,39 +4520,39 @@
       <c r="J92" s="32" t="n"/>
       <c r="K92" s="42" t="inlineStr">
         <is>
-          <t>24-1102-0015</t>
-        </is>
-      </c>
-      <c r="L92" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0061</t>
+        </is>
+      </c>
+      <c r="L92" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="34" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="B93" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C93" s="35" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="D93" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E93" s="35" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F93" s="32" t="n"/>
@@ -4520,39 +4562,39 @@
       <c r="J93" s="32" t="n"/>
       <c r="K93" s="42" t="inlineStr">
         <is>
-          <t>24-1102-0016</t>
-        </is>
-      </c>
-      <c r="L93" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0062</t>
+        </is>
+      </c>
+      <c r="L93" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="34" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="B94" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C94" s="35" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="D94" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E94" s="35" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F94" s="32" t="n"/>
@@ -4562,125 +4604,145 @@
       <c r="J94" s="32" t="n"/>
       <c r="K94" s="42" t="inlineStr">
         <is>
-          <t>24-1102-0017</t>
-        </is>
-      </c>
-      <c r="L94" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0063</t>
+        </is>
+      </c>
+      <c r="L94" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="34" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="B95" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C95" s="35" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="D95" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E95" s="35" t="inlineStr">
         <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F95" s="24" t="n"/>
-      <c r="G95" s="24" t="n"/>
-      <c r="H95" s="24" t="n"/>
-      <c r="I95" s="24" t="n"/>
-      <c r="J95" s="24" t="n"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F95" s="32" t="n"/>
+      <c r="G95" s="32" t="n"/>
+      <c r="H95" s="32" t="n"/>
+      <c r="I95" s="32" t="n"/>
+      <c r="J95" s="32" t="n"/>
       <c r="K95" s="42" t="inlineStr">
         <is>
-          <t>24-1102-0018</t>
-        </is>
-      </c>
-      <c r="L95" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0064</t>
+        </is>
+      </c>
+      <c r="L95" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="34" t="n"/>
-      <c r="B96" s="35" t="n"/>
-      <c r="C96" s="35" t="n"/>
-      <c r="D96" s="35" t="n"/>
-      <c r="E96" s="35" t="n"/>
-      <c r="F96" s="42" t="n"/>
-      <c r="G96" s="42" t="n"/>
-      <c r="H96" s="42" t="n"/>
-      <c r="I96" s="24" t="n"/>
-      <c r="J96" s="42" t="n"/>
-      <c r="K96" s="42" t="n"/>
-      <c r="L96" s="39" t="n"/>
+      <c r="A96" s="34" t="inlineStr">
+        <is>
+          <t>Malaga Single Door</t>
+        </is>
+      </c>
+      <c r="B96" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C96" s="35" t="inlineStr">
+        <is>
+          <t>Gunmetal</t>
+        </is>
+      </c>
+      <c r="D96" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E96" s="35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F96" s="32" t="n"/>
+      <c r="G96" s="32" t="n"/>
+      <c r="H96" s="32" t="n"/>
+      <c r="I96" s="32" t="n"/>
+      <c r="J96" s="32" t="n"/>
+      <c r="K96" s="42" t="inlineStr">
+        <is>
+          <t>26-0618-0065</t>
+        </is>
+      </c>
+      <c r="L96" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="72" t="inlineStr">
-        <is>
-          <t>Sevilla French Door</t>
-        </is>
-      </c>
-      <c r="B97" s="73" t="inlineStr">
+      <c r="A97" s="34" t="inlineStr">
+        <is>
+          <t>Malaga Single Door</t>
+        </is>
+      </c>
+      <c r="B97" s="35" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C97" s="73" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D97" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E97" s="73" t="inlineStr">
+      <c r="C97" s="35" t="inlineStr">
+        <is>
+          <t>Gunmetal</t>
+        </is>
+      </c>
+      <c r="D97" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E97" s="35" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F97" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G97" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="H97" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="I97" s="24" t="n"/>
-      <c r="J97" s="42" t="n">
-        <v>7</v>
-      </c>
+      <c r="F97" s="32" t="n"/>
+      <c r="G97" s="32" t="n"/>
+      <c r="H97" s="32" t="n"/>
+      <c r="I97" s="32" t="n"/>
+      <c r="J97" s="32" t="n"/>
       <c r="K97" s="42" t="inlineStr">
         <is>
-          <t>24-1102-0019</t>
-        </is>
-      </c>
-      <c r="L97" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0066</t>
+        </is>
+      </c>
+      <c r="L97" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="34" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="B98" s="35" t="inlineStr">
@@ -4690,7 +4752,7 @@
       </c>
       <c r="C98" s="35" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="D98" s="35" t="inlineStr">
@@ -4703,26 +4765,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F98" s="24" t="n"/>
-      <c r="G98" s="24" t="n"/>
-      <c r="H98" s="24" t="n"/>
-      <c r="I98" s="24" t="n"/>
-      <c r="J98" s="24" t="n"/>
+      <c r="F98" s="38" t="n"/>
+      <c r="G98" s="38" t="n"/>
+      <c r="H98" s="38" t="n"/>
+      <c r="I98" s="38" t="n"/>
+      <c r="J98" s="38" t="n"/>
       <c r="K98" s="42" t="inlineStr">
         <is>
-          <t>24-1102-0020</t>
-        </is>
-      </c>
-      <c r="L98" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0067</t>
+        </is>
+      </c>
+      <c r="L98" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="34" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="B99" s="35" t="inlineStr">
@@ -4732,7 +4794,7 @@
       </c>
       <c r="C99" s="35" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="D99" s="35" t="inlineStr">
@@ -4745,26 +4807,26 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F99" s="24" t="n"/>
-      <c r="G99" s="24" t="n"/>
-      <c r="H99" s="24" t="n"/>
-      <c r="I99" s="24" t="n"/>
-      <c r="J99" s="24" t="n"/>
+      <c r="F99" s="42" t="n"/>
+      <c r="G99" s="42" t="n"/>
+      <c r="H99" s="42" t="n"/>
+      <c r="I99" s="32" t="n"/>
+      <c r="J99" s="43" t="n"/>
       <c r="K99" s="42" t="inlineStr">
         <is>
-          <t>24-1102-0021</t>
-        </is>
-      </c>
-      <c r="L99" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0068</t>
+        </is>
+      </c>
+      <c r="L99" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="34" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="B100" s="35" t="inlineStr">
@@ -4774,7 +4836,7 @@
       </c>
       <c r="C100" s="35" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="D100" s="35" t="inlineStr">
@@ -4787,14 +4849,14 @@
           <t>None</t>
         </is>
       </c>
-      <c r="F100" s="24" t="n"/>
-      <c r="G100" s="24" t="n"/>
-      <c r="H100" s="24" t="n"/>
-      <c r="I100" s="24" t="n"/>
-      <c r="J100" s="24" t="n"/>
+      <c r="F100" s="32" t="n"/>
+      <c r="G100" s="32" t="n"/>
+      <c r="H100" s="32" t="n"/>
+      <c r="I100" s="32" t="n"/>
+      <c r="J100" s="32" t="n"/>
       <c r="K100" s="42" t="inlineStr">
         <is>
-          <t>26-0521-0021</t>
+          <t>26-0618-0069</t>
         </is>
       </c>
       <c r="L100" s="64" t="inlineStr">
@@ -4804,184 +4866,164 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="34" t="inlineStr">
-        <is>
-          <t>Sevilla French Door</t>
-        </is>
-      </c>
-      <c r="B101" s="35" t="inlineStr">
+      <c r="A101" s="49" t="inlineStr">
+        <is>
+          <t>Malaga Single Door</t>
+        </is>
+      </c>
+      <c r="B101" s="50" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C101" s="35" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D101" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E101" s="35" t="inlineStr">
+      <c r="C101" s="50" t="inlineStr">
+        <is>
+          <t>Gunmetal</t>
+        </is>
+      </c>
+      <c r="D101" s="50" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E101" s="50" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F101" s="24" t="n"/>
-      <c r="G101" s="24" t="n"/>
-      <c r="H101" s="24" t="n"/>
-      <c r="I101" s="24" t="n"/>
-      <c r="J101" s="24" t="n"/>
-      <c r="K101" s="42" t="inlineStr">
-        <is>
-          <t>26-0521-0022</t>
-        </is>
-      </c>
-      <c r="L101" s="64" t="inlineStr">
+      <c r="F101" s="51" t="n"/>
+      <c r="G101" s="51" t="n"/>
+      <c r="H101" s="51" t="n"/>
+      <c r="I101" s="51" t="n"/>
+      <c r="J101" s="51" t="n"/>
+      <c r="K101" s="55" t="inlineStr">
+        <is>
+          <t>26-0618-0070</t>
+        </is>
+      </c>
+      <c r="L101" s="67" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="34" t="inlineStr">
-        <is>
-          <t>Sevilla French Door</t>
-        </is>
-      </c>
-      <c r="B102" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C102" s="35" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D102" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E102" s="35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F102" s="24" t="n"/>
-      <c r="G102" s="24" t="n"/>
-      <c r="H102" s="24" t="n"/>
+      <c r="A102" s="66" t="n"/>
+      <c r="B102" s="66" t="n"/>
+      <c r="C102" s="66" t="n"/>
+      <c r="D102" s="66" t="n"/>
+      <c r="E102" s="66" t="n"/>
+      <c r="F102" s="42" t="n"/>
+      <c r="G102" s="42" t="n"/>
+      <c r="H102" s="42" t="n"/>
       <c r="I102" s="24" t="n"/>
-      <c r="J102" s="24" t="n"/>
+      <c r="J102" s="42" t="n"/>
       <c r="K102" s="42" t="n"/>
-      <c r="L102" s="36" t="inlineStr">
-        <is>
-          <t>In Production</t>
-        </is>
-      </c>
+      <c r="L102" s="42" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="34" t="inlineStr">
-        <is>
-          <t>Sevilla French Door</t>
-        </is>
-      </c>
-      <c r="B103" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C103" s="35" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D103" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E103" s="35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="A103" s="35" t="n"/>
+      <c r="B103" s="35" t="n"/>
+      <c r="C103" s="35" t="n"/>
+      <c r="D103" s="35" t="n"/>
+      <c r="E103" s="35" t="n"/>
       <c r="F103" s="24" t="n"/>
       <c r="G103" s="24" t="n"/>
       <c r="H103" s="24" t="n"/>
       <c r="I103" s="24" t="n"/>
       <c r="J103" s="24" t="n"/>
       <c r="K103" s="42" t="n"/>
-      <c r="L103" s="36" t="inlineStr">
-        <is>
-          <t>In Production</t>
-        </is>
-      </c>
+      <c r="L103" s="42" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="34" t="n"/>
-      <c r="B104" s="35" t="n"/>
-      <c r="C104" s="35" t="n"/>
-      <c r="D104" s="35" t="n"/>
-      <c r="E104" s="35" t="n"/>
-      <c r="F104" s="24" t="n"/>
-      <c r="G104" s="24" t="n"/>
-      <c r="H104" s="24" t="n"/>
-      <c r="I104" s="24" t="n"/>
-      <c r="J104" s="24" t="n"/>
-      <c r="K104" s="42" t="n"/>
-      <c r="L104" s="39" t="n"/>
+      <c r="A104" s="68" t="inlineStr">
+        <is>
+          <t>Sevilla French Door</t>
+        </is>
+      </c>
+      <c r="B104" s="69" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C104" s="69" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D104" s="69" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E104" s="69" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F104" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="70" t="n"/>
+      <c r="J104" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" s="27" t="inlineStr">
+        <is>
+          <t>24-1102-0014</t>
+        </is>
+      </c>
+      <c r="L104" s="29" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="72" t="inlineStr">
+      <c r="A105" s="34" t="inlineStr">
         <is>
           <t>Sevilla French Door</t>
         </is>
       </c>
-      <c r="B105" s="73" t="inlineStr">
-        <is>
-          <t>72" x 80"</t>
-        </is>
-      </c>
-      <c r="C105" s="73" t="inlineStr">
-        <is>
-          <t>Matte White</t>
-        </is>
-      </c>
-      <c r="D105" s="73" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E105" s="73" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F105" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="42" t="n">
-        <v>5</v>
-      </c>
+      <c r="B105" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C105" s="35" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D105" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E105" s="35" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F105" s="24" t="n"/>
+      <c r="G105" s="24" t="n"/>
+      <c r="H105" s="24" t="n"/>
       <c r="I105" s="24" t="n"/>
-      <c r="J105" s="42" t="n">
-        <v>5</v>
-      </c>
+      <c r="J105" s="24" t="n"/>
       <c r="K105" s="42" t="inlineStr">
         <is>
-          <t>26-0521-0023</t>
-        </is>
-      </c>
-      <c r="L105" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>24-1102-0015</t>
+        </is>
+      </c>
+      <c r="L105" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -4993,22 +5035,22 @@
       </c>
       <c r="B106" s="35" t="inlineStr">
         <is>
-          <t>72" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C106" s="35" t="inlineStr">
         <is>
-          <t>Matte White</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D106" s="35" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E106" s="35" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="F106" s="24" t="n"/>
@@ -5018,12 +5060,12 @@
       <c r="J106" s="24" t="n"/>
       <c r="K106" s="42" t="inlineStr">
         <is>
-          <t>26-0521-0024</t>
-        </is>
-      </c>
-      <c r="L106" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>24-1102-0016</t>
+        </is>
+      </c>
+      <c r="L106" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -5035,22 +5077,22 @@
       </c>
       <c r="B107" s="35" t="inlineStr">
         <is>
-          <t>72" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C107" s="35" t="inlineStr">
         <is>
-          <t>Matte White</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D107" s="35" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E107" s="35" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="F107" s="24" t="n"/>
@@ -5060,12 +5102,12 @@
       <c r="J107" s="24" t="n"/>
       <c r="K107" s="42" t="inlineStr">
         <is>
-          <t>26-0521-0025</t>
-        </is>
-      </c>
-      <c r="L107" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>24-1102-0017</t>
+        </is>
+      </c>
+      <c r="L107" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -5077,22 +5119,22 @@
       </c>
       <c r="B108" s="35" t="inlineStr">
         <is>
-          <t>72" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C108" s="35" t="inlineStr">
         <is>
-          <t>Matte White</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D108" s="35" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E108" s="35" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="F108" s="24" t="n"/>
@@ -5102,130 +5144,158 @@
       <c r="J108" s="24" t="n"/>
       <c r="K108" s="42" t="inlineStr">
         <is>
-          <t>26-0521-0026</t>
-        </is>
-      </c>
-      <c r="L108" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>24-1102-0018</t>
+        </is>
+      </c>
+      <c r="L108" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="49" t="inlineStr">
+      <c r="A109" s="37" t="n"/>
+      <c r="B109" s="38" t="n"/>
+      <c r="C109" s="38" t="n"/>
+      <c r="D109" s="38" t="n"/>
+      <c r="E109" s="38" t="n"/>
+      <c r="F109" s="38" t="n"/>
+      <c r="G109" s="38" t="n"/>
+      <c r="H109" s="38" t="n"/>
+      <c r="I109" s="38" t="n"/>
+      <c r="J109" s="38" t="n"/>
+      <c r="K109" s="38" t="n"/>
+      <c r="L109" s="39" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="65" t="inlineStr">
         <is>
           <t>Sevilla French Door</t>
         </is>
       </c>
-      <c r="B109" s="50" t="inlineStr">
-        <is>
-          <t>72" x 80"</t>
-        </is>
-      </c>
-      <c r="C109" s="50" t="inlineStr">
-        <is>
-          <t>Matte White</t>
-        </is>
-      </c>
-      <c r="D109" s="50" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E109" s="50" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F109" s="51" t="n"/>
-      <c r="G109" s="51" t="n"/>
-      <c r="H109" s="51" t="n"/>
-      <c r="I109" s="51" t="n"/>
-      <c r="J109" s="51" t="n"/>
-      <c r="K109" s="55" t="inlineStr">
-        <is>
-          <t>26-0521-0027</t>
-        </is>
-      </c>
-      <c r="L109" s="65" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="35" t="n"/>
-      <c r="B110" s="35" t="n"/>
-      <c r="C110" s="35" t="n"/>
-      <c r="D110" s="35" t="n"/>
-      <c r="E110" s="35" t="n"/>
-      <c r="F110" s="24" t="n"/>
-      <c r="G110" s="24" t="n"/>
-      <c r="H110" s="24" t="n"/>
-      <c r="I110" s="24" t="n"/>
-      <c r="J110" s="24" t="n"/>
-      <c r="K110" s="42" t="n"/>
-      <c r="L110" s="42" t="n"/>
+      <c r="B110" s="66" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C110" s="66" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D110" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E110" s="66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F110" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G110" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" s="38" t="n"/>
+      <c r="J110" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K110" s="42" t="inlineStr">
+        <is>
+          <t>24-1102-0019</t>
+        </is>
+      </c>
+      <c r="L110" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="38" t="n"/>
-      <c r="B111" s="38" t="n"/>
-      <c r="C111" s="38" t="n"/>
-      <c r="D111" s="38" t="n"/>
-      <c r="E111" s="38" t="n"/>
-      <c r="F111" s="38" t="n"/>
-      <c r="G111" s="38" t="n"/>
-      <c r="H111" s="38" t="n"/>
-      <c r="I111" s="38" t="n"/>
-      <c r="J111" s="38" t="n"/>
-      <c r="K111" s="38" t="n"/>
-      <c r="L111" s="42" t="n"/>
+      <c r="A111" s="34" t="inlineStr">
+        <is>
+          <t>Sevilla French Door</t>
+        </is>
+      </c>
+      <c r="B111" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C111" s="35" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D111" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E111" s="35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F111" s="42" t="n"/>
+      <c r="G111" s="42" t="n"/>
+      <c r="H111" s="42" t="n"/>
+      <c r="I111" s="32" t="n"/>
+      <c r="J111" s="42" t="n"/>
+      <c r="K111" s="42" t="inlineStr">
+        <is>
+          <t>24-1102-0020</t>
+        </is>
+      </c>
+      <c r="L111" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="70" t="inlineStr">
-        <is>
-          <t>Valencia Single Door</t>
-        </is>
-      </c>
-      <c r="B112" s="71" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C112" s="71" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D112" s="71" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E112" s="71" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F112" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G112" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="H112" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="I112" s="68" t="n"/>
-      <c r="J112" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="K112" s="27" t="inlineStr">
-        <is>
-          <t>24-0315-0001</t>
-        </is>
-      </c>
-      <c r="L112" s="29" t="inlineStr">
+      <c r="A112" s="34" t="inlineStr">
+        <is>
+          <t>Sevilla French Door</t>
+        </is>
+      </c>
+      <c r="B112" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C112" s="35" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D112" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E112" s="35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F112" s="32" t="n"/>
+      <c r="G112" s="32" t="n"/>
+      <c r="H112" s="32" t="n"/>
+      <c r="I112" s="32" t="n"/>
+      <c r="J112" s="32" t="n"/>
+      <c r="K112" s="42" t="inlineStr">
+        <is>
+          <t>24-1102-0021</t>
+        </is>
+      </c>
+      <c r="L112" s="33" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -5234,17 +5304,17 @@
     <row r="113">
       <c r="A113" s="34" t="inlineStr">
         <is>
-          <t>Valencia Single Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="B113" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C113" s="35" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="D113" s="35" t="inlineStr">
@@ -5254,39 +5324,39 @@
       </c>
       <c r="E113" s="35" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F113" s="42" t="n"/>
-      <c r="G113" s="42" t="n"/>
-      <c r="H113" s="42" t="n"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F113" s="32" t="n"/>
+      <c r="G113" s="32" t="n"/>
+      <c r="H113" s="32" t="n"/>
       <c r="I113" s="32" t="n"/>
-      <c r="J113" s="43" t="n"/>
+      <c r="J113" s="32" t="n"/>
       <c r="K113" s="42" t="inlineStr">
         <is>
-          <t>24-0315-0002</t>
-        </is>
-      </c>
-      <c r="L113" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0521-0021</t>
+        </is>
+      </c>
+      <c r="L113" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="34" t="inlineStr">
         <is>
-          <t>Valencia Single Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="B114" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C114" s="35" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="D114" s="35" t="inlineStr">
@@ -5296,7 +5366,7 @@
       </c>
       <c r="E114" s="35" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F114" s="32" t="n"/>
@@ -5306,29 +5376,29 @@
       <c r="J114" s="32" t="n"/>
       <c r="K114" s="42" t="inlineStr">
         <is>
-          <t>24-0315-0003</t>
-        </is>
-      </c>
-      <c r="L114" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0521-0022</t>
+        </is>
+      </c>
+      <c r="L114" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="34" t="inlineStr">
         <is>
-          <t>Valencia Single Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="B115" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C115" s="35" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="D115" s="35" t="inlineStr">
@@ -5338,39 +5408,35 @@
       </c>
       <c r="E115" s="35" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F115" s="32" t="n"/>
-      <c r="G115" s="32" t="n"/>
-      <c r="H115" s="32" t="n"/>
-      <c r="I115" s="32" t="n"/>
-      <c r="J115" s="32" t="n"/>
-      <c r="K115" s="42" t="inlineStr">
-        <is>
-          <t>24-0315-0004</t>
-        </is>
-      </c>
-      <c r="L115" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F115" s="24" t="n"/>
+      <c r="G115" s="24" t="n"/>
+      <c r="H115" s="24" t="n"/>
+      <c r="I115" s="24" t="n"/>
+      <c r="J115" s="24" t="n"/>
+      <c r="K115" s="42" t="n"/>
+      <c r="L115" s="36" t="inlineStr">
+        <is>
+          <t>In Production</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="34" t="inlineStr">
         <is>
-          <t>Valencia Single Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="B116" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C116" s="35" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="D116" s="35" t="inlineStr">
@@ -5380,101 +5446,77 @@
       </c>
       <c r="E116" s="35" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F116" s="32" t="n"/>
-      <c r="G116" s="32" t="n"/>
-      <c r="H116" s="32" t="n"/>
-      <c r="I116" s="32" t="n"/>
-      <c r="J116" s="32" t="n"/>
-      <c r="K116" s="42" t="inlineStr">
-        <is>
-          <t>26-0502-0010</t>
-        </is>
-      </c>
-      <c r="L116" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F116" s="42" t="n"/>
+      <c r="G116" s="42" t="n"/>
+      <c r="H116" s="42" t="n"/>
+      <c r="I116" s="24" t="n"/>
+      <c r="J116" s="42" t="n"/>
+      <c r="K116" s="42" t="n"/>
+      <c r="L116" s="36" t="inlineStr">
+        <is>
+          <t>In Production</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="34" t="inlineStr">
-        <is>
-          <t>Valencia Single Door</t>
-        </is>
-      </c>
-      <c r="B117" s="35" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C117" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D117" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E117" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F117" s="32" t="n"/>
-      <c r="G117" s="32" t="n"/>
-      <c r="H117" s="32" t="n"/>
-      <c r="I117" s="32" t="n"/>
-      <c r="J117" s="32" t="n"/>
-      <c r="K117" s="42" t="inlineStr">
-        <is>
-          <t>26-0502-0011</t>
-        </is>
-      </c>
-      <c r="L117" s="64" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-001</t>
-        </is>
-      </c>
+      <c r="A117" s="34" t="n"/>
+      <c r="B117" s="35" t="n"/>
+      <c r="C117" s="35" t="n"/>
+      <c r="D117" s="35" t="n"/>
+      <c r="E117" s="35" t="n"/>
+      <c r="F117" s="24" t="n"/>
+      <c r="G117" s="24" t="n"/>
+      <c r="H117" s="24" t="n"/>
+      <c r="I117" s="24" t="n"/>
+      <c r="J117" s="24" t="n"/>
+      <c r="K117" s="42" t="n"/>
+      <c r="L117" s="39" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="34" t="inlineStr">
-        <is>
-          <t>Valencia Single Door</t>
-        </is>
-      </c>
-      <c r="B118" s="35" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C118" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D118" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E118" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F118" s="38" t="n"/>
-      <c r="G118" s="38" t="n"/>
-      <c r="H118" s="38" t="n"/>
-      <c r="I118" s="38" t="n"/>
-      <c r="J118" s="38" t="n"/>
+      <c r="A118" s="65" t="inlineStr">
+        <is>
+          <t>Sevilla French Door</t>
+        </is>
+      </c>
+      <c r="B118" s="66" t="inlineStr">
+        <is>
+          <t>72" x 80"</t>
+        </is>
+      </c>
+      <c r="C118" s="66" t="inlineStr">
+        <is>
+          <t>Matte White</t>
+        </is>
+      </c>
+      <c r="D118" s="66" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E118" s="66" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F118" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I118" s="24" t="n"/>
+      <c r="J118" s="42" t="n">
+        <v>5</v>
+      </c>
       <c r="K118" s="42" t="inlineStr">
         <is>
-          <t>26-0502-0012</t>
+          <t>26-0521-0023</t>
         </is>
       </c>
       <c r="L118" s="64" t="inlineStr">
@@ -5486,17 +5528,17 @@
     <row r="119">
       <c r="A119" s="34" t="inlineStr">
         <is>
-          <t>Valencia Single Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="B119" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>72" x 80"</t>
         </is>
       </c>
       <c r="C119" s="35" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Matte White</t>
         </is>
       </c>
       <c r="D119" s="35" t="inlineStr">
@@ -5506,35 +5548,39 @@
       </c>
       <c r="E119" s="35" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F119" s="42" t="n"/>
-      <c r="G119" s="42" t="n"/>
-      <c r="H119" s="42" t="n"/>
-      <c r="I119" s="32" t="n"/>
-      <c r="J119" s="42" t="n"/>
-      <c r="K119" s="42" t="n"/>
-      <c r="L119" s="36" t="inlineStr">
-        <is>
-          <t>In Production</t>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F119" s="24" t="n"/>
+      <c r="G119" s="24" t="n"/>
+      <c r="H119" s="24" t="n"/>
+      <c r="I119" s="24" t="n"/>
+      <c r="J119" s="24" t="n"/>
+      <c r="K119" s="42" t="inlineStr">
+        <is>
+          <t>26-0521-0024</t>
+        </is>
+      </c>
+      <c r="L119" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="34" t="inlineStr">
         <is>
-          <t>Valencia Single Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="B120" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>72" x 80"</t>
         </is>
       </c>
       <c r="C120" s="35" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Matte White</t>
         </is>
       </c>
       <c r="D120" s="35" t="inlineStr">
@@ -5544,35 +5590,39 @@
       </c>
       <c r="E120" s="35" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F120" s="32" t="n"/>
-      <c r="G120" s="32" t="n"/>
-      <c r="H120" s="32" t="n"/>
-      <c r="I120" s="32" t="n"/>
-      <c r="J120" s="32" t="n"/>
-      <c r="K120" s="42" t="n"/>
-      <c r="L120" s="36" t="inlineStr">
-        <is>
-          <t>In Production</t>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F120" s="24" t="n"/>
+      <c r="G120" s="24" t="n"/>
+      <c r="H120" s="24" t="n"/>
+      <c r="I120" s="24" t="n"/>
+      <c r="J120" s="24" t="n"/>
+      <c r="K120" s="42" t="inlineStr">
+        <is>
+          <t>26-0521-0025</t>
+        </is>
+      </c>
+      <c r="L120" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="34" t="inlineStr">
         <is>
-          <t>Valencia Single Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="B121" s="35" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>72" x 80"</t>
         </is>
       </c>
       <c r="C121" s="35" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Matte White</t>
         </is>
       </c>
       <c r="D121" s="35" t="inlineStr">
@@ -5582,164 +5632,140 @@
       </c>
       <c r="E121" s="35" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F121" s="32" t="n"/>
-      <c r="G121" s="32" t="n"/>
-      <c r="H121" s="32" t="n"/>
-      <c r="I121" s="32" t="n"/>
-      <c r="J121" s="32" t="n"/>
-      <c r="K121" s="42" t="n"/>
-      <c r="L121" s="36" t="inlineStr">
-        <is>
-          <t>In Production</t>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F121" s="24" t="n"/>
+      <c r="G121" s="24" t="n"/>
+      <c r="H121" s="24" t="n"/>
+      <c r="I121" s="24" t="n"/>
+      <c r="J121" s="24" t="n"/>
+      <c r="K121" s="42" t="inlineStr">
+        <is>
+          <t>26-0521-0026</t>
+        </is>
+      </c>
+      <c r="L121" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="34" t="n"/>
-      <c r="B122" s="35" t="n"/>
-      <c r="C122" s="35" t="n"/>
-      <c r="D122" s="35" t="n"/>
-      <c r="E122" s="35" t="n"/>
-      <c r="F122" s="24" t="n"/>
-      <c r="G122" s="24" t="n"/>
-      <c r="H122" s="24" t="n"/>
-      <c r="I122" s="24" t="n"/>
-      <c r="J122" s="24" t="n"/>
-      <c r="K122" s="42" t="n"/>
-      <c r="L122" s="39" t="n"/>
+      <c r="A122" s="49" t="inlineStr">
+        <is>
+          <t>Sevilla French Door</t>
+        </is>
+      </c>
+      <c r="B122" s="50" t="inlineStr">
+        <is>
+          <t>72" x 80"</t>
+        </is>
+      </c>
+      <c r="C122" s="50" t="inlineStr">
+        <is>
+          <t>Matte White</t>
+        </is>
+      </c>
+      <c r="D122" s="50" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E122" s="50" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F122" s="51" t="n"/>
+      <c r="G122" s="51" t="n"/>
+      <c r="H122" s="51" t="n"/>
+      <c r="I122" s="51" t="n"/>
+      <c r="J122" s="51" t="n"/>
+      <c r="K122" s="55" t="inlineStr">
+        <is>
+          <t>26-0521-0027</t>
+        </is>
+      </c>
+      <c r="L122" s="67" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="72" t="inlineStr">
-        <is>
-          <t>Valencia Single Door</t>
-        </is>
-      </c>
-      <c r="B123" s="73" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C123" s="73" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D123" s="73" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E123" s="73" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F123" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G123" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="42" t="n">
-        <v>0</v>
-      </c>
+      <c r="A123" s="35" t="n"/>
+      <c r="B123" s="35" t="n"/>
+      <c r="C123" s="35" t="n"/>
+      <c r="D123" s="35" t="n"/>
+      <c r="E123" s="35" t="n"/>
+      <c r="F123" s="24" t="n"/>
+      <c r="G123" s="24" t="n"/>
+      <c r="H123" s="24" t="n"/>
       <c r="I123" s="24" t="n"/>
-      <c r="J123" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K123" s="42" t="inlineStr">
-        <is>
-          <t>24-0315-0005</t>
-        </is>
-      </c>
-      <c r="L123" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="J123" s="24" t="n"/>
+      <c r="K123" s="42" t="n"/>
+      <c r="L123" s="42" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="34" t="inlineStr">
-        <is>
-          <t>Valencia Single Door</t>
-        </is>
-      </c>
-      <c r="B124" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C124" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D124" s="35" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E124" s="35" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
+      <c r="A124" s="35" t="n"/>
+      <c r="B124" s="35" t="n"/>
+      <c r="C124" s="35" t="n"/>
+      <c r="D124" s="35" t="n"/>
+      <c r="E124" s="35" t="n"/>
       <c r="F124" s="24" t="n"/>
       <c r="G124" s="24" t="n"/>
       <c r="H124" s="24" t="n"/>
       <c r="I124" s="24" t="n"/>
       <c r="J124" s="24" t="n"/>
-      <c r="K124" s="42" t="inlineStr">
-        <is>
-          <t>24-0315-0006</t>
-        </is>
-      </c>
-      <c r="L124" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="K124" s="42" t="n"/>
+      <c r="L124" s="42" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="34" t="inlineStr">
+      <c r="A125" s="68" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B125" s="35" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C125" s="35" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D125" s="35" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E125" s="35" t="inlineStr">
+      <c r="B125" s="69" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C125" s="69" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D125" s="69" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E125" s="69" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F125" s="24" t="n"/>
-      <c r="G125" s="24" t="n"/>
-      <c r="H125" s="24" t="n"/>
-      <c r="I125" s="24" t="n"/>
-      <c r="J125" s="24" t="n"/>
-      <c r="K125" s="42" t="inlineStr">
-        <is>
-          <t>24-0315-0007</t>
-        </is>
-      </c>
-      <c r="L125" s="33" t="inlineStr">
+      <c r="F125" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G125" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I125" s="70" t="n"/>
+      <c r="J125" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="K125" s="27" t="inlineStr">
+        <is>
+          <t>24-0315-0001</t>
+        </is>
+      </c>
+      <c r="L125" s="29" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -5753,7 +5779,7 @@
       </c>
       <c r="B126" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C126" s="35" t="inlineStr">
@@ -5763,7 +5789,7 @@
       </c>
       <c r="D126" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E126" s="35" t="inlineStr">
@@ -5771,14 +5797,14 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F126" s="38" t="n"/>
-      <c r="G126" s="38" t="n"/>
-      <c r="H126" s="38" t="n"/>
-      <c r="I126" s="38" t="n"/>
-      <c r="J126" s="38" t="n"/>
+      <c r="F126" s="24" t="n"/>
+      <c r="G126" s="24" t="n"/>
+      <c r="H126" s="24" t="n"/>
+      <c r="I126" s="24" t="n"/>
+      <c r="J126" s="24" t="n"/>
       <c r="K126" s="42" t="inlineStr">
         <is>
-          <t>24-0315-0008</t>
+          <t>24-0315-0002</t>
         </is>
       </c>
       <c r="L126" s="33" t="inlineStr">
@@ -5795,7 +5821,7 @@
       </c>
       <c r="B127" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C127" s="35" t="inlineStr">
@@ -5805,7 +5831,7 @@
       </c>
       <c r="D127" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E127" s="35" t="inlineStr">
@@ -5813,14 +5839,14 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F127" s="42" t="n"/>
-      <c r="G127" s="42" t="n"/>
-      <c r="H127" s="42" t="n"/>
-      <c r="I127" s="32" t="n"/>
-      <c r="J127" s="43" t="n"/>
+      <c r="F127" s="24" t="n"/>
+      <c r="G127" s="24" t="n"/>
+      <c r="H127" s="24" t="n"/>
+      <c r="I127" s="24" t="n"/>
+      <c r="J127" s="24" t="n"/>
       <c r="K127" s="42" t="inlineStr">
         <is>
-          <t>24-0315-0009</t>
+          <t>24-0315-0003</t>
         </is>
       </c>
       <c r="L127" s="33" t="inlineStr">
@@ -5837,7 +5863,7 @@
       </c>
       <c r="B128" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C128" s="35" t="inlineStr">
@@ -5847,7 +5873,7 @@
       </c>
       <c r="D128" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E128" s="35" t="inlineStr">
@@ -5862,7 +5888,7 @@
       <c r="J128" s="24" t="n"/>
       <c r="K128" s="42" t="inlineStr">
         <is>
-          <t>24-0315-0010</t>
+          <t>24-0315-0004</t>
         </is>
       </c>
       <c r="L128" s="33" t="inlineStr">
@@ -5879,7 +5905,7 @@
       </c>
       <c r="B129" s="35" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C129" s="35" t="inlineStr">
@@ -5889,7 +5915,7 @@
       </c>
       <c r="D129" s="35" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E129" s="35" t="inlineStr">
@@ -5897,141 +5923,1047 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F129" s="42" t="n"/>
-      <c r="G129" s="42" t="n"/>
-      <c r="H129" s="42" t="n"/>
+      <c r="F129" s="24" t="n"/>
+      <c r="G129" s="24" t="n"/>
+      <c r="H129" s="24" t="n"/>
       <c r="I129" s="24" t="n"/>
-      <c r="J129" s="42" t="n"/>
+      <c r="J129" s="24" t="n"/>
       <c r="K129" s="42" t="inlineStr">
         <is>
-          <t>24-0315-0011</t>
-        </is>
-      </c>
-      <c r="L129" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0502-0010</t>
+        </is>
+      </c>
+      <c r="L129" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="34" t="n"/>
-      <c r="B130" s="35" t="n"/>
-      <c r="C130" s="35" t="n"/>
-      <c r="D130" s="35" t="n"/>
-      <c r="E130" s="35" t="n"/>
+      <c r="A130" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B130" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C130" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D130" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E130" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
       <c r="F130" s="24" t="n"/>
       <c r="G130" s="24" t="n"/>
       <c r="H130" s="24" t="n"/>
       <c r="I130" s="24" t="n"/>
       <c r="J130" s="24" t="n"/>
-      <c r="K130" s="42" t="n"/>
-      <c r="L130" s="39" t="n"/>
+      <c r="K130" s="42" t="inlineStr">
+        <is>
+          <t>26-0502-0011</t>
+        </is>
+      </c>
+      <c r="L130" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="72" t="inlineStr">
+      <c r="A131" s="34" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B131" s="73" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C131" s="73" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D131" s="73" t="inlineStr">
-        <is>
-          <t>Right Outswing</t>
-        </is>
-      </c>
-      <c r="E131" s="73" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F131" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="42" t="n">
-        <v>0</v>
-      </c>
+      <c r="B131" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C131" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D131" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E131" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F131" s="24" t="n"/>
+      <c r="G131" s="24" t="n"/>
+      <c r="H131" s="24" t="n"/>
       <c r="I131" s="24" t="n"/>
-      <c r="J131" s="42" t="n">
-        <v>2</v>
-      </c>
+      <c r="J131" s="24" t="n"/>
       <c r="K131" s="42" t="inlineStr">
         <is>
-          <t>24-0721-0012</t>
-        </is>
-      </c>
-      <c r="L131" s="33" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0502-0012</t>
+        </is>
+      </c>
+      <c r="L131" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="49" t="inlineStr">
+      <c r="A132" s="34" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B132" s="50" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C132" s="50" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D132" s="50" t="inlineStr">
-        <is>
-          <t>Right Outswing</t>
-        </is>
-      </c>
-      <c r="E132" s="50" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F132" s="51" t="n"/>
-      <c r="G132" s="51" t="n"/>
-      <c r="H132" s="51" t="n"/>
-      <c r="I132" s="51" t="n"/>
-      <c r="J132" s="51" t="n"/>
-      <c r="K132" s="55" t="inlineStr">
-        <is>
-          <t>24-0721-0013</t>
-        </is>
-      </c>
-      <c r="L132" s="47" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+      <c r="B132" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C132" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D132" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E132" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F132" s="24" t="n"/>
+      <c r="G132" s="24" t="n"/>
+      <c r="H132" s="24" t="n"/>
+      <c r="I132" s="24" t="n"/>
+      <c r="J132" s="24" t="n"/>
+      <c r="K132" s="42" t="n"/>
+      <c r="L132" s="36" t="inlineStr">
+        <is>
+          <t>In Production</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="24" t="n"/>
-      <c r="B133" s="24" t="n"/>
-      <c r="C133" s="24" t="n"/>
-      <c r="D133" s="24" t="n"/>
-      <c r="E133" s="24" t="n"/>
+      <c r="A133" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B133" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C133" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D133" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E133" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
       <c r="F133" s="24" t="n"/>
       <c r="G133" s="24" t="n"/>
       <c r="H133" s="24" t="n"/>
       <c r="I133" s="24" t="n"/>
       <c r="J133" s="24" t="n"/>
-      <c r="K133" s="24" t="n"/>
-      <c r="L133" s="63" t="n"/>
+      <c r="K133" s="42" t="n"/>
+      <c r="L133" s="36" t="inlineStr">
+        <is>
+          <t>In Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B134" s="35" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C134" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D134" s="35" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E134" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F134" s="24" t="n"/>
+      <c r="G134" s="24" t="n"/>
+      <c r="H134" s="24" t="n"/>
+      <c r="I134" s="24" t="n"/>
+      <c r="J134" s="24" t="n"/>
+      <c r="K134" s="42" t="n"/>
+      <c r="L134" s="36" t="inlineStr">
+        <is>
+          <t>In Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="34" t="n"/>
+      <c r="B135" s="35" t="n"/>
+      <c r="C135" s="35" t="n"/>
+      <c r="D135" s="35" t="n"/>
+      <c r="E135" s="35" t="n"/>
+      <c r="F135" s="24" t="n"/>
+      <c r="G135" s="24" t="n"/>
+      <c r="H135" s="24" t="n"/>
+      <c r="I135" s="24" t="n"/>
+      <c r="J135" s="24" t="n"/>
+      <c r="K135" s="42" t="n"/>
+      <c r="L135" s="39" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="65" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B136" s="66" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C136" s="66" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D136" s="66" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E136" s="66" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F136" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G136" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I136" s="38" t="n"/>
+      <c r="J136" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="K136" s="42" t="inlineStr">
+        <is>
+          <t>24-0315-0005</t>
+        </is>
+      </c>
+      <c r="L136" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B137" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C137" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D137" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E137" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F137" s="38" t="n"/>
+      <c r="G137" s="38" t="n"/>
+      <c r="H137" s="38" t="n"/>
+      <c r="I137" s="38" t="n"/>
+      <c r="J137" s="38" t="n"/>
+      <c r="K137" s="42" t="inlineStr">
+        <is>
+          <t>24-0315-0006</t>
+        </is>
+      </c>
+      <c r="L137" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B138" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C138" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D138" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E138" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F138" s="42" t="n"/>
+      <c r="G138" s="42" t="n"/>
+      <c r="H138" s="42" t="n"/>
+      <c r="I138" s="32" t="n"/>
+      <c r="J138" s="43" t="n"/>
+      <c r="K138" s="42" t="inlineStr">
+        <is>
+          <t>24-0315-0007</t>
+        </is>
+      </c>
+      <c r="L138" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B139" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C139" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D139" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E139" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F139" s="32" t="n"/>
+      <c r="G139" s="32" t="n"/>
+      <c r="H139" s="32" t="n"/>
+      <c r="I139" s="32" t="n"/>
+      <c r="J139" s="32" t="n"/>
+      <c r="K139" s="42" t="inlineStr">
+        <is>
+          <t>24-0315-0008</t>
+        </is>
+      </c>
+      <c r="L139" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B140" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C140" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D140" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E140" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F140" s="32" t="n"/>
+      <c r="G140" s="32" t="n"/>
+      <c r="H140" s="32" t="n"/>
+      <c r="I140" s="32" t="n"/>
+      <c r="J140" s="32" t="n"/>
+      <c r="K140" s="42" t="inlineStr">
+        <is>
+          <t>24-0315-0009</t>
+        </is>
+      </c>
+      <c r="L140" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B141" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C141" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D141" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E141" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F141" s="32" t="n"/>
+      <c r="G141" s="32" t="n"/>
+      <c r="H141" s="32" t="n"/>
+      <c r="I141" s="32" t="n"/>
+      <c r="J141" s="32" t="n"/>
+      <c r="K141" s="42" t="inlineStr">
+        <is>
+          <t>24-0315-0010</t>
+        </is>
+      </c>
+      <c r="L141" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B142" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C142" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D142" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E142" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F142" s="32" t="n"/>
+      <c r="G142" s="32" t="n"/>
+      <c r="H142" s="32" t="n"/>
+      <c r="I142" s="32" t="n"/>
+      <c r="J142" s="32" t="n"/>
+      <c r="K142" s="42" t="inlineStr">
+        <is>
+          <t>24-0315-0011</t>
+        </is>
+      </c>
+      <c r="L142" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B143" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C143" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D143" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E143" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F143" s="38" t="n"/>
+      <c r="G143" s="38" t="n"/>
+      <c r="H143" s="38" t="n"/>
+      <c r="I143" s="38" t="n"/>
+      <c r="J143" s="38" t="n"/>
+      <c r="K143" s="42" t="inlineStr">
+        <is>
+          <t>26-0515-0013</t>
+        </is>
+      </c>
+      <c r="L143" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B144" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C144" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D144" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E144" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F144" s="42" t="n"/>
+      <c r="G144" s="42" t="n"/>
+      <c r="H144" s="42" t="n"/>
+      <c r="I144" s="32" t="n"/>
+      <c r="J144" s="42" t="n"/>
+      <c r="K144" s="42" t="inlineStr">
+        <is>
+          <t>26-0515-0014</t>
+        </is>
+      </c>
+      <c r="L144" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B145" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C145" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D145" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E145" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F145" s="32" t="n"/>
+      <c r="G145" s="32" t="n"/>
+      <c r="H145" s="32" t="n"/>
+      <c r="I145" s="32" t="n"/>
+      <c r="J145" s="32" t="n"/>
+      <c r="K145" s="42" t="inlineStr">
+        <is>
+          <t>26-0515-0015</t>
+        </is>
+      </c>
+      <c r="L145" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B146" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C146" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D146" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E146" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F146" s="32" t="n"/>
+      <c r="G146" s="32" t="n"/>
+      <c r="H146" s="32" t="n"/>
+      <c r="I146" s="32" t="n"/>
+      <c r="J146" s="32" t="n"/>
+      <c r="K146" s="42" t="inlineStr">
+        <is>
+          <t>26-0515-0016</t>
+        </is>
+      </c>
+      <c r="L146" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B147" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C147" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D147" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E147" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F147" s="24" t="n"/>
+      <c r="G147" s="24" t="n"/>
+      <c r="H147" s="24" t="n"/>
+      <c r="I147" s="24" t="n"/>
+      <c r="J147" s="24" t="n"/>
+      <c r="K147" s="42" t="inlineStr">
+        <is>
+          <t>26-0515-0017</t>
+        </is>
+      </c>
+      <c r="L147" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B148" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C148" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D148" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E148" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F148" s="24" t="n"/>
+      <c r="G148" s="24" t="n"/>
+      <c r="H148" s="24" t="n"/>
+      <c r="I148" s="24" t="n"/>
+      <c r="J148" s="24" t="n"/>
+      <c r="K148" s="42" t="inlineStr">
+        <is>
+          <t>26-0515-0018</t>
+        </is>
+      </c>
+      <c r="L148" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B149" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C149" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D149" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E149" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F149" s="24" t="n"/>
+      <c r="G149" s="24" t="n"/>
+      <c r="H149" s="24" t="n"/>
+      <c r="I149" s="24" t="n"/>
+      <c r="J149" s="24" t="n"/>
+      <c r="K149" s="42" t="inlineStr">
+        <is>
+          <t>26-0515-0019</t>
+        </is>
+      </c>
+      <c r="L149" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="34" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B150" s="35" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C150" s="35" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D150" s="35" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E150" s="35" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F150" s="24" t="n"/>
+      <c r="G150" s="24" t="n"/>
+      <c r="H150" s="24" t="n"/>
+      <c r="I150" s="24" t="n"/>
+      <c r="J150" s="24" t="n"/>
+      <c r="K150" s="42" t="inlineStr">
+        <is>
+          <t>26-0515-0020</t>
+        </is>
+      </c>
+      <c r="L150" s="64" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="37" t="n"/>
+      <c r="B151" s="38" t="n"/>
+      <c r="C151" s="38" t="n"/>
+      <c r="D151" s="38" t="n"/>
+      <c r="E151" s="38" t="n"/>
+      <c r="F151" s="38" t="n"/>
+      <c r="G151" s="38" t="n"/>
+      <c r="H151" s="38" t="n"/>
+      <c r="I151" s="38" t="n"/>
+      <c r="J151" s="38" t="n"/>
+      <c r="K151" s="38" t="n"/>
+      <c r="L151" s="39" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="65" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B152" s="66" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C152" s="66" t="inlineStr">
+        <is>
+          <t>Oil-Rubbed Bronze</t>
+        </is>
+      </c>
+      <c r="D152" s="66" t="inlineStr">
+        <is>
+          <t>Right Outswing</t>
+        </is>
+      </c>
+      <c r="E152" s="66" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F152" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G152" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="32" t="n"/>
+      <c r="J152" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K152" s="42" t="inlineStr">
+        <is>
+          <t>24-0721-0012</t>
+        </is>
+      </c>
+      <c r="L152" s="33" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="49" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B153" s="50" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C153" s="50" t="inlineStr">
+        <is>
+          <t>Oil-Rubbed Bronze</t>
+        </is>
+      </c>
+      <c r="D153" s="50" t="inlineStr">
+        <is>
+          <t>Right Outswing</t>
+        </is>
+      </c>
+      <c r="E153" s="50" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F153" s="51" t="n"/>
+      <c r="G153" s="51" t="n"/>
+      <c r="H153" s="51" t="n"/>
+      <c r="I153" s="51" t="n"/>
+      <c r="J153" s="51" t="n"/>
+      <c r="K153" s="55" t="inlineStr">
+        <is>
+          <t>24-0721-0013</t>
+        </is>
+      </c>
+      <c r="L153" s="47" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="66" t="n"/>
+      <c r="B154" s="66" t="n"/>
+      <c r="C154" s="66" t="n"/>
+      <c r="D154" s="66" t="n"/>
+      <c r="E154" s="66" t="n"/>
+      <c r="F154" s="42" t="n"/>
+      <c r="G154" s="42" t="n"/>
+      <c r="H154" s="42" t="n"/>
+      <c r="I154" s="24" t="n"/>
+      <c r="J154" s="42" t="n"/>
+      <c r="K154" s="42" t="n"/>
+      <c r="L154" s="42" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="35" t="n"/>
+      <c r="B155" s="35" t="n"/>
+      <c r="C155" s="35" t="n"/>
+      <c r="D155" s="35" t="n"/>
+      <c r="E155" s="35" t="n"/>
+      <c r="F155" s="24" t="n"/>
+      <c r="G155" s="24" t="n"/>
+      <c r="H155" s="24" t="n"/>
+      <c r="I155" s="24" t="n"/>
+      <c r="J155" s="24" t="n"/>
+      <c r="K155" s="42" t="n"/>
+      <c r="L155" s="42" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="35" t="n"/>
+      <c r="B156" s="35" t="n"/>
+      <c r="C156" s="35" t="n"/>
+      <c r="D156" s="35" t="n"/>
+      <c r="E156" s="35" t="n"/>
+      <c r="F156" s="24" t="n"/>
+      <c r="G156" s="24" t="n"/>
+      <c r="H156" s="24" t="n"/>
+      <c r="I156" s="24" t="n"/>
+      <c r="J156" s="24" t="n"/>
+      <c r="K156" s="42" t="n"/>
+      <c r="L156" s="42" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="35" t="n"/>
+      <c r="B157" s="35" t="n"/>
+      <c r="C157" s="35" t="n"/>
+      <c r="D157" s="35" t="n"/>
+      <c r="E157" s="35" t="n"/>
+      <c r="F157" s="24" t="n"/>
+      <c r="G157" s="24" t="n"/>
+      <c r="H157" s="24" t="n"/>
+      <c r="I157" s="24" t="n"/>
+      <c r="J157" s="24" t="n"/>
+      <c r="K157" s="42" t="n"/>
+      <c r="L157" s="42" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="24" t="n"/>
+      <c r="B158" s="24" t="n"/>
+      <c r="C158" s="24" t="n"/>
+      <c r="D158" s="24" t="n"/>
+      <c r="E158" s="24" t="n"/>
+      <c r="F158" s="24" t="n"/>
+      <c r="G158" s="24" t="n"/>
+      <c r="H158" s="24" t="n"/>
+      <c r="I158" s="24" t="n"/>
+      <c r="J158" s="24" t="n"/>
+      <c r="K158" s="24" t="n"/>
+      <c r="L158" s="63" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J3:J74">

--- a/inventory_master.xlsx
+++ b/inventory_master.xlsx
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M285"/>
+  <dimension ref="A1:M286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1901,12 +1901,12 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>26-0702-0082</t>
+          <t>26-0618-0126</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -1948,12 +1948,12 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>26-0702-0083</t>
+          <t>26-0618-0127</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0126</t>
+          <t>26-0618-0128</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -2042,12 +2042,12 @@
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0127</t>
+          <t>26-0702-0082</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       <c r="K32" s="20" t="n"/>
       <c r="L32" s="19" t="inlineStr">
         <is>
-          <t>26-0618-0128</t>
+          <t>26-0702-0083</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>26-0714-0097</t>
+          <t>26-0618-0131</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>26-0714-0098</t>
+          <t>26-0618-0132</t>
         </is>
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0131</t>
+          <t>26-0707-0176</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-004</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2577,12 @@
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0132</t>
+          <t>26-0714-0097</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       <c r="K45" s="20" t="n"/>
       <c r="L45" s="19" t="inlineStr">
         <is>
-          <t>26-0707-0176</t>
+          <t>26-0714-0098</t>
         </is>
       </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -6027,13 +6027,13 @@
         </is>
       </c>
       <c r="G124" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J124" s="9" t="n">
         <v>22</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0057</t>
+          <t>26-0618-0059</t>
         </is>
       </c>
       <c r="M124" s="10" t="inlineStr">
@@ -6090,7 +6090,7 @@
       <c r="K125" s="2" t="n"/>
       <c r="L125" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0058</t>
+          <t>26-0618-0060</t>
         </is>
       </c>
       <c r="M125" s="10" t="inlineStr">
@@ -6137,7 +6137,7 @@
       <c r="K126" s="2" t="n"/>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0059</t>
+          <t>26-0618-0061</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
@@ -6184,7 +6184,7 @@
       <c r="K127" s="2" t="n"/>
       <c r="L127" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0060</t>
+          <t>26-0618-0062</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
@@ -6231,7 +6231,7 @@
       <c r="K128" s="2" t="n"/>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0061</t>
+          <t>26-0618-0063</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
@@ -6278,7 +6278,7 @@
       <c r="K129" s="2" t="n"/>
       <c r="L129" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0062</t>
+          <t>26-0618-0064</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
@@ -6325,7 +6325,7 @@
       <c r="K130" s="2" t="n"/>
       <c r="L130" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0063</t>
+          <t>26-0618-0065</t>
         </is>
       </c>
       <c r="M130" s="10" t="inlineStr">
@@ -6372,7 +6372,7 @@
       <c r="K131" s="2" t="n"/>
       <c r="L131" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0064</t>
+          <t>26-0618-0066</t>
         </is>
       </c>
       <c r="M131" s="10" t="inlineStr">
@@ -6419,7 +6419,7 @@
       <c r="K132" s="2" t="n"/>
       <c r="L132" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0065</t>
+          <t>26-0618-0067</t>
         </is>
       </c>
       <c r="M132" s="10" t="inlineStr">
@@ -6466,7 +6466,7 @@
       <c r="K133" s="2" t="n"/>
       <c r="L133" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0066</t>
+          <t>26-0618-0068</t>
         </is>
       </c>
       <c r="M133" s="10" t="inlineStr">
@@ -6513,7 +6513,7 @@
       <c r="K134" s="2" t="n"/>
       <c r="L134" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0067</t>
+          <t>26-0618-0069</t>
         </is>
       </c>
       <c r="M134" s="10" t="inlineStr">
@@ -6560,7 +6560,7 @@
       <c r="K135" s="2" t="n"/>
       <c r="L135" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0068</t>
+          <t>26-0618-0070</t>
         </is>
       </c>
       <c r="M135" s="10" t="inlineStr">
@@ -6607,12 +6607,12 @@
       <c r="K136" s="2" t="n"/>
       <c r="L136" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0069</t>
-        </is>
-      </c>
-      <c r="M136" s="10" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0149</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       <c r="K137" s="2" t="n"/>
       <c r="L137" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0070</t>
-        </is>
-      </c>
-      <c r="M137" s="10" t="inlineStr">
-        <is>
-          <t>In Stock</t>
+          <t>26-0618-0150</t>
+        </is>
+      </c>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       <c r="K138" s="2" t="n"/>
       <c r="L138" s="9" t="inlineStr">
         <is>
-          <t>26-0709-0086</t>
+          <t>26-0622-0211</t>
         </is>
       </c>
       <c r="M138" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6748,12 @@
       <c r="K139" s="2" t="n"/>
       <c r="L139" s="9" t="inlineStr">
         <is>
-          <t>26-0709-0087</t>
+          <t>26-0622-0212</t>
         </is>
       </c>
       <c r="M139" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
@@ -6795,12 +6795,12 @@
       <c r="K140" s="2" t="n"/>
       <c r="L140" s="9" t="inlineStr">
         <is>
-          <t>26-0709-0088</t>
+          <t>26-0707-0185</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-004</t>
         </is>
       </c>
     </row>
@@ -6842,12 +6842,12 @@
       <c r="K141" s="2" t="n"/>
       <c r="L141" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0149</t>
+          <t>26-0707-0186</t>
         </is>
       </c>
       <c r="M141" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-004</t>
         </is>
       </c>
     </row>
@@ -6889,12 +6889,12 @@
       <c r="K142" s="2" t="n"/>
       <c r="L142" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0150</t>
+          <t>26-0709-0084</t>
         </is>
       </c>
       <c r="M142" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -6936,12 +6936,12 @@
       <c r="K143" s="2" t="n"/>
       <c r="L143" s="9" t="inlineStr">
         <is>
-          <t>26-0707-0185</t>
+          <t>26-0709-0085</t>
         </is>
       </c>
       <c r="M143" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -6983,12 +6983,12 @@
       <c r="K144" s="2" t="n"/>
       <c r="L144" s="9" t="inlineStr">
         <is>
-          <t>26-0707-0186</t>
+          <t>26-0709-0086</t>
         </is>
       </c>
       <c r="M144" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       <c r="K145" s="2" t="n"/>
       <c r="L145" s="9" t="inlineStr">
         <is>
-          <t>26-0622-0211</t>
+          <t>26-0709-0087</t>
         </is>
       </c>
       <c r="M145" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-005</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -7077,12 +7077,12 @@
       <c r="K146" s="20" t="n"/>
       <c r="L146" s="19" t="inlineStr">
         <is>
-          <t>26-0622-0212</t>
+          <t>26-0709-0088</t>
         </is>
       </c>
       <c r="M146" s="21" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-005</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>26-0721-0099</t>
+          <t>26-0618-0152</t>
         </is>
       </c>
       <c r="M166" s="24" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       <c r="K167" s="2" t="n"/>
       <c r="L167" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0100</t>
+          <t>26-0707-0187</t>
         </is>
       </c>
       <c r="M167" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-004</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7937,7 @@
       <c r="K168" s="2" t="n"/>
       <c r="L168" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0101</t>
+          <t>26-0721-0099</t>
         </is>
       </c>
       <c r="M168" s="11" t="inlineStr">
@@ -7984,7 +7984,7 @@
       <c r="K169" s="2" t="n"/>
       <c r="L169" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0102</t>
+          <t>26-0721-0100</t>
         </is>
       </c>
       <c r="M169" s="11" t="inlineStr">
@@ -8031,7 +8031,7 @@
       <c r="K170" s="2" t="n"/>
       <c r="L170" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0103</t>
+          <t>26-0721-0101</t>
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr">
@@ -8078,12 +8078,12 @@
       <c r="K171" s="2" t="n"/>
       <c r="L171" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0152</t>
+          <t>26-0721-0102</t>
         </is>
       </c>
       <c r="M171" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       <c r="K172" s="2" t="n"/>
       <c r="L172" s="9" t="inlineStr">
         <is>
-          <t>26-0707-0187</t>
+          <t>26-0721-0103</t>
         </is>
       </c>
       <c r="M172" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -8197,12 +8197,12 @@
       </c>
       <c r="L174" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0105</t>
+          <t>26-0618-0153</t>
         </is>
       </c>
       <c r="M174" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -8244,12 +8244,12 @@
       <c r="K175" s="2" t="n"/>
       <c r="L175" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0106</t>
+          <t>26-0618-0154</t>
         </is>
       </c>
       <c r="M175" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -8291,12 +8291,12 @@
       <c r="K176" s="2" t="n"/>
       <c r="L176" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0107</t>
+          <t>26-0622-0222</t>
         </is>
       </c>
       <c r="M176" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
@@ -8338,12 +8338,12 @@
       <c r="K177" s="2" t="n"/>
       <c r="L177" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0108</t>
+          <t>26-0622-0223</t>
         </is>
       </c>
       <c r="M177" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
@@ -8385,12 +8385,12 @@
       <c r="K178" s="2" t="n"/>
       <c r="L178" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0109</t>
+          <t>26-0707-0189</t>
         </is>
       </c>
       <c r="M178" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-004</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       <c r="K179" s="2" t="n"/>
       <c r="L179" s="9" t="inlineStr">
         <is>
-          <t>26-0721-0110</t>
+          <t>26-0721-0105</t>
         </is>
       </c>
       <c r="M179" s="11" t="inlineStr">
@@ -8479,12 +8479,12 @@
       <c r="K180" s="2" t="n"/>
       <c r="L180" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0153</t>
+          <t>26-0721-0106</t>
         </is>
       </c>
       <c r="M180" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -8526,12 +8526,12 @@
       <c r="K181" s="2" t="n"/>
       <c r="L181" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0154</t>
+          <t>26-0721-0107</t>
         </is>
       </c>
       <c r="M181" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -8573,12 +8573,12 @@
       <c r="K182" s="2" t="n"/>
       <c r="L182" s="9" t="inlineStr">
         <is>
-          <t>26-0707-0189</t>
+          <t>26-0721-0108</t>
         </is>
       </c>
       <c r="M182" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -8620,12 +8620,12 @@
       <c r="K183" s="2" t="n"/>
       <c r="L183" s="9" t="inlineStr">
         <is>
-          <t>26-0622-0222</t>
+          <t>26-0721-0109</t>
         </is>
       </c>
       <c r="M183" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-005</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -8667,12 +8667,12 @@
       <c r="K184" s="20" t="n"/>
       <c r="L184" s="19" t="inlineStr">
         <is>
-          <t>26-0622-0223</t>
+          <t>26-0721-0110</t>
         </is>
       </c>
       <c r="M184" s="21" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-005</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -9123,17 +9123,17 @@
         <v>0</v>
       </c>
       <c r="I196" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J196" s="9" t="n">
         <v>0</v>
       </c>
       <c r="K196" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L196" s="9" t="inlineStr">
         <is>
-          <t>26-0622-0239</t>
+          <t>26-0622-0237</t>
         </is>
       </c>
       <c r="M196" s="11" t="inlineStr">
@@ -9180,7 +9180,7 @@
       <c r="K197" s="2" t="n"/>
       <c r="L197" s="9" t="inlineStr">
         <is>
-          <t>26-0622-0240</t>
+          <t>26-0622-0239</t>
         </is>
       </c>
       <c r="M197" s="11" t="inlineStr">
@@ -9190,185 +9190,217 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="12" t="n"/>
-      <c r="B198" s="2" t="n"/>
-      <c r="C198" s="2" t="n"/>
-      <c r="D198" s="2" t="n"/>
-      <c r="E198" s="2" t="n"/>
-      <c r="F198" s="2" t="n"/>
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>Segovia Barn Door</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>48" x 84"</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E198" s="8" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F198" s="9" t="inlineStr">
+        <is>
+          <t>SEG-48X84-MB-RI-CLR</t>
+        </is>
+      </c>
       <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="n"/>
       <c r="J198" s="2" t="n"/>
       <c r="K198" s="2" t="n"/>
-      <c r="L198" s="2" t="n"/>
-      <c r="M198" s="13" t="n"/>
+      <c r="L198" s="9" t="inlineStr">
+        <is>
+          <t>26-0622-0240</t>
+        </is>
+      </c>
+      <c r="M198" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-005</t>
+        </is>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="14" t="inlineStr">
+      <c r="A199" s="12" t="n"/>
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="2" t="n"/>
+      <c r="G199" s="2" t="n"/>
+      <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2" t="n"/>
+      <c r="J199" s="2" t="n"/>
+      <c r="K199" s="2" t="n"/>
+      <c r="L199" s="2" t="n"/>
+      <c r="M199" s="13" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="14" t="inlineStr">
         <is>
           <t>Segovia Barn Door</t>
         </is>
       </c>
-      <c r="B199" s="15" t="inlineStr">
+      <c r="B200" s="15" t="inlineStr">
         <is>
           <t>60" x 84"</t>
         </is>
       </c>
-      <c r="C199" s="15" t="inlineStr">
+      <c r="C200" s="15" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D199" s="15" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E199" s="15" t="inlineStr">
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E200" s="15" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F199" s="9" t="inlineStr">
+      <c r="F200" s="9" t="inlineStr">
         <is>
           <t>SEG-60X84-ORB-LI-FRS</t>
         </is>
       </c>
-      <c r="G199" s="9" t="n">
+      <c r="G200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H199" s="9" t="n">
+      <c r="H200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I199" s="9" t="n">
+      <c r="I200" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J199" s="9" t="n">
+      <c r="J200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K199" s="9" t="n">
+      <c r="K200" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="L199" s="9" t="inlineStr">
+      <c r="L200" s="9" t="inlineStr">
         <is>
           <t>26-0622-0244</t>
         </is>
       </c>
-      <c r="M199" s="11" t="inlineStr">
+      <c r="M200" s="11" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="7" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
         <is>
           <t>Segovia Barn Door</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>60" x 84"</t>
         </is>
       </c>
-      <c r="C200" s="8" t="inlineStr">
+      <c r="C201" s="8" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D200" s="8" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E200" s="8" t="inlineStr">
+      <c r="D201" s="8" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E201" s="8" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F200" s="9" t="inlineStr">
+      <c r="F201" s="9" t="inlineStr">
         <is>
           <t>SEG-60X84-ORB-LI-FRS</t>
         </is>
       </c>
-      <c r="G200" s="2" t="n"/>
-      <c r="H200" s="2" t="n"/>
-      <c r="I200" s="2" t="n"/>
-      <c r="J200" s="2" t="n"/>
-      <c r="K200" s="2" t="n"/>
-      <c r="L200" s="9" t="inlineStr">
+      <c r="G201" s="2" t="n"/>
+      <c r="H201" s="2" t="n"/>
+      <c r="I201" s="2" t="n"/>
+      <c r="J201" s="2" t="n"/>
+      <c r="K201" s="2" t="n"/>
+      <c r="L201" s="9" t="inlineStr">
         <is>
           <t>26-0622-0245</t>
         </is>
       </c>
-      <c r="M200" s="11" t="inlineStr">
+      <c r="M201" s="11" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="17" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="17" t="inlineStr">
         <is>
           <t>Segovia Barn Door</t>
         </is>
       </c>
-      <c r="B201" s="18" t="inlineStr">
+      <c r="B202" s="18" t="inlineStr">
         <is>
           <t>60" x 84"</t>
         </is>
       </c>
-      <c r="C201" s="18" t="inlineStr">
+      <c r="C202" s="18" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D201" s="18" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E201" s="18" t="inlineStr">
+      <c r="D202" s="18" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E202" s="18" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F201" s="19" t="inlineStr">
+      <c r="F202" s="19" t="inlineStr">
         <is>
           <t>SEG-60X84-ORB-LI-FRS</t>
         </is>
       </c>
-      <c r="G201" s="20" t="n"/>
-      <c r="H201" s="20" t="n"/>
-      <c r="I201" s="20" t="n"/>
-      <c r="J201" s="20" t="n"/>
-      <c r="K201" s="20" t="n"/>
-      <c r="L201" s="19" t="inlineStr">
+      <c r="G202" s="20" t="n"/>
+      <c r="H202" s="20" t="n"/>
+      <c r="I202" s="20" t="n"/>
+      <c r="J202" s="20" t="n"/>
+      <c r="K202" s="20" t="n"/>
+      <c r="L202" s="19" t="inlineStr">
         <is>
           <t>26-0622-0246</t>
         </is>
       </c>
-      <c r="M201" s="21" t="inlineStr">
+      <c r="M202" s="21" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="n"/>
-      <c r="B202" s="2" t="n"/>
-      <c r="C202" s="2" t="n"/>
-      <c r="D202" s="2" t="n"/>
-      <c r="E202" s="2" t="n"/>
-      <c r="F202" s="2" t="n"/>
-      <c r="G202" s="2" t="n"/>
-      <c r="H202" s="2" t="n"/>
-      <c r="I202" s="2" t="n"/>
-      <c r="J202" s="2" t="n"/>
-      <c r="K202" s="2" t="n"/>
-      <c r="L202" s="2" t="n"/>
-      <c r="M202" s="22" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -9386,104 +9418,72 @@
       <c r="M203" s="22" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="inlineStr">
+      <c r="A204" s="2" t="n"/>
+      <c r="B204" s="2" t="n"/>
+      <c r="C204" s="2" t="n"/>
+      <c r="D204" s="2" t="n"/>
+      <c r="E204" s="2" t="n"/>
+      <c r="F204" s="2" t="n"/>
+      <c r="G204" s="2" t="n"/>
+      <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+      <c r="J204" s="2" t="n"/>
+      <c r="K204" s="2" t="n"/>
+      <c r="L204" s="2" t="n"/>
+      <c r="M204" s="22" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t>Sevilla French Door</t>
         </is>
       </c>
-      <c r="B204" s="4" t="inlineStr">
+      <c r="B205" s="4" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C204" s="4" t="inlineStr">
+      <c r="C205" s="4" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D204" s="4" t="inlineStr">
+      <c r="D205" s="4" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E204" s="4" t="inlineStr">
+      <c r="E205" s="4" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F204" s="5" t="inlineStr">
+      <c r="F205" s="5" t="inlineStr">
         <is>
           <t>SEV-32X80-BN-RI-RN</t>
         </is>
       </c>
-      <c r="G204" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H204" s="5" t="n">
+      <c r="G205" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H205" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I204" s="5" t="n">
+      <c r="I205" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J204" s="5" t="n">
+      <c r="J205" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K204" s="23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L204" s="5" t="inlineStr">
-        <is>
-          <t>24-1102-0014</t>
-        </is>
-      </c>
-      <c r="M204" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="7" t="inlineStr">
-        <is>
-          <t>Sevilla French Door</t>
-        </is>
-      </c>
-      <c r="B205" s="8" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C205" s="8" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D205" s="8" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E205" s="8" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F205" s="9" t="inlineStr">
-        <is>
-          <t>SEV-32X80-BN-RI-RN</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="n"/>
-      <c r="H205" s="2" t="n"/>
-      <c r="I205" s="2" t="n"/>
-      <c r="J205" s="2" t="n"/>
-      <c r="K205" s="2" t="n"/>
-      <c r="L205" s="9" t="inlineStr">
+      <c r="K205" s="23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L205" s="5" t="inlineStr">
         <is>
           <t>24-1102-0015</t>
         </is>
       </c>
-      <c r="M205" s="10" t="inlineStr">
+      <c r="M205" s="6" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="G219" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H219" s="9" t="n">
         <v>0</v>
@@ -10090,11 +10090,11 @@
         <v>7</v>
       </c>
       <c r="K219" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L219" s="9" t="inlineStr">
         <is>
-          <t>26-0521-0024</t>
+          <t>26-0521-0023</t>
         </is>
       </c>
       <c r="M219" s="10" t="inlineStr">
@@ -10141,7 +10141,7 @@
       <c r="K220" s="2" t="n"/>
       <c r="L220" s="9" t="inlineStr">
         <is>
-          <t>26-0521-0025</t>
+          <t>26-0521-0024</t>
         </is>
       </c>
       <c r="M220" s="10" t="inlineStr">
@@ -10188,7 +10188,7 @@
       <c r="K221" s="2" t="n"/>
       <c r="L221" s="9" t="inlineStr">
         <is>
-          <t>26-0521-0026</t>
+          <t>26-0521-0025</t>
         </is>
       </c>
       <c r="M221" s="10" t="inlineStr">
@@ -10235,7 +10235,7 @@
       <c r="K222" s="2" t="n"/>
       <c r="L222" s="9" t="inlineStr">
         <is>
-          <t>26-0521-0027</t>
+          <t>26-0521-0026</t>
         </is>
       </c>
       <c r="M222" s="10" t="inlineStr">
@@ -10282,12 +10282,12 @@
       <c r="K223" s="2" t="n"/>
       <c r="L223" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0159</t>
-        </is>
-      </c>
-      <c r="M223" s="11" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>26-0521-0027</t>
+        </is>
+      </c>
+      <c r="M223" s="10" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       <c r="K224" s="2" t="n"/>
       <c r="L224" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0160</t>
+          <t>26-0618-0159</t>
         </is>
       </c>
       <c r="M224" s="11" t="inlineStr">
@@ -10376,12 +10376,12 @@
       <c r="K225" s="2" t="n"/>
       <c r="L225" s="9" t="inlineStr">
         <is>
-          <t>26-0622-0206</t>
+          <t>26-0618-0160</t>
         </is>
       </c>
       <c r="M225" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-005</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -10423,76 +10423,108 @@
       <c r="K226" s="2" t="n"/>
       <c r="L226" s="9" t="inlineStr">
         <is>
+          <t>26-0622-0206</t>
+        </is>
+      </c>
+      <c r="M226" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>Sevilla French Door</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>72" x 80"</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>Matte White</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>SEV-72X80-MW-LI-FRS</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="n"/>
+      <c r="H227" s="2" t="n"/>
+      <c r="I227" s="2" t="n"/>
+      <c r="J227" s="2" t="n"/>
+      <c r="K227" s="2" t="n"/>
+      <c r="L227" s="9" t="inlineStr">
+        <is>
           <t>26-0622-0207</t>
         </is>
       </c>
-      <c r="M226" s="11" t="inlineStr">
+      <c r="M227" s="11" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="17" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="17" t="inlineStr">
         <is>
           <t>Sevilla French Door</t>
         </is>
       </c>
-      <c r="B227" s="18" t="inlineStr">
+      <c r="B228" s="18" t="inlineStr">
         <is>
           <t>72" x 80"</t>
         </is>
       </c>
-      <c r="C227" s="18" t="inlineStr">
+      <c r="C228" s="18" t="inlineStr">
         <is>
           <t>Matte White</t>
         </is>
       </c>
-      <c r="D227" s="18" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E227" s="18" t="inlineStr">
+      <c r="D228" s="18" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E228" s="18" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F227" s="19" t="inlineStr">
+      <c r="F228" s="19" t="inlineStr">
         <is>
           <t>SEV-72X80-MW-LI-FRS</t>
         </is>
       </c>
-      <c r="G227" s="20" t="n"/>
-      <c r="H227" s="20" t="n"/>
-      <c r="I227" s="20" t="n"/>
-      <c r="J227" s="20" t="n"/>
-      <c r="K227" s="20" t="n"/>
-      <c r="L227" s="19" t="inlineStr">
+      <c r="G228" s="20" t="n"/>
+      <c r="H228" s="20" t="n"/>
+      <c r="I228" s="20" t="n"/>
+      <c r="J228" s="20" t="n"/>
+      <c r="K228" s="20" t="n"/>
+      <c r="L228" s="19" t="inlineStr">
         <is>
           <t>26-0622-0208</t>
         </is>
       </c>
-      <c r="M227" s="21" t="inlineStr">
+      <c r="M228" s="21" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="n"/>
-      <c r="B228" s="2" t="n"/>
-      <c r="C228" s="2" t="n"/>
-      <c r="D228" s="2" t="n"/>
-      <c r="E228" s="2" t="n"/>
-      <c r="F228" s="2" t="n"/>
-      <c r="G228" s="2" t="n"/>
-      <c r="H228" s="2" t="n"/>
-      <c r="I228" s="2" t="n"/>
-      <c r="J228" s="2" t="n"/>
-      <c r="K228" s="2" t="n"/>
-      <c r="L228" s="2" t="n"/>
-      <c r="M228" s="22" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -10510,106 +10542,74 @@
       <c r="M229" s="22" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="inlineStr">
+      <c r="A230" s="2" t="n"/>
+      <c r="B230" s="2" t="n"/>
+      <c r="C230" s="2" t="n"/>
+      <c r="D230" s="2" t="n"/>
+      <c r="E230" s="2" t="n"/>
+      <c r="F230" s="2" t="n"/>
+      <c r="G230" s="2" t="n"/>
+      <c r="H230" s="2" t="n"/>
+      <c r="I230" s="2" t="n"/>
+      <c r="J230" s="2" t="n"/>
+      <c r="K230" s="2" t="n"/>
+      <c r="L230" s="2" t="n"/>
+      <c r="M230" s="22" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
         <is>
           <t>Toledo Dutch Door</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
+      <c r="B231" s="4" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C230" s="4" t="inlineStr">
+      <c r="C231" s="4" t="inlineStr">
         <is>
           <t>Gunmetal</t>
         </is>
       </c>
-      <c r="D230" s="4" t="inlineStr">
+      <c r="D231" s="4" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E230" s="4" t="inlineStr">
+      <c r="E231" s="4" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F230" s="5" t="inlineStr">
+      <c r="F231" s="5" t="inlineStr">
         <is>
           <t>TOL-36X80-GM-RI-RN</t>
         </is>
       </c>
-      <c r="G230" s="5" t="n">
+      <c r="G231" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H230" s="5" t="n">
+      <c r="H231" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I230" s="5" t="n">
+      <c r="I231" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J230" s="5" t="n">
+      <c r="J231" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K230" s="5" t="n">
+      <c r="K231" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L230" s="5" t="inlineStr">
-        <is>
-          <t>26-0728-0116</t>
-        </is>
-      </c>
-      <c r="M230" s="24" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="7" t="inlineStr">
-        <is>
-          <t>Toledo Dutch Door</t>
-        </is>
-      </c>
-      <c r="B231" s="8" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C231" s="8" t="inlineStr">
-        <is>
-          <t>Gunmetal</t>
-        </is>
-      </c>
-      <c r="D231" s="8" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E231" s="8" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F231" s="9" t="inlineStr">
-        <is>
-          <t>TOL-36X80-GM-RI-RN</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="n"/>
-      <c r="H231" s="2" t="n"/>
-      <c r="I231" s="2" t="n"/>
-      <c r="J231" s="2" t="n"/>
-      <c r="K231" s="2" t="n"/>
-      <c r="L231" s="9" t="inlineStr">
-        <is>
-          <t>26-0728-0117</t>
-        </is>
-      </c>
-      <c r="M231" s="11" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-002</t>
+      <c r="L231" s="5" t="inlineStr">
+        <is>
+          <t>26-0618-0161</t>
+        </is>
+      </c>
+      <c r="M231" s="24" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       <c r="K232" s="2" t="n"/>
       <c r="L232" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0161</t>
+          <t>26-0618-0162</t>
         </is>
       </c>
       <c r="M232" s="11" t="inlineStr">
@@ -10698,12 +10698,12 @@
       <c r="K233" s="2" t="n"/>
       <c r="L233" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0162</t>
+          <t>26-0707-0194</t>
         </is>
       </c>
       <c r="M233" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-004</t>
         </is>
       </c>
     </row>
@@ -10745,131 +10745,131 @@
       <c r="K234" s="2" t="n"/>
       <c r="L234" s="9" t="inlineStr">
         <is>
-          <t>26-0707-0194</t>
+          <t>26-0728-0116</t>
         </is>
       </c>
       <c r="M234" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="12" t="n"/>
-      <c r="B235" s="2" t="n"/>
-      <c r="C235" s="2" t="n"/>
-      <c r="D235" s="2" t="n"/>
-      <c r="E235" s="2" t="n"/>
-      <c r="F235" s="2" t="n"/>
+      <c r="A235" s="7" t="inlineStr">
+        <is>
+          <t>Toledo Dutch Door</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>Gunmetal</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E235" s="8" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>TOL-36X80-GM-RI-RN</t>
+        </is>
+      </c>
       <c r="G235" s="2" t="n"/>
       <c r="H235" s="2" t="n"/>
       <c r="I235" s="2" t="n"/>
       <c r="J235" s="2" t="n"/>
       <c r="K235" s="2" t="n"/>
-      <c r="L235" s="2" t="n"/>
-      <c r="M235" s="13" t="n"/>
+      <c r="L235" s="9" t="inlineStr">
+        <is>
+          <t>26-0728-0117</t>
+        </is>
+      </c>
+      <c r="M235" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-002</t>
+        </is>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="14" t="inlineStr">
+      <c r="A236" s="12" t="n"/>
+      <c r="B236" s="2" t="n"/>
+      <c r="C236" s="2" t="n"/>
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="n"/>
+      <c r="F236" s="2" t="n"/>
+      <c r="G236" s="2" t="n"/>
+      <c r="H236" s="2" t="n"/>
+      <c r="I236" s="2" t="n"/>
+      <c r="J236" s="2" t="n"/>
+      <c r="K236" s="2" t="n"/>
+      <c r="L236" s="2" t="n"/>
+      <c r="M236" s="13" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="14" t="inlineStr">
         <is>
           <t>Toledo Dutch Door</t>
         </is>
       </c>
-      <c r="B236" s="15" t="inlineStr">
+      <c r="B237" s="15" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C236" s="15" t="inlineStr">
+      <c r="C237" s="15" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D236" s="15" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E236" s="15" t="inlineStr">
+      <c r="D237" s="15" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E237" s="15" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F236" s="9" t="inlineStr">
+      <c r="F237" s="9" t="inlineStr">
         <is>
           <t>TOL-36X80-MB-LI-CLR</t>
         </is>
       </c>
-      <c r="G236" s="9" t="n">
+      <c r="G237" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H236" s="9" t="n">
+      <c r="H237" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I236" s="9" t="n">
+      <c r="I237" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="J236" s="9" t="n">
+      <c r="J237" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="K236" s="9" t="n">
+      <c r="K237" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L236" s="9" t="inlineStr">
-        <is>
-          <t>26-0728-0111</t>
-        </is>
-      </c>
-      <c r="M236" s="11" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="7" t="inlineStr">
-        <is>
-          <t>Toledo Dutch Door</t>
-        </is>
-      </c>
-      <c r="B237" s="8" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C237" s="8" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D237" s="8" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E237" s="8" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F237" s="9" t="inlineStr">
-        <is>
-          <t>TOL-36X80-MB-LI-CLR</t>
-        </is>
-      </c>
-      <c r="G237" s="2" t="n"/>
-      <c r="H237" s="2" t="n"/>
-      <c r="I237" s="2" t="n"/>
-      <c r="J237" s="2" t="n"/>
-      <c r="K237" s="2" t="n"/>
       <c r="L237" s="9" t="inlineStr">
         <is>
-          <t>26-0728-0112</t>
+          <t>26-0618-0163</t>
         </is>
       </c>
       <c r="M237" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -10911,12 +10911,12 @@
       <c r="K238" s="2" t="n"/>
       <c r="L238" s="9" t="inlineStr">
         <is>
-          <t>26-0728-0113</t>
+          <t>26-0618-0164</t>
         </is>
       </c>
       <c r="M238" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -10958,12 +10958,12 @@
       <c r="K239" s="2" t="n"/>
       <c r="L239" s="9" t="inlineStr">
         <is>
-          <t>26-0728-0114</t>
+          <t>26-0622-0218</t>
         </is>
       </c>
       <c r="M239" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       <c r="K240" s="2" t="n"/>
       <c r="L240" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0163</t>
+          <t>26-0707-0196</t>
         </is>
       </c>
       <c r="M240" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-004</t>
         </is>
       </c>
     </row>
@@ -11052,12 +11052,12 @@
       <c r="K241" s="2" t="n"/>
       <c r="L241" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0164</t>
+          <t>26-0728-0111</t>
         </is>
       </c>
       <c r="M241" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -11099,76 +11099,108 @@
       <c r="K242" s="2" t="n"/>
       <c r="L242" s="9" t="inlineStr">
         <is>
-          <t>26-0707-0196</t>
+          <t>26-0728-0112</t>
         </is>
       </c>
       <c r="M242" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="17" t="inlineStr">
+      <c r="A243" s="7" t="inlineStr">
         <is>
           <t>Toledo Dutch Door</t>
         </is>
       </c>
-      <c r="B243" s="18" t="inlineStr">
+      <c r="B243" s="8" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C243" s="18" t="inlineStr">
+      <c r="C243" s="8" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D243" s="18" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E243" s="18" t="inlineStr">
+      <c r="D243" s="8" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E243" s="8" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F243" s="19" t="inlineStr">
+      <c r="F243" s="9" t="inlineStr">
         <is>
           <t>TOL-36X80-MB-LI-CLR</t>
         </is>
       </c>
-      <c r="G243" s="20" t="n"/>
-      <c r="H243" s="20" t="n"/>
-      <c r="I243" s="20" t="n"/>
-      <c r="J243" s="20" t="n"/>
-      <c r="K243" s="20" t="n"/>
-      <c r="L243" s="19" t="inlineStr">
-        <is>
-          <t>26-0622-0218</t>
-        </is>
-      </c>
-      <c r="M243" s="21" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-005</t>
+      <c r="G243" s="2" t="n"/>
+      <c r="H243" s="2" t="n"/>
+      <c r="I243" s="2" t="n"/>
+      <c r="J243" s="2" t="n"/>
+      <c r="K243" s="2" t="n"/>
+      <c r="L243" s="9" t="inlineStr">
+        <is>
+          <t>26-0728-0113</t>
+        </is>
+      </c>
+      <c r="M243" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n"/>
-      <c r="B244" s="2" t="n"/>
-      <c r="C244" s="2" t="n"/>
-      <c r="D244" s="2" t="n"/>
-      <c r="E244" s="2" t="n"/>
-      <c r="F244" s="2" t="n"/>
-      <c r="G244" s="2" t="n"/>
-      <c r="H244" s="2" t="n"/>
-      <c r="I244" s="2" t="n"/>
-      <c r="J244" s="2" t="n"/>
-      <c r="K244" s="2" t="n"/>
-      <c r="L244" s="2" t="n"/>
-      <c r="M244" s="22" t="n"/>
+      <c r="A244" s="17" t="inlineStr">
+        <is>
+          <t>Toledo Dutch Door</t>
+        </is>
+      </c>
+      <c r="B244" s="18" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C244" s="18" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D244" s="18" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E244" s="18" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F244" s="19" t="inlineStr">
+        <is>
+          <t>TOL-36X80-MB-LI-CLR</t>
+        </is>
+      </c>
+      <c r="G244" s="20" t="n"/>
+      <c r="H244" s="20" t="n"/>
+      <c r="I244" s="20" t="n"/>
+      <c r="J244" s="20" t="n"/>
+      <c r="K244" s="20" t="n"/>
+      <c r="L244" s="19" t="inlineStr">
+        <is>
+          <t>26-0728-0114</t>
+        </is>
+      </c>
+      <c r="M244" s="21" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-002</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -11186,104 +11218,72 @@
       <c r="M245" s="22" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="inlineStr">
+      <c r="A246" s="2" t="n"/>
+      <c r="B246" s="2" t="n"/>
+      <c r="C246" s="2" t="n"/>
+      <c r="D246" s="2" t="n"/>
+      <c r="E246" s="2" t="n"/>
+      <c r="F246" s="2" t="n"/>
+      <c r="G246" s="2" t="n"/>
+      <c r="H246" s="2" t="n"/>
+      <c r="I246" s="2" t="n"/>
+      <c r="J246" s="2" t="n"/>
+      <c r="K246" s="2" t="n"/>
+      <c r="L246" s="2" t="n"/>
+      <c r="M246" s="22" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B246" s="4" t="inlineStr">
+      <c r="B247" s="4" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C246" s="4" t="inlineStr">
+      <c r="C247" s="4" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E246" s="4" t="inlineStr">
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F246" s="5" t="inlineStr">
+      <c r="F247" s="5" t="inlineStr">
         <is>
           <t>VAL-32X80-MB-LI-CLR</t>
         </is>
       </c>
-      <c r="G246" s="5" t="n">
+      <c r="G247" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H246" s="5" t="n">
+      <c r="H247" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I246" s="5" t="n">
+      <c r="I247" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J246" s="5" t="n">
+      <c r="J247" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="K246" s="5" t="n">
+      <c r="K247" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L246" s="5" t="inlineStr">
+      <c r="L247" s="5" t="inlineStr">
         <is>
           <t>24-0315-0001</t>
         </is>
       </c>
-      <c r="M246" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="7" t="inlineStr">
-        <is>
-          <t>Valencia Single Door</t>
-        </is>
-      </c>
-      <c r="B247" s="8" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C247" s="8" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D247" s="8" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E247" s="8" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F247" s="9" t="inlineStr">
-        <is>
-          <t>VAL-32X80-MB-LI-CLR</t>
-        </is>
-      </c>
-      <c r="G247" s="2" t="n"/>
-      <c r="H247" s="2" t="n"/>
-      <c r="I247" s="2" t="n"/>
-      <c r="J247" s="2" t="n"/>
-      <c r="K247" s="2" t="n"/>
-      <c r="L247" s="9" t="inlineStr">
-        <is>
-          <t>24-0315-0002</t>
-        </is>
-      </c>
-      <c r="M247" s="10" t="inlineStr">
+      <c r="M247" s="6" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -11327,7 +11327,7 @@
       <c r="K248" s="2" t="n"/>
       <c r="L248" s="9" t="inlineStr">
         <is>
-          <t>24-0315-0003</t>
+          <t>24-0315-0002</t>
         </is>
       </c>
       <c r="M248" s="10" t="inlineStr">
@@ -11374,7 +11374,7 @@
       <c r="K249" s="2" t="n"/>
       <c r="L249" s="9" t="inlineStr">
         <is>
-          <t>24-0315-0004</t>
+          <t>24-0315-0003</t>
         </is>
       </c>
       <c r="M249" s="10" t="inlineStr">
@@ -11421,7 +11421,7 @@
       <c r="K250" s="2" t="n"/>
       <c r="L250" s="9" t="inlineStr">
         <is>
-          <t>26-0502-0011</t>
+          <t>24-0315-0004</t>
         </is>
       </c>
       <c r="M250" s="10" t="inlineStr">
@@ -11468,7 +11468,7 @@
       <c r="K251" s="2" t="n"/>
       <c r="L251" s="9" t="inlineStr">
         <is>
-          <t>26-0502-0012</t>
+          <t>26-0502-0011</t>
         </is>
       </c>
       <c r="M251" s="10" t="inlineStr">
@@ -11515,12 +11515,12 @@
       <c r="K252" s="2" t="n"/>
       <c r="L252" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0165</t>
-        </is>
-      </c>
-      <c r="M252" s="11" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>26-0502-0012</t>
+        </is>
+      </c>
+      <c r="M252" s="10" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       <c r="K253" s="2" t="n"/>
       <c r="L253" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0166</t>
+          <t>26-0618-0165</t>
         </is>
       </c>
       <c r="M253" s="11" t="inlineStr">
@@ -11609,7 +11609,7 @@
       <c r="K254" s="2" t="n"/>
       <c r="L254" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0167</t>
+          <t>26-0618-0166</t>
         </is>
       </c>
       <c r="M254" s="11" t="inlineStr">
@@ -11656,12 +11656,12 @@
       <c r="K255" s="2" t="n"/>
       <c r="L255" s="9" t="inlineStr">
         <is>
-          <t>26-0707-0197</t>
+          <t>26-0618-0167</t>
         </is>
       </c>
       <c r="M255" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -11760,116 +11760,116 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="12" t="n"/>
-      <c r="B258" s="2" t="n"/>
-      <c r="C258" s="2" t="n"/>
-      <c r="D258" s="2" t="n"/>
-      <c r="E258" s="2" t="n"/>
-      <c r="F258" s="2" t="n"/>
+      <c r="A258" s="7" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B258" s="8" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C258" s="8" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D258" s="8" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E258" s="8" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F258" s="9" t="inlineStr">
+        <is>
+          <t>VAL-32X80-MB-LI-CLR</t>
+        </is>
+      </c>
       <c r="G258" s="2" t="n"/>
       <c r="H258" s="2" t="n"/>
       <c r="I258" s="2" t="n"/>
       <c r="J258" s="2" t="n"/>
       <c r="K258" s="2" t="n"/>
-      <c r="L258" s="2" t="n"/>
-      <c r="M258" s="13" t="n"/>
+      <c r="L258" s="9" t="inlineStr">
+        <is>
+          <t>26-0707-0197</t>
+        </is>
+      </c>
+      <c r="M258" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-004</t>
+        </is>
+      </c>
     </row>
     <row r="259">
-      <c r="A259" s="14" t="inlineStr">
+      <c r="A259" s="12" t="n"/>
+      <c r="B259" s="2" t="n"/>
+      <c r="C259" s="2" t="n"/>
+      <c r="D259" s="2" t="n"/>
+      <c r="E259" s="2" t="n"/>
+      <c r="F259" s="2" t="n"/>
+      <c r="G259" s="2" t="n"/>
+      <c r="H259" s="2" t="n"/>
+      <c r="I259" s="2" t="n"/>
+      <c r="J259" s="2" t="n"/>
+      <c r="K259" s="2" t="n"/>
+      <c r="L259" s="2" t="n"/>
+      <c r="M259" s="13" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="14" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B259" s="15" t="inlineStr">
+      <c r="B260" s="15" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C259" s="15" t="inlineStr">
+      <c r="C260" s="15" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D259" s="15" t="inlineStr">
+      <c r="D260" s="15" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E259" s="15" t="inlineStr">
+      <c r="E260" s="15" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F259" s="9" t="inlineStr">
+      <c r="F260" s="9" t="inlineStr">
         <is>
           <t>VAL-36X80-MB-RI-CLR</t>
         </is>
       </c>
-      <c r="G259" s="9" t="n">
+      <c r="G260" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="H259" s="9" t="n">
+      <c r="H260" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I259" s="9" t="n">
+      <c r="I260" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="J259" s="9" t="n">
+      <c r="J260" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="K259" s="9" t="n">
+      <c r="K260" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L259" s="9" t="inlineStr">
+      <c r="L260" s="9" t="inlineStr">
         <is>
           <t>24-0315-0005</t>
-        </is>
-      </c>
-      <c r="M259" s="10" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="7" t="inlineStr">
-        <is>
-          <t>Valencia Single Door</t>
-        </is>
-      </c>
-      <c r="B260" s="8" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C260" s="8" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D260" s="8" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E260" s="8" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F260" s="9" t="inlineStr">
-        <is>
-          <t>VAL-36X80-MB-RI-CLR</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="n"/>
-      <c r="H260" s="2" t="n"/>
-      <c r="I260" s="2" t="n"/>
-      <c r="J260" s="2" t="n"/>
-      <c r="K260" s="2" t="n"/>
-      <c r="L260" s="9" t="inlineStr">
-        <is>
-          <t>24-0315-0006</t>
         </is>
       </c>
       <c r="M260" s="10" t="inlineStr">
@@ -11916,7 +11916,7 @@
       <c r="K261" s="2" t="n"/>
       <c r="L261" s="9" t="inlineStr">
         <is>
-          <t>24-0315-0007</t>
+          <t>24-0315-0006</t>
         </is>
       </c>
       <c r="M261" s="10" t="inlineStr">
@@ -11963,7 +11963,7 @@
       <c r="K262" s="2" t="n"/>
       <c r="L262" s="9" t="inlineStr">
         <is>
-          <t>24-0315-0008</t>
+          <t>24-0315-0007</t>
         </is>
       </c>
       <c r="M262" s="10" t="inlineStr">
@@ -12010,7 +12010,7 @@
       <c r="K263" s="2" t="n"/>
       <c r="L263" s="9" t="inlineStr">
         <is>
-          <t>24-0315-0009</t>
+          <t>24-0315-0008</t>
         </is>
       </c>
       <c r="M263" s="10" t="inlineStr">
@@ -12057,7 +12057,7 @@
       <c r="K264" s="2" t="n"/>
       <c r="L264" s="9" t="inlineStr">
         <is>
-          <t>24-0315-0010</t>
+          <t>24-0315-0009</t>
         </is>
       </c>
       <c r="M264" s="10" t="inlineStr">
@@ -12104,7 +12104,7 @@
       <c r="K265" s="2" t="n"/>
       <c r="L265" s="9" t="inlineStr">
         <is>
-          <t>24-0315-0011</t>
+          <t>24-0315-0010</t>
         </is>
       </c>
       <c r="M265" s="10" t="inlineStr">
@@ -12151,7 +12151,7 @@
       <c r="K266" s="2" t="n"/>
       <c r="L266" s="9" t="inlineStr">
         <is>
-          <t>26-0515-0015</t>
+          <t>24-0315-0011</t>
         </is>
       </c>
       <c r="M266" s="10" t="inlineStr">
@@ -12198,7 +12198,7 @@
       <c r="K267" s="2" t="n"/>
       <c r="L267" s="9" t="inlineStr">
         <is>
-          <t>26-0515-0016</t>
+          <t>26-0515-0015</t>
         </is>
       </c>
       <c r="M267" s="10" t="inlineStr">
@@ -12245,7 +12245,7 @@
       <c r="K268" s="2" t="n"/>
       <c r="L268" s="9" t="inlineStr">
         <is>
-          <t>26-0515-0017</t>
+          <t>26-0515-0016</t>
         </is>
       </c>
       <c r="M268" s="10" t="inlineStr">
@@ -12292,7 +12292,7 @@
       <c r="K269" s="2" t="n"/>
       <c r="L269" s="9" t="inlineStr">
         <is>
-          <t>26-0515-0018</t>
+          <t>26-0515-0017</t>
         </is>
       </c>
       <c r="M269" s="10" t="inlineStr">
@@ -12339,7 +12339,7 @@
       <c r="K270" s="2" t="n"/>
       <c r="L270" s="9" t="inlineStr">
         <is>
-          <t>26-0515-0019</t>
+          <t>26-0515-0018</t>
         </is>
       </c>
       <c r="M270" s="10" t="inlineStr">
@@ -12386,7 +12386,7 @@
       <c r="K271" s="2" t="n"/>
       <c r="L271" s="9" t="inlineStr">
         <is>
-          <t>26-0515-0020</t>
+          <t>26-0515-0019</t>
         </is>
       </c>
       <c r="M271" s="10" t="inlineStr">
@@ -12433,12 +12433,12 @@
       <c r="K272" s="2" t="n"/>
       <c r="L272" s="9" t="inlineStr">
         <is>
-          <t>26-0702-0078</t>
-        </is>
-      </c>
-      <c r="M272" s="11" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>26-0515-0020</t>
+        </is>
+      </c>
+      <c r="M272" s="10" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -12480,12 +12480,12 @@
       <c r="K273" s="2" t="n"/>
       <c r="L273" s="9" t="inlineStr">
         <is>
-          <t>26-0702-0079</t>
+          <t>26-0618-0168</t>
         </is>
       </c>
       <c r="M273" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -12527,12 +12527,12 @@
       <c r="K274" s="2" t="n"/>
       <c r="L274" s="9" t="inlineStr">
         <is>
-          <t>26-0702-0080</t>
+          <t>26-0618-0169</t>
         </is>
       </c>
       <c r="M274" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-002</t>
+          <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
@@ -12574,12 +12574,12 @@
       <c r="K275" s="2" t="n"/>
       <c r="L275" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0168</t>
+          <t>26-0622-0202</t>
         </is>
       </c>
       <c r="M275" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
@@ -12621,12 +12621,12 @@
       <c r="K276" s="2" t="n"/>
       <c r="L276" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0169</t>
+          <t>26-0622-0203</t>
         </is>
       </c>
       <c r="M276" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>Pre-Sale - CNT-005</t>
         </is>
       </c>
     </row>
@@ -12668,12 +12668,12 @@
       <c r="K277" s="2" t="n"/>
       <c r="L277" s="9" t="inlineStr">
         <is>
-          <t>26-0707-0199</t>
+          <t>26-0702-0078</t>
         </is>
       </c>
       <c r="M277" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-004</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -12715,12 +12715,12 @@
       <c r="K278" s="2" t="n"/>
       <c r="L278" s="9" t="inlineStr">
         <is>
-          <t>26-0622-0202</t>
+          <t>26-0702-0079</t>
         </is>
       </c>
       <c r="M278" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-005</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
@@ -12762,126 +12762,126 @@
       <c r="K279" s="2" t="n"/>
       <c r="L279" s="9" t="inlineStr">
         <is>
-          <t>26-0622-0203</t>
+          <t>26-0702-0080</t>
         </is>
       </c>
       <c r="M279" s="11" t="inlineStr">
         <is>
-          <t>Pre-Sale - CNT-005</t>
+          <t>Pre-Sale - CNT-002</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="12" t="n"/>
-      <c r="B280" s="2" t="n"/>
-      <c r="C280" s="2" t="n"/>
-      <c r="D280" s="2" t="n"/>
-      <c r="E280" s="2" t="n"/>
-      <c r="F280" s="2" t="n"/>
+      <c r="A280" s="7" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B280" s="8" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D280" s="8" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E280" s="8" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F280" s="9" t="inlineStr">
+        <is>
+          <t>VAL-36X80-MB-RI-CLR</t>
+        </is>
+      </c>
       <c r="G280" s="2" t="n"/>
       <c r="H280" s="2" t="n"/>
       <c r="I280" s="2" t="n"/>
       <c r="J280" s="2" t="n"/>
       <c r="K280" s="2" t="n"/>
-      <c r="L280" s="2" t="n"/>
-      <c r="M280" s="13" t="n"/>
+      <c r="L280" s="9" t="inlineStr">
+        <is>
+          <t>26-0707-0199</t>
+        </is>
+      </c>
+      <c r="M280" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-004</t>
+        </is>
+      </c>
     </row>
     <row r="281">
-      <c r="A281" s="14" t="inlineStr">
+      <c r="A281" s="12" t="n"/>
+      <c r="B281" s="2" t="n"/>
+      <c r="C281" s="2" t="n"/>
+      <c r="D281" s="2" t="n"/>
+      <c r="E281" s="2" t="n"/>
+      <c r="F281" s="2" t="n"/>
+      <c r="G281" s="2" t="n"/>
+      <c r="H281" s="2" t="n"/>
+      <c r="I281" s="2" t="n"/>
+      <c r="J281" s="2" t="n"/>
+      <c r="K281" s="2" t="n"/>
+      <c r="L281" s="2" t="n"/>
+      <c r="M281" s="13" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="14" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B281" s="15" t="inlineStr">
+      <c r="B282" s="15" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C281" s="15" t="inlineStr">
+      <c r="C282" s="15" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D281" s="15" t="inlineStr">
+      <c r="D282" s="15" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E281" s="15" t="inlineStr">
+      <c r="E282" s="15" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F281" s="9" t="inlineStr">
+      <c r="F282" s="9" t="inlineStr">
         <is>
           <t>VAL-36X96-ORB-RO-FRS</t>
         </is>
       </c>
-      <c r="G281" s="9" t="n">
+      <c r="G282" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H281" s="9" t="n">
+      <c r="H282" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I281" s="9" t="n">
+      <c r="I282" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J281" s="9" t="n">
+      <c r="J282" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="K281" s="9" t="n">
+      <c r="K282" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L281" s="9" t="inlineStr">
+      <c r="L282" s="9" t="inlineStr">
         <is>
           <t>24-0721-0012</t>
-        </is>
-      </c>
-      <c r="M281" s="10" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="7" t="inlineStr">
-        <is>
-          <t>Valencia Single Door</t>
-        </is>
-      </c>
-      <c r="B282" s="8" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C282" s="8" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D282" s="8" t="inlineStr">
-        <is>
-          <t>Right Outswing</t>
-        </is>
-      </c>
-      <c r="E282" s="8" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F282" s="9" t="inlineStr">
-        <is>
-          <t>VAL-36X96-ORB-RO-FRS</t>
-        </is>
-      </c>
-      <c r="G282" s="2" t="n"/>
-      <c r="H282" s="2" t="n"/>
-      <c r="I282" s="2" t="n"/>
-      <c r="J282" s="2" t="n"/>
-      <c r="K282" s="2" t="n"/>
-      <c r="L282" s="9" t="inlineStr">
-        <is>
-          <t>24-0721-0013</t>
         </is>
       </c>
       <c r="M282" s="10" t="inlineStr">
@@ -12928,12 +12928,12 @@
       <c r="K283" s="2" t="n"/>
       <c r="L283" s="9" t="inlineStr">
         <is>
-          <t>26-0618-0170</t>
-        </is>
-      </c>
-      <c r="M283" s="11" t="inlineStr">
-        <is>
-          <t>Pre-Sale - CNT-003</t>
+          <t>24-0721-0013</t>
+        </is>
+      </c>
+      <c r="M283" s="10" t="inlineStr">
+        <is>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -12975,57 +12975,104 @@
       <c r="K284" s="2" t="n"/>
       <c r="L284" s="9" t="inlineStr">
         <is>
+          <t>26-0618-0170</t>
+        </is>
+      </c>
+      <c r="M284" s="11" t="inlineStr">
+        <is>
+          <t>Pre-Sale - CNT-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="7" t="inlineStr">
+        <is>
+          <t>Valencia Single Door</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>Oil-Rubbed Bronze</t>
+        </is>
+      </c>
+      <c r="D285" s="8" t="inlineStr">
+        <is>
+          <t>Right Outswing</t>
+        </is>
+      </c>
+      <c r="E285" s="8" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F285" s="9" t="inlineStr">
+        <is>
+          <t>VAL-36X96-ORB-RO-FRS</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="n"/>
+      <c r="H285" s="2" t="n"/>
+      <c r="I285" s="2" t="n"/>
+      <c r="J285" s="2" t="n"/>
+      <c r="K285" s="2" t="n"/>
+      <c r="L285" s="9" t="inlineStr">
+        <is>
           <t>26-0618-0171</t>
         </is>
       </c>
-      <c r="M284" s="11" t="inlineStr">
+      <c r="M285" s="11" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-003</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="17" t="inlineStr">
+    <row r="286">
+      <c r="A286" s="17" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B285" s="18" t="inlineStr">
+      <c r="B286" s="18" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C285" s="18" t="inlineStr">
+      <c r="C286" s="18" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D285" s="18" t="inlineStr">
+      <c r="D286" s="18" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E285" s="18" t="inlineStr">
+      <c r="E286" s="18" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F285" s="19" t="inlineStr">
+      <c r="F286" s="19" t="inlineStr">
         <is>
           <t>VAL-36X96-ORB-RO-FRS</t>
         </is>
       </c>
-      <c r="G285" s="20" t="n"/>
-      <c r="H285" s="20" t="n"/>
-      <c r="I285" s="20" t="n"/>
-      <c r="J285" s="20" t="n"/>
-      <c r="K285" s="20" t="n"/>
-      <c r="L285" s="19" t="inlineStr">
+      <c r="G286" s="20" t="n"/>
+      <c r="H286" s="20" t="n"/>
+      <c r="I286" s="20" t="n"/>
+      <c r="J286" s="20" t="n"/>
+      <c r="K286" s="20" t="n"/>
+      <c r="L286" s="19" t="inlineStr">
         <is>
           <t>26-0707-0200</t>
         </is>
       </c>
-      <c r="M285" s="21" t="inlineStr">
+      <c r="M286" s="21" t="inlineStr">
         <is>
           <t>Pre-Sale - CNT-004</t>
         </is>
@@ -13042,7 +13089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13744,27 +13791,27 @@
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>ORD-00006</t>
+          <t>ORD-00007</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Lisa Chen</t>
+          <t>Marcus Williams</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>Malaga Single Door</t>
+          <t>Cordova Sliding Window</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>48" x 36"</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
@@ -13774,27 +13821,27 @@
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>MAL-36X80-GM-LI-NON</t>
+          <t>COR-48X36-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
-          <t>26-0709-0084</t>
+          <t>26-0618-0139</t>
         </is>
       </c>
       <c r="J12" s="26" t="inlineStr">
         <is>
-          <t>CNT-002</t>
+          <t>CNT-003</t>
         </is>
       </c>
       <c r="K12" s="26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="L12" s="26" t="inlineStr">
@@ -13806,17 +13853,17 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>ORD-00006</t>
+          <t>ORD-00008</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Lisa Chen</t>
+          <t>Stephanie Davis</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Malaga Single Door</t>
+          <t>Marbella French Door</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
@@ -13826,37 +13873,37 @@
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Frosted</t>
         </is>
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>MAL-36X80-GM-LI-NON</t>
+          <t>MAR-36X80-BN-RI-FRS</t>
         </is>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
-          <t>26-0709-0085</t>
+          <t>26-0622-0228</t>
         </is>
       </c>
       <c r="J13" s="26" t="inlineStr">
         <is>
-          <t>CNT-002</t>
+          <t>CNT-005</t>
         </is>
       </c>
       <c r="K13" s="26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="L13" s="26" t="inlineStr">
@@ -13868,22 +13915,22 @@
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>ORD-00007</t>
+          <t>ORD-00009</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Marcus Williams</t>
+          <t>Ryan Thompson</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>Cordova Sliding Window</t>
+          <t>Granada Bi-fold Door</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>48" x 36"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -13893,7 +13940,7 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
@@ -13903,22 +13950,22 @@
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
-          <t>COR-48X36-MB-LI-CLR</t>
+          <t>GRN-36X80-MB-RI-CLR</t>
         </is>
       </c>
       <c r="I14" s="26" t="inlineStr">
         <is>
-          <t>26-0618-0139</t>
+          <t>26-0707-0180</t>
         </is>
       </c>
       <c r="J14" s="26" t="inlineStr">
         <is>
-          <t>CNT-003</t>
+          <t>CNT-004</t>
         </is>
       </c>
       <c r="K14" s="26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="L14" s="26" t="inlineStr">
@@ -13930,57 +13977,57 @@
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>ORD-00008</t>
+          <t>ORD-00010</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>Stephanie Davis</t>
+          <t>Amanda Garcia</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Marbella French Door</t>
+          <t>Cadiz Pivot Door</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>42" x 84"</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>MAR-36X80-BN-RI-FRS</t>
+          <t>CAD-42X84-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
-          <t>26-0622-0228</t>
+          <t>26-0714-0089</t>
         </is>
       </c>
       <c r="J15" s="26" t="inlineStr">
         <is>
-          <t>CNT-005</t>
+          <t>CNT-002</t>
         </is>
       </c>
       <c r="K15" s="26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="L15" s="26" t="inlineStr">
@@ -13992,12 +14039,12 @@
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>ORD-00009</t>
+          <t>ORD-00011</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Ryan Thompson</t>
+          <t>Daniel Lee</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
@@ -14032,17 +14079,17 @@
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
-          <t>26-0707-0180</t>
+          <t>26-0618-0141</t>
         </is>
       </c>
       <c r="J16" s="26" t="inlineStr">
         <is>
-          <t>CNT-004</t>
+          <t>CNT-003</t>
         </is>
       </c>
       <c r="K16" s="26" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="L16" s="26" t="inlineStr">
@@ -14054,22 +14101,22 @@
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>ORD-00010</t>
+          <t>ORD-00013</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>Amanda Garcia</t>
+          <t>Carlos Mendez</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>Cadiz Pivot Door</t>
+          <t>Toledo Dutch Door</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>42" x 84"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -14089,22 +14136,22 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>CAD-42X84-MB-LI-CLR</t>
+          <t>TOL-36X80-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
-          <t>26-0714-0089</t>
+          <t>26-0707-0195</t>
         </is>
       </c>
       <c r="J17" s="26" t="inlineStr">
         <is>
-          <t>CNT-002</t>
+          <t>CNT-004</t>
         </is>
       </c>
       <c r="K17" s="26" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="L17" s="26" t="inlineStr">
@@ -14116,22 +14163,22 @@
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>ORD-00011</t>
+          <t>ORD-00014</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>Daniel Lee</t>
+          <t>Hannah Brown</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>Granada Bi-fold Door</t>
+          <t>Altea Double Door</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>72" x 80"</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -14141,7 +14188,7 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
@@ -14151,22 +14198,22 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>GRN-36X80-MB-RI-CLR</t>
+          <t>ALT-72X80-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I18" s="26" t="inlineStr">
         <is>
-          <t>26-0618-0141</t>
+          <t>26-0702-0081</t>
         </is>
       </c>
       <c r="J18" s="26" t="inlineStr">
         <is>
-          <t>CNT-003</t>
+          <t>CNT-002</t>
         </is>
       </c>
       <c r="K18" s="26" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="L18" s="26" t="inlineStr">
@@ -14178,57 +14225,57 @@
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>ORD-00012</t>
+          <t>ORD-00015</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>Rachel Kim</t>
+          <t>Tyler Johnson</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Segovia Barn Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>48" x 84"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>SEG-48X84-MB-RI-CLR</t>
+          <t>MAL-32X80-BN-LI-NON</t>
         </is>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
-          <t>26-0622-0237</t>
+          <t>26-0618-0147</t>
         </is>
       </c>
       <c r="J19" s="26" t="inlineStr">
         <is>
-          <t>CNT-005</t>
+          <t>CNT-003</t>
         </is>
       </c>
       <c r="K19" s="26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="L19" s="26" t="inlineStr">
@@ -14240,22 +14287,22 @@
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>ORD-00012</t>
+          <t>ORD-00016</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Rachel Kim</t>
+          <t>Ashley Martinez</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>Segovia Barn Door</t>
+          <t>Ronda Louvered Door</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>48" x 84"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
@@ -14265,22 +14312,22 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>SEG-48X84-MB-RI-CLR</t>
+          <t>RON-36X80-MB-LI-NON</t>
         </is>
       </c>
       <c r="I20" s="26" t="inlineStr">
         <is>
-          <t>26-0622-0238</t>
+          <t>26-0622-0221</t>
         </is>
       </c>
       <c r="J20" s="26" t="inlineStr">
@@ -14290,7 +14337,7 @@
       </c>
       <c r="K20" s="26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="L20" s="26" t="inlineStr">
@@ -14302,22 +14349,22 @@
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>ORD-00013</t>
+          <t>ORD-00017</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>Carlos Mendez</t>
+          <t>Derek Wilson</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>Toledo Dutch Door</t>
+          <t>Altea Double Door</t>
         </is>
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>72" x 80"</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
@@ -14337,12 +14384,12 @@
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>TOL-36X80-MB-LI-CLR</t>
+          <t>ALT-72X80-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I21" s="26" t="inlineStr">
         <is>
-          <t>26-0707-0195</t>
+          <t>26-0707-0173</t>
         </is>
       </c>
       <c r="J21" s="26" t="inlineStr">
@@ -14352,7 +14399,7 @@
       </c>
       <c r="K21" s="26" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L21" s="26" t="inlineStr">
@@ -14364,12 +14411,12 @@
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>ORD-00014</t>
+          <t>ORD-00017</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>Hannah Brown</t>
+          <t>Derek Wilson</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
@@ -14404,17 +14451,17 @@
       </c>
       <c r="I22" s="26" t="inlineStr">
         <is>
-          <t>26-0702-0081</t>
+          <t>26-0707-0174</t>
         </is>
       </c>
       <c r="J22" s="26" t="inlineStr">
         <is>
-          <t>CNT-002</t>
+          <t>CNT-004</t>
         </is>
       </c>
       <c r="K22" s="26" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="L22" s="26" t="inlineStr">
@@ -14426,27 +14473,27 @@
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>ORD-00015</t>
+          <t>ORD-00018</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>Tyler Johnson</t>
+          <t>Nicole Baker</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Malaga Single Door</t>
+          <t>Ronda Louvered Door</t>
         </is>
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -14461,22 +14508,22 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>MAL-32X80-BN-LI-NON</t>
+          <t>RON-36X80-MB-LI-NON</t>
         </is>
       </c>
       <c r="I23" s="26" t="inlineStr">
         <is>
-          <t>26-0618-0147</t>
+          <t>26-0721-0104</t>
         </is>
       </c>
       <c r="J23" s="26" t="inlineStr">
         <is>
-          <t>CNT-003</t>
+          <t>CNT-002</t>
         </is>
       </c>
       <c r="K23" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="L23" s="26" t="inlineStr">
@@ -14488,22 +14535,22 @@
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>ORD-00016</t>
+          <t>ORD-00019</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Ashley Martinez</t>
+          <t>Justin Nguyen</t>
         </is>
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>Ronda Louvered Door</t>
+          <t>Cadiz Pivot Door</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>42" x 84"</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
@@ -14518,27 +14565,27 @@
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>RON-36X80-MB-LI-NON</t>
+          <t>CAD-42X84-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
-          <t>26-0622-0221</t>
+          <t>26-0618-0129</t>
         </is>
       </c>
       <c r="J24" s="26" t="inlineStr">
         <is>
-          <t>CNT-005</t>
+          <t>CNT-003</t>
         </is>
       </c>
       <c r="K24" s="26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L24" s="26" t="inlineStr">
@@ -14550,22 +14597,22 @@
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>ORD-00017</t>
+          <t>ORD-00019</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Derek Wilson</t>
+          <t>Justin Nguyen</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Altea Double Door</t>
+          <t>Cadiz Pivot Door</t>
         </is>
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>72" x 80"</t>
+          <t>42" x 84"</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
@@ -14585,22 +14632,22 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>ALT-72X80-MB-LI-CLR</t>
+          <t>CAD-42X84-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">
         <is>
-          <t>26-0707-0173</t>
+          <t>26-0618-0130</t>
         </is>
       </c>
       <c r="J25" s="26" t="inlineStr">
         <is>
-          <t>CNT-004</t>
+          <t>CNT-003</t>
         </is>
       </c>
       <c r="K25" s="26" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L25" s="26" t="inlineStr">
@@ -14612,22 +14659,22 @@
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>ORD-00017</t>
+          <t>ORD-00020</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>Derek Wilson</t>
+          <t>Megan Foster</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>Altea Double Door</t>
+          <t>Granada Bi-fold Door</t>
         </is>
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>72" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E26" s="25" t="inlineStr">
@@ -14637,7 +14684,7 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
@@ -14647,22 +14694,22 @@
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>ALT-72X80-MB-LI-CLR</t>
+          <t>GRN-36X80-MB-RI-CLR</t>
         </is>
       </c>
       <c r="I26" s="26" t="inlineStr">
         <is>
-          <t>26-0707-0174</t>
+          <t>26-0622-0213</t>
         </is>
       </c>
       <c r="J26" s="26" t="inlineStr">
         <is>
-          <t>CNT-004</t>
+          <t>CNT-005</t>
         </is>
       </c>
       <c r="K26" s="26" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L26" s="26" t="inlineStr">
@@ -14674,17 +14721,17 @@
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>ORD-00018</t>
+          <t>ORD-00020</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>Nicole Baker</t>
+          <t>Megan Foster</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>Ronda Louvered Door</t>
+          <t>Granada Bi-fold Door</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr">
@@ -14699,32 +14746,32 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>RON-36X80-MB-LI-NON</t>
+          <t>GRN-36X80-MB-RI-CLR</t>
         </is>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
-          <t>26-0721-0104</t>
+          <t>26-0622-0214</t>
         </is>
       </c>
       <c r="J27" s="26" t="inlineStr">
         <is>
-          <t>CNT-002</t>
+          <t>CNT-005</t>
         </is>
       </c>
       <c r="K27" s="26" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="L27" s="26" t="inlineStr">
@@ -14736,22 +14783,22 @@
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>ORD-00019</t>
+          <t>ORD-00021</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Justin Nguyen</t>
+          <t>Connor Hayes</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>Cadiz Pivot Door</t>
+          <t>Ronda Louvered Door</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>42" x 84"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E28" s="25" t="inlineStr">
@@ -14766,27 +14813,27 @@
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>CAD-42X84-MB-LI-CLR</t>
+          <t>RON-36X80-MB-LI-NON</t>
         </is>
       </c>
       <c r="I28" s="26" t="inlineStr">
         <is>
-          <t>26-0618-0129</t>
+          <t>26-0707-0188</t>
         </is>
       </c>
       <c r="J28" s="26" t="inlineStr">
         <is>
-          <t>CNT-003</t>
+          <t>CNT-004</t>
         </is>
       </c>
       <c r="K28" s="26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="L28" s="26" t="inlineStr">
@@ -14798,57 +14845,57 @@
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>ORD-00019</t>
+          <t>ORD-00022</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>Justin Nguyen</t>
+          <t>Lauren Phillips</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>Cadiz Pivot Door</t>
+          <t>Toledo Dutch Door</t>
         </is>
       </c>
       <c r="D29" s="25" t="inlineStr">
         <is>
-          <t>42" x 84"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E29" s="25" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="H29" s="26" t="inlineStr">
         <is>
-          <t>CAD-42X84-MB-LI-CLR</t>
+          <t>TOL-36X80-GM-RI-RN</t>
         </is>
       </c>
       <c r="I29" s="26" t="inlineStr">
         <is>
-          <t>26-0618-0130</t>
+          <t>26-0728-0115</t>
         </is>
       </c>
       <c r="J29" s="26" t="inlineStr">
         <is>
-          <t>CNT-003</t>
+          <t>CNT-002</t>
         </is>
       </c>
       <c r="K29" s="26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="L29" s="26" t="inlineStr">
@@ -14860,27 +14907,27 @@
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>ORD-00020</t>
+          <t>ORD-00023</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Megan Foster</t>
+          <t>Ethan Cruz</t>
         </is>
       </c>
       <c r="C30" s="25" t="inlineStr">
         <is>
-          <t>Granada Bi-fold Door</t>
+          <t>Ronda Louvered Door</t>
         </is>
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="E30" s="25" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -14890,27 +14937,27 @@
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H30" s="26" t="inlineStr">
         <is>
-          <t>GRN-36X80-MB-RI-CLR</t>
+          <t>RON-32X80-SW-RI-NON</t>
         </is>
       </c>
       <c r="I30" s="26" t="inlineStr">
         <is>
-          <t>26-0622-0213</t>
+          <t>26-0618-0151</t>
         </is>
       </c>
       <c r="J30" s="26" t="inlineStr">
         <is>
-          <t>CNT-005</t>
+          <t>CNT-003</t>
         </is>
       </c>
       <c r="K30" s="26" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="L30" s="26" t="inlineStr">
@@ -14922,22 +14969,22 @@
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>ORD-00020</t>
+          <t>ORD-00024</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Megan Foster</t>
+          <t>Brittany Sanders</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Granada Bi-fold Door</t>
+          <t>Cadiz Pivot Door</t>
         </is>
       </c>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>42" x 84"</t>
         </is>
       </c>
       <c r="E31" s="25" t="inlineStr">
@@ -14947,7 +14994,7 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
@@ -14957,12 +15004,12 @@
       </c>
       <c r="H31" s="26" t="inlineStr">
         <is>
-          <t>GRN-36X80-MB-RI-CLR</t>
+          <t>CAD-42X84-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I31" s="26" t="inlineStr">
         <is>
-          <t>26-0622-0214</t>
+          <t>26-0622-0219</t>
         </is>
       </c>
       <c r="J31" s="26" t="inlineStr">
@@ -14972,7 +15019,7 @@
       </c>
       <c r="K31" s="26" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L31" s="26" t="inlineStr">
@@ -14984,22 +15031,22 @@
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>ORD-00021</t>
+          <t>ORD-00024</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>Connor Hayes</t>
+          <t>Brittany Sanders</t>
         </is>
       </c>
       <c r="C32" s="25" t="inlineStr">
         <is>
-          <t>Ronda Louvered Door</t>
+          <t>Cadiz Pivot Door</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>42" x 84"</t>
         </is>
       </c>
       <c r="E32" s="25" t="inlineStr">
@@ -15014,27 +15061,27 @@
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H32" s="26" t="inlineStr">
         <is>
-          <t>RON-36X80-MB-LI-NON</t>
+          <t>CAD-42X84-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I32" s="26" t="inlineStr">
         <is>
-          <t>26-0707-0188</t>
+          <t>26-0622-0220</t>
         </is>
       </c>
       <c r="J32" s="26" t="inlineStr">
         <is>
-          <t>CNT-004</t>
+          <t>CNT-005</t>
         </is>
       </c>
       <c r="K32" s="26" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L32" s="26" t="inlineStr">
@@ -15046,57 +15093,57 @@
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>ORD-00022</t>
+          <t>ORD-00025</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Lauren Phillips</t>
+          <t>Jacob Reed</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>Toledo Dutch Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>72" x 80"</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Matte White</t>
         </is>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Frosted</t>
         </is>
       </c>
       <c r="H33" s="26" t="inlineStr">
         <is>
-          <t>TOL-36X80-GM-RI-RN</t>
+          <t>SEV-72X80-MW-LI-FRS</t>
         </is>
       </c>
       <c r="I33" s="26" t="inlineStr">
         <is>
-          <t>26-0728-0115</t>
+          <t>26-0707-0192</t>
         </is>
       </c>
       <c r="J33" s="26" t="inlineStr">
         <is>
-          <t>CNT-002</t>
+          <t>CNT-004</t>
         </is>
       </c>
       <c r="K33" s="26" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L33" s="26" t="inlineStr">
@@ -15108,57 +15155,57 @@
     <row r="34">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>ORD-00023</t>
+          <t>ORD-00025</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Ethan Cruz</t>
+          <t>Jacob Reed</t>
         </is>
       </c>
       <c r="C34" s="25" t="inlineStr">
         <is>
-          <t>Ronda Louvered Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>72" x 80"</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Matte White</t>
         </is>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Frosted</t>
         </is>
       </c>
       <c r="H34" s="26" t="inlineStr">
         <is>
-          <t>RON-32X80-SW-RI-NON</t>
+          <t>SEV-72X80-MW-LI-FRS</t>
         </is>
       </c>
       <c r="I34" s="26" t="inlineStr">
         <is>
-          <t>26-0618-0151</t>
+          <t>26-0707-0193</t>
         </is>
       </c>
       <c r="J34" s="26" t="inlineStr">
         <is>
-          <t>CNT-003</t>
+          <t>CNT-004</t>
         </is>
       </c>
       <c r="K34" s="26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L34" s="26" t="inlineStr">
@@ -15170,12 +15217,12 @@
     <row r="35">
       <c r="A35" s="25" t="inlineStr">
         <is>
-          <t>ORD-00024</t>
+          <t>ORD-00026</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>Brittany Sanders</t>
+          <t>Olivia Bell</t>
         </is>
       </c>
       <c r="C35" s="25" t="inlineStr">
@@ -15185,12 +15232,12 @@
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>42" x 84"</t>
+          <t>48" x 84"</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="F35" s="25" t="inlineStr">
@@ -15200,27 +15247,27 @@
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Frosted</t>
         </is>
       </c>
       <c r="H35" s="26" t="inlineStr">
         <is>
-          <t>CAD-42X84-MB-LI-CLR</t>
+          <t>CAD-48X84-BN-LI-FRS</t>
         </is>
       </c>
       <c r="I35" s="26" t="inlineStr">
         <is>
-          <t>26-0622-0219</t>
+          <t>26-0714-0095</t>
         </is>
       </c>
       <c r="J35" s="26" t="inlineStr">
         <is>
-          <t>CNT-005</t>
+          <t>CNT-002</t>
         </is>
       </c>
       <c r="K35" s="26" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L35" s="26" t="inlineStr">
@@ -15232,12 +15279,12 @@
     <row r="36">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>ORD-00024</t>
+          <t>ORD-00026</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>Brittany Sanders</t>
+          <t>Olivia Bell</t>
         </is>
       </c>
       <c r="C36" s="25" t="inlineStr">
@@ -15247,12 +15294,12 @@
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>42" x 84"</t>
+          <t>48" x 84"</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="F36" s="25" t="inlineStr">
@@ -15262,27 +15309,27 @@
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Frosted</t>
         </is>
       </c>
       <c r="H36" s="26" t="inlineStr">
         <is>
-          <t>CAD-42X84-MB-LI-CLR</t>
+          <t>CAD-48X84-BN-LI-FRS</t>
         </is>
       </c>
       <c r="I36" s="26" t="inlineStr">
         <is>
-          <t>26-0622-0220</t>
+          <t>26-0714-0096</t>
         </is>
       </c>
       <c r="J36" s="26" t="inlineStr">
         <is>
-          <t>CNT-005</t>
+          <t>CNT-002</t>
         </is>
       </c>
       <c r="K36" s="26" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L36" s="26" t="inlineStr">
@@ -15294,12 +15341,12 @@
     <row r="37">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>ORD-00025</t>
+          <t>ORD-00040</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>Jacob Reed</t>
+          <t>Nathan Castillo</t>
         </is>
       </c>
       <c r="C37" s="25" t="inlineStr">
@@ -15309,42 +15356,42 @@
       </c>
       <c r="D37" s="25" t="inlineStr">
         <is>
-          <t>72" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
         <is>
-          <t>Matte White</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="H37" s="26" t="inlineStr">
         <is>
-          <t>SEV-72X80-MW-LI-FRS</t>
+          <t>SEV-32X80-BN-RI-RN</t>
         </is>
       </c>
       <c r="I37" s="26" t="inlineStr">
         <is>
-          <t>26-0707-0192</t>
+          <t>26-0618-0155</t>
         </is>
       </c>
       <c r="J37" s="26" t="inlineStr">
         <is>
-          <t>CNT-004</t>
+          <t>CNT-003</t>
         </is>
       </c>
       <c r="K37" s="26" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L37" s="26" t="inlineStr">
@@ -15356,27 +15403,27 @@
     <row r="38">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>ORD-00025</t>
+          <t>ORD-00041</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>Jacob Reed</t>
+          <t>Emma Clarke</t>
         </is>
       </c>
       <c r="C38" s="25" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Toledo Dutch Door</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>72" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E38" s="25" t="inlineStr">
         <is>
-          <t>Matte White</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="F38" s="25" t="inlineStr">
@@ -15386,27 +15433,27 @@
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H38" s="26" t="inlineStr">
         <is>
-          <t>SEV-72X80-MW-LI-FRS</t>
+          <t>TOL-36X80-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I38" s="26" t="inlineStr">
         <is>
-          <t>26-0707-0193</t>
+          <t>26-0622-0217</t>
         </is>
       </c>
       <c r="J38" s="26" t="inlineStr">
         <is>
-          <t>CNT-004</t>
+          <t>CNT-005</t>
         </is>
       </c>
       <c r="K38" s="26" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="L38" s="26" t="inlineStr">
@@ -15418,57 +15465,53 @@
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>ORD-00026</t>
+          <t>ORD-TEST</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>Olivia Bell</t>
+          <t>Test Customer</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>Cadiz Pivot Door</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>48" x 84"</t>
+          <t>36x80</t>
         </is>
       </c>
       <c r="E39" s="25" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H39" s="26" t="inlineStr">
         <is>
-          <t>CAD-48X84-BN-LI-FRS</t>
+          <t>VAL-36X80-MB-RI-CLR</t>
         </is>
       </c>
       <c r="I39" s="26" t="inlineStr">
         <is>
-          <t>26-0714-0095</t>
-        </is>
-      </c>
-      <c r="J39" s="26" t="inlineStr">
-        <is>
-          <t>CNT-002</t>
-        </is>
-      </c>
+          <t>25-0101-0001</t>
+        </is>
+      </c>
+      <c r="J39" s="26" t="n"/>
       <c r="K39" s="26" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="L39" s="26" t="inlineStr">
@@ -15480,27 +15523,27 @@
     <row r="40">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>ORD-00026</t>
+          <t>ORD-00033</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Olivia Bell</t>
+          <t>James Rivera</t>
         </is>
       </c>
       <c r="C40" s="25" t="inlineStr">
         <is>
-          <t>Cadiz Pivot Door</t>
+          <t>Altea Double Door</t>
         </is>
       </c>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>48" x 84"</t>
+          <t>72" x 80"</t>
         </is>
       </c>
       <c r="E40" s="25" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="F40" s="25" t="inlineStr">
@@ -15510,212 +15553,30 @@
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H40" s="26" t="inlineStr">
         <is>
-          <t>CAD-48X84-BN-LI-FRS</t>
+          <t>ALT-72X80-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I40" s="26" t="inlineStr">
         <is>
-          <t>26-0714-0096</t>
+          <t>26-0625-0073</t>
         </is>
       </c>
       <c r="J40" s="26" t="inlineStr">
         <is>
-          <t>CNT-002</t>
+          <t>CNT-001</t>
         </is>
       </c>
       <c r="K40" s="26" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="L40" s="26" t="inlineStr">
-        <is>
-          <t>Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>ORD-00040</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>Nathan Castillo</t>
-        </is>
-      </c>
-      <c r="C41" s="25" t="inlineStr">
-        <is>
-          <t>Sevilla French Door</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="G41" s="25" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="H41" s="26" t="inlineStr">
-        <is>
-          <t>SEV-32X80-BN-RI-RN</t>
-        </is>
-      </c>
-      <c r="I41" s="26" t="inlineStr">
-        <is>
-          <t>26-0618-0155</t>
-        </is>
-      </c>
-      <c r="J41" s="26" t="inlineStr">
-        <is>
-          <t>CNT-003</t>
-        </is>
-      </c>
-      <c r="K41" s="26" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="L41" s="26" t="inlineStr">
-        <is>
-          <t>Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>ORD-00041</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>Emma Clarke</t>
-        </is>
-      </c>
-      <c r="C42" s="25" t="inlineStr">
-        <is>
-          <t>Toledo Dutch Door</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="E42" s="25" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="F42" s="25" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="G42" s="25" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="H42" s="26" t="inlineStr">
-        <is>
-          <t>TOL-36X80-MB-LI-CLR</t>
-        </is>
-      </c>
-      <c r="I42" s="26" t="inlineStr">
-        <is>
-          <t>26-0622-0217</t>
-        </is>
-      </c>
-      <c r="J42" s="26" t="inlineStr">
-        <is>
-          <t>CNT-005</t>
-        </is>
-      </c>
-      <c r="K42" s="26" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="L42" s="26" t="inlineStr">
-        <is>
-          <t>Allocated</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>ORD-TEST</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="inlineStr">
-        <is>
-          <t>Test Customer</t>
-        </is>
-      </c>
-      <c r="C43" s="25" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>36x80</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="F43" s="25" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="G43" s="25" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="H43" s="26" t="inlineStr">
-        <is>
-          <t>VAL-36X80-MB-RI-CLR</t>
-        </is>
-      </c>
-      <c r="I43" s="26" t="inlineStr">
-        <is>
-          <t>25-0101-0001</t>
-        </is>
-      </c>
-      <c r="J43" s="26" t="n"/>
-      <c r="K43" s="26" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="L43" s="26" t="inlineStr">
         <is>
           <t>Allocated</t>
         </is>
@@ -15732,7 +15593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15978,7 +15839,7 @@
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>26-0625-0073</t>
+          <t>26-0625-0074</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr">
@@ -16000,27 +15861,27 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>ORD-00033</t>
+          <t>ORD-00034</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>James Rivera</t>
+          <t>Emma Thompson</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Altea Double Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>72" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Gunmetal</t>
         </is>
       </c>
       <c r="F5" s="25" t="inlineStr">
@@ -16030,17 +15891,17 @@
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H5" s="26" t="inlineStr">
         <is>
-          <t>ALT-72X80-MB-LI-CLR</t>
+          <t>MAL-36X80-GM-LI-NON</t>
         </is>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t>26-0625-0074</t>
+          <t>26-0618-0056</t>
         </is>
       </c>
       <c r="J5" s="26" t="inlineStr">
@@ -16062,27 +15923,27 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>ORD-00034</t>
+          <t>ORD-00035</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>Emma Thompson</t>
+          <t>David Chen</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>Malaga Single Door</t>
+          <t>Granada Bi-fold Door</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>96" x 80"</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>Gunmetal</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="F6" s="25" t="inlineStr">
@@ -16092,17 +15953,17 @@
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H6" s="26" t="inlineStr">
         <is>
-          <t>MAL-36X80-GM-LI-NON</t>
+          <t>GRN-96X80-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I6" s="26" t="inlineStr">
         <is>
-          <t>26-0618-0056</t>
+          <t>26-0611-0049</t>
         </is>
       </c>
       <c r="J6" s="26" t="inlineStr">
@@ -16164,7 +16025,7 @@
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
-          <t>26-0611-0049</t>
+          <t>26-0611-0050</t>
         </is>
       </c>
       <c r="J7" s="26" t="inlineStr">
@@ -16186,27 +16047,27 @@
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>ORD-00035</t>
+          <t>ORD-00036</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Linda Park</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>Granada Bi-fold Door</t>
+          <t>Sevilla French Door</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>96" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="F8" s="25" t="inlineStr">
@@ -16216,24 +16077,20 @@
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
-          <t>GRN-96X80-MB-LI-CLR</t>
+          <t>SEV-36X80-SW-LI-NON</t>
         </is>
       </c>
       <c r="I8" s="26" t="inlineStr">
         <is>
-          <t>26-0611-0050</t>
-        </is>
-      </c>
-      <c r="J8" s="26" t="inlineStr">
-        <is>
-          <t>CNT-001</t>
-        </is>
-      </c>
+          <t>24-1102-0019</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="n"/>
       <c r="K8" s="26" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -16248,27 +16105,27 @@
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>ORD-00036</t>
+          <t>ORD-00037</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Linda Park</t>
+          <t>Robert Kim</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Sevilla French Door</t>
+          <t>Cordova Sliding Window</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>48" x 36"</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="F9" s="25" t="inlineStr">
@@ -16278,20 +16135,24 @@
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="H9" s="26" t="inlineStr">
         <is>
-          <t>SEV-36X80-SW-LI-NON</t>
+          <t>COR-48X36-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
-          <t>24-1102-0019</t>
-        </is>
-      </c>
-      <c r="J9" s="26" t="n"/>
+          <t>26-0604-0034</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>CNT-001</t>
+        </is>
+      </c>
       <c r="K9" s="26" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -16346,7 +16207,7 @@
       </c>
       <c r="I10" s="26" t="inlineStr">
         <is>
-          <t>26-0604-0034</t>
+          <t>26-0604-0035</t>
         </is>
       </c>
       <c r="J10" s="26" t="inlineStr">
@@ -16368,22 +16229,22 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>ORD-00037</t>
+          <t>ORD-00038</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>Robert Kim</t>
+          <t>Jessica Adams</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Cordova Sliding Window</t>
+          <t>Valencia Single Door</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>48" x 36"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
@@ -16403,12 +16264,12 @@
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>COR-48X36-MB-LI-CLR</t>
+          <t>VAL-32X80-MB-LI-CLR</t>
         </is>
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
-          <t>26-0604-0035</t>
+          <t>26-0502-0010</t>
         </is>
       </c>
       <c r="J11" s="26" t="inlineStr">
@@ -16430,17 +16291,17 @@
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>ORD-00038</t>
+          <t>ORD-00039</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Jessica Adams</t>
+          <t>Michael Torres</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>Valencia Single Door</t>
+          <t>Malaga Single Door</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
@@ -16450,7 +16311,7 @@
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
@@ -16460,17 +16321,17 @@
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>VAL-32X80-MB-LI-CLR</t>
+          <t>MAL-32X80-BN-LI-NON</t>
         </is>
       </c>
       <c r="I12" s="26" t="inlineStr">
         <is>
-          <t>26-0502-0010</t>
+          <t>26-0618-0052</t>
         </is>
       </c>
       <c r="J12" s="26" t="inlineStr">
@@ -16492,12 +16353,12 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>ORD-00039</t>
+          <t>ORD-00006</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Michael Torres</t>
+          <t>Lisa Chen</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
@@ -16507,45 +16368,227 @@
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>Gunmetal</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>MAL-36X80-GM-LI-NON</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>26-0618-0057</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="inlineStr">
+        <is>
+          <t>CNT-001</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>In Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>ORD-00006</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Lisa Chen</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Malaga Single Door</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>Gunmetal</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>MAL-36X80-GM-LI-NON</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>26-0618-0058</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>CNT-001</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>In Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>ORD-00012</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Rachel Kim</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>Sevilla French Door</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="G13" s="25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H13" s="26" t="inlineStr">
-        <is>
-          <t>MAL-32X80-BN-LI-NON</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="inlineStr">
-        <is>
-          <t>26-0618-0052</t>
-        </is>
-      </c>
-      <c r="J13" s="26" t="inlineStr">
-        <is>
-          <t>CNT-001</t>
-        </is>
-      </c>
-      <c r="K13" s="26" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>SEV-32X80-BN-RI-RN</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>24-1102-0014</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n"/>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="inlineStr">
+        <is>
+          <t>In Prep</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>ORD-00012</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Rachel Kim</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Segovia Barn Door</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>48" x 84"</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>SEG-48X84-MB-RI-CLR</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>26-0622-0238</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="inlineStr">
+        <is>
+          <t>CNT-005</t>
+        </is>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="inlineStr">
         <is>
           <t>In Prep</t>
         </is>
